--- a/HoneyMetrics_Backlog_Scrum.xlsx
+++ b/HoneyMetrics_Backlog_Scrum.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -54,6 +54,20 @@
       <name val="Calibri"/>
       <color rgb="00000000"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <b val="1"/>
+      <color rgb="000284C7"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="002563EB"/>
+      <sz val="10"/>
+      <u val="single"/>
     </font>
   </fonts>
   <fills count="5">
@@ -108,7 +122,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -131,6 +145,18 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3536,14 +3562,14 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="45" customWidth="1" min="6" max="6"/>
     <col width="55" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
@@ -3604,7 +3630,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>Mockup / UI</t>
+          <t>Mockup / UI (React)</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -3619,7 +3645,7 @@
           <t>PB-HM-02.1</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>PB-HM-02</t>
         </is>
@@ -3650,9 +3676,9 @@
           <t>5</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>mockups/mockup_login_3d.jpg</t>
+      <c r="I5" s="11" t="inlineStr">
+        <is>
+          <t>src/pages/Login.jsx</t>
         </is>
       </c>
       <c r="J5" s="6" t="inlineStr">
@@ -3667,7 +3693,7 @@
           <t>PB-HM-07.1</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>PB-HM-07</t>
         </is>
@@ -3698,9 +3724,9 @@
           <t>5</t>
         </is>
       </c>
-      <c r="I6" s="8" t="inlineStr">
-        <is>
-          <t>mockups/mockup_login_otp.jpg</t>
+      <c r="I6" s="13" t="inlineStr">
+        <is>
+          <t>src/pages/Login.jsx</t>
         </is>
       </c>
       <c r="J6" s="9" t="inlineStr">
@@ -3715,7 +3741,7 @@
           <t>PB-HM-08.1</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>PB-HM-08</t>
         </is>
@@ -3746,9 +3772,9 @@
           <t>3</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>mockups/mockup_qr_setup.jpg</t>
+      <c r="I7" s="11" t="inlineStr">
+        <is>
+          <t>src/pages/Login.jsx</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
@@ -3763,7 +3789,7 @@
           <t>PB-HM-71.1</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>PB-HM-71</t>
         </is>
@@ -3794,9 +3820,9 @@
           <t>5</t>
         </is>
       </c>
-      <c r="I8" s="8" t="inlineStr">
-        <is>
-          <t>mockups/mockup_threat_list.jpg</t>
+      <c r="I8" s="13" t="inlineStr">
+        <is>
+          <t>src/pages/ThreatCenter.jsx</t>
         </is>
       </c>
       <c r="J8" s="9" t="inlineStr">
@@ -3811,7 +3837,7 @@
           <t>PB-HM-72.1</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>PB-HM-72</t>
         </is>
@@ -3842,9 +3868,9 @@
           <t>5</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>mockups/mockup_threat_create.jpg</t>
+      <c r="I9" s="11" t="inlineStr">
+        <is>
+          <t>src/components/threats/ThreatModal.jsx</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
@@ -3859,7 +3885,7 @@
           <t>PB-HM-73.1</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>PB-HM-73</t>
         </is>
@@ -3890,9 +3916,9 @@
           <t>3</t>
         </is>
       </c>
-      <c r="I10" s="8" t="inlineStr">
-        <is>
-          <t>mockups/mockup_threat_edit.jpg</t>
+      <c r="I10" s="13" t="inlineStr">
+        <is>
+          <t>src/components/threats/ThreatModal.jsx</t>
         </is>
       </c>
       <c r="J10" s="9" t="inlineStr">
@@ -3907,7 +3933,7 @@
           <t>PB-HM-74.1</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>PB-HM-74</t>
         </is>
@@ -3938,9 +3964,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
-          <t>mockups/mockup_threat_delete.jpg</t>
+      <c r="I11" s="11" t="inlineStr">
+        <is>
+          <t>src/pages/ThreatCenter.jsx</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
@@ -3955,7 +3981,7 @@
           <t>PB-HM-62.1</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>PB-HM-62</t>
         </is>
@@ -3986,9 +4012,9 @@
           <t>5</t>
         </is>
       </c>
-      <c r="I12" s="8" t="inlineStr">
-        <is>
-          <t>mockups/mockup_botnet_alert.jpg</t>
+      <c r="I12" s="13" t="inlineStr">
+        <is>
+          <t>src/components/threats/BotnetAlertBadge.jsx</t>
         </is>
       </c>
       <c r="J12" s="9" t="inlineStr">
@@ -4003,7 +4029,7 @@
           <t>PB-HM-63.1</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>PB-HM-63</t>
         </is>
@@ -4034,9 +4060,9 @@
           <t>5</t>
         </is>
       </c>
-      <c r="I13" s="5" t="inlineStr">
-        <is>
-          <t>mockups/mockup_bot_classifier.jpg</t>
+      <c r="I13" s="11" t="inlineStr">
+        <is>
+          <t>src/components/threats/ThreatScoreCard.jsx</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
@@ -4051,7 +4077,7 @@
           <t>PB-HM-26.1</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>PB-HM-26</t>
         </is>
@@ -4082,9 +4108,9 @@
           <t>8</t>
         </is>
       </c>
-      <c r="I14" s="8" t="inlineStr">
-        <is>
-          <t>mockups/mockup_plotly_dashboard.jpg</t>
+      <c r="I14" s="13" t="inlineStr">
+        <is>
+          <t>src/pages/DashboardPage.jsx</t>
         </is>
       </c>
       <c r="J14" s="9" t="inlineStr">
@@ -4099,7 +4125,7 @@
           <t>PB-HM-27.1</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>PB-HM-27</t>
         </is>
@@ -4130,9 +4156,9 @@
           <t>3</t>
         </is>
       </c>
-      <c r="I15" s="5" t="inlineStr">
-        <is>
-          <t>mockups/mockup_time_filter.jpg</t>
+      <c r="I15" s="11" t="inlineStr">
+        <is>
+          <t>src/components/dashboard/PlotlyCharts.jsx</t>
         </is>
       </c>
       <c r="J15" s="6" t="inlineStr">
@@ -4147,7 +4173,7 @@
           <t>PB-HM-70.1</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>PB-HM-70</t>
         </is>
@@ -4178,9 +4204,9 @@
           <t>3</t>
         </is>
       </c>
-      <c r="I16" s="8" t="inlineStr">
-        <is>
-          <t>mockups/mockup_predictive_heatmap.jpg</t>
+      <c r="I16" s="13" t="inlineStr">
+        <is>
+          <t>src/components/dashboard/PlotlyCharts.jsx</t>
         </is>
       </c>
       <c r="J16" s="9" t="inlineStr">
@@ -4195,7 +4221,7 @@
           <t>PB-HM-37.1</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>PB-HM-37</t>
         </is>
@@ -4226,9 +4252,9 @@
           <t>8</t>
         </is>
       </c>
-      <c r="I17" s="5" t="inlineStr">
-        <is>
-          <t>mockups/mockup_async_export.jpg</t>
+      <c r="I17" s="11" t="inlineStr">
+        <is>
+          <t>src/pages/LogsReport.jsx</t>
         </is>
       </c>
       <c r="J17" s="6" t="inlineStr">
@@ -4243,7 +4269,7 @@
           <t>PB-HM-38.1</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>PB-HM-38</t>
         </is>
@@ -4274,9 +4300,9 @@
           <t>3</t>
         </is>
       </c>
-      <c r="I18" s="8" t="inlineStr">
-        <is>
-          <t>mockups/mockup_export_history.jpg</t>
+      <c r="I18" s="13" t="inlineStr">
+        <is>
+          <t>src/pages/LogsReport.jsx</t>
         </is>
       </c>
       <c r="J18" s="9" t="inlineStr">
@@ -4291,7 +4317,7 @@
           <t>PB-HM-39.1</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>PB-HM-39</t>
         </is>
@@ -4322,9 +4348,9 @@
           <t>3</t>
         </is>
       </c>
-      <c r="I19" s="5" t="inlineStr">
-        <is>
-          <t>mockups/mockup_jsonl_download.jpg</t>
+      <c r="I19" s="11" t="inlineStr">
+        <is>
+          <t>src/pages/LogsReport.jsx</t>
         </is>
       </c>
       <c r="J19" s="6" t="inlineStr">
@@ -4339,7 +4365,7 @@
           <t>PB-HM-40.1</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>PB-HM-40</t>
         </is>
@@ -4370,9 +4396,9 @@
           <t>8</t>
         </is>
       </c>
-      <c r="I20" s="8" t="inlineStr">
-        <is>
-          <t>mockups/mockup_telegram_approval.jpg</t>
+      <c r="I20" s="13" t="inlineStr">
+        <is>
+          <t>src/components/logs/ExportModal.jsx</t>
         </is>
       </c>
       <c r="J20" s="9" t="inlineStr">
@@ -4387,7 +4413,7 @@
           <t>PB-HM-42.1</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>PB-HM-42</t>
         </is>
@@ -4418,9 +4444,9 @@
           <t>5</t>
         </is>
       </c>
-      <c r="I21" s="5" t="inlineStr">
-        <is>
-          <t>mockups/mockup_pdf_generator.jpg</t>
+      <c r="I21" s="11" t="inlineStr">
+        <is>
+          <t>src/utils/PdfGenerator.js</t>
         </is>
       </c>
       <c r="J21" s="6" t="inlineStr">
@@ -4435,7 +4461,7 @@
           <t>PB-HM-44.1</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B22" s="12" t="inlineStr">
         <is>
           <t>PB-HM-44</t>
         </is>
@@ -4466,9 +4492,9 @@
           <t>8</t>
         </is>
       </c>
-      <c r="I22" s="8" t="inlineStr">
-        <is>
-          <t>mockups/mockup_spike_alert.jpg</t>
+      <c r="I22" s="13" t="inlineStr">
+        <is>
+          <t>src/components/layout/StatusBanner.jsx</t>
         </is>
       </c>
       <c r="J22" s="9" t="inlineStr">
@@ -4483,7 +4509,7 @@
           <t>PB-HM-65.1</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B23" s="10" t="inlineStr">
         <is>
           <t>PB-HM-65</t>
         </is>
@@ -4514,9 +4540,9 @@
           <t>3</t>
         </is>
       </c>
-      <c r="I23" s="5" t="inlineStr">
-        <is>
-          <t>mockups/mockup_honeypot_advisor.jpg</t>
+      <c r="I23" s="11" t="inlineStr">
+        <is>
+          <t>src/pages/DashboardMock.jsx</t>
         </is>
       </c>
       <c r="J23" s="6" t="inlineStr">
@@ -4531,7 +4557,7 @@
           <t>PB-HM-64.1</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>PB-HM-64</t>
         </is>
@@ -4562,9 +4588,9 @@
           <t>8</t>
         </is>
       </c>
-      <c r="I24" s="8" t="inlineStr">
-        <is>
-          <t>mockups/mockup_patch_intel.jpg</t>
+      <c r="I24" s="13" t="inlineStr">
+        <is>
+          <t>src/pages/Dashboard.jsx</t>
         </is>
       </c>
       <c r="J24" s="9" t="inlineStr">
@@ -4579,7 +4605,7 @@
           <t>PB-HM-66.1</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B25" s="10" t="inlineStr">
         <is>
           <t>PB-HM-66</t>
         </is>
@@ -4610,9 +4636,9 @@
           <t>8</t>
         </is>
       </c>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>mockups/mockup_fim_timeline.jpg</t>
+      <c r="I25" s="11" t="inlineStr">
+        <is>
+          <t>src/pages/ThreatCenter.jsx</t>
         </is>
       </c>
       <c r="J25" s="6" t="inlineStr">
@@ -4627,7 +4653,7 @@
           <t>PB-HM-67.1</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B26" s="12" t="inlineStr">
         <is>
           <t>PB-HM-67</t>
         </is>
@@ -4658,9 +4684,9 @@
           <t>8</t>
         </is>
       </c>
-      <c r="I26" s="8" t="inlineStr">
-        <is>
-          <t>N/A (Lógica backend)</t>
+      <c r="I26" s="13" t="inlineStr">
+        <is>
+          <t>src/mocks/threatsDatabase.js</t>
         </is>
       </c>
       <c r="J26" s="9" t="inlineStr">
@@ -4675,7 +4701,7 @@
           <t>PB-HM-67.2</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B27" s="10" t="inlineStr">
         <is>
           <t>PB-HM-67</t>
         </is>
@@ -4706,9 +4732,9 @@
           <t>5</t>
         </is>
       </c>
-      <c r="I27" s="5" t="inlineStr">
-        <is>
-          <t>mockups/mockup_kill_chain_ui.jpg</t>
+      <c r="I27" s="11" t="inlineStr">
+        <is>
+          <t>src/pages/ThreatCenter.jsx</t>
         </is>
       </c>
       <c r="J27" s="6" t="inlineStr">
@@ -4723,7 +4749,7 @@
           <t>PB-HM-68.1</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B28" s="12" t="inlineStr">
         <is>
           <t>PB-HM-68</t>
         </is>
@@ -4754,9 +4780,9 @@
           <t>5</t>
         </is>
       </c>
-      <c r="I28" s="8" t="inlineStr">
-        <is>
-          <t>mockups/mockup_hitl_rootcheck.jpg</t>
+      <c r="I28" s="13" t="inlineStr">
+        <is>
+          <t>src/pages/ThreatCenter.jsx</t>
         </is>
       </c>
       <c r="J28" s="9" t="inlineStr">
@@ -4771,7 +4797,7 @@
           <t>PB-HM-69.1</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B29" s="10" t="inlineStr">
         <is>
           <t>PB-HM-69</t>
         </is>
@@ -4802,9 +4828,9 @@
           <t>5</t>
         </is>
       </c>
-      <c r="I29" s="5" t="inlineStr">
-        <is>
-          <t>mockups/mockup_cis_compliance.jpg</t>
+      <c r="I29" s="11" t="inlineStr">
+        <is>
+          <t>src/pages/DashboardMock.jsx</t>
         </is>
       </c>
       <c r="J29" s="6" t="inlineStr">
@@ -4819,7 +4845,7 @@
           <t>PB-HM-48.1</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="B30" s="12" t="inlineStr">
         <is>
           <t>PB-HM-48</t>
         </is>
@@ -4850,9 +4876,9 @@
           <t>8</t>
         </is>
       </c>
-      <c r="I30" s="8" t="inlineStr">
-        <is>
-          <t>mockups/mockup_ml_metrics.jpg</t>
+      <c r="I30" s="13" t="inlineStr">
+        <is>
+          <t>src/pages/DashboardMock.jsx</t>
         </is>
       </c>
       <c r="J30" s="9" t="inlineStr">
@@ -4867,7 +4893,7 @@
           <t>PB-HM-56.1</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B31" s="10" t="inlineStr">
         <is>
           <t>PB-HM-56</t>
         </is>
@@ -4898,9 +4924,9 @@
           <t>3</t>
         </is>
       </c>
-      <c r="I31" s="5" t="inlineStr">
-        <is>
-          <t>N/A (Lógica global)</t>
+      <c r="I31" s="11" t="inlineStr">
+        <is>
+          <t>src/context/AuthContext.jsx</t>
         </is>
       </c>
       <c r="J31" s="6" t="inlineStr">
@@ -4910,6 +4936,62 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I17" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I27" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I28" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B29" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I29" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B30" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I30" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="rId54"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/HoneyMetrics_Backlog_Scrum.xlsx
+++ b/HoneyMetrics_Backlog_Scrum.xlsx
@@ -2758,9 +2758,9 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>- [ ] Diseñar e implementar el componente UI necesario
-- [ ] Establecer lógica de estado (React hooks) y validaciones
-- [ ] Conectar la interfaz con la API Backend correspondiente</t>
+          <t>- [ ] Configurar proveedor de correos transaccionales (Resend) y verificar dominio `johan-d3v.site` en Cloudflare (registros SPF, DKIM, DMARC).
+- [ ] Plan de Contingencia (Opción B): Si fallan los filtros universitarios, documentar e implementar envío de correos vía Microsoft Graph API usando un entorno M365 Developer.
+- [ ] Integrar SDK de correo en FastAPI y conectar UI (React) para solicitar y procesar el token de recuperación de contraseña.</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">

--- a/HoneyMetrics_Backlog_Scrum.xlsx
+++ b/HoneyMetrics_Backlog_Scrum.xlsx
@@ -4,55 +4,80 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PRODUCT BACKLOG" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HISTORIAS DE USUARIO" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
+      <charset val="1"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="0"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="0"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="0"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
+      <charset val="1"/>
+      <family val="0"/>
       <b val="1"/>
-      <color rgb="00000000"/>
+      <color rgb="FF000000"/>
       <sz val="16"/>
     </font>
     <font>
       <name val="Calibri"/>
+      <charset val="1"/>
+      <family val="0"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="00000000"/>
+      <charset val="1"/>
+      <family val="0"/>
+      <color rgb="FF000000"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
+      <charset val="1"/>
+      <family val="0"/>
       <b val="1"/>
-      <color rgb="00000000"/>
+      <color rgb="FF000000"/>
       <sz val="11"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <color rgb="000000FF"/>
-      <sz val="10"/>
+      <name val="Cambria"/>
+      <charset val="1"/>
+      <family val="0"/>
+      <color rgb="FF0563C1"/>
+      <sz val="11"/>
       <u val="single"/>
     </font>
   </fonts>
@@ -65,14 +90,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00808080"/>
-        <bgColor rgb="00808080"/>
+        <fgColor rgb="FF808080"/>
+        <bgColor rgb="FF969696"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C2D69B"/>
-        <bgColor rgb="00C2D69B"/>
+        <fgColor rgb="FFC2D69B"/>
+        <bgColor rgb="FFFFCC99"/>
       </patternFill>
     </fill>
   </fills>
@@ -85,153 +110,178 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="00000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="00000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="00000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00000000"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="16">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="6">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
+    <cellStyle name="Currency" xfId="3" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
+    <cellStyle name="Percent" xfId="5" builtinId="5"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFC2D69B"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0563C1"/>
+      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
     </indexedColors>
   </colors>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="1f497d"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="eeece1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4f81bd"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="c0504d"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="9bbb59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="8064a2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="4bacc6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="f79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0000ff"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -239,2524 +289,2504 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme>
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="50000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="35000">
               <a:schemeClr val="phClr">
                 <a:tint val="37000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:tint val="15000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:shade val="51000"/>
-                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
                 <a:shade val="93000"/>
-                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="94000"/>
-                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
+          <a:effectLst/>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="40000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="40000">
               <a:schemeClr val="phClr">
                 <a:tint val="45000"/>
                 <a:shade val="99000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="20000"/>
-                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="80000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="30000"/>
-                <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
+  <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="A2:G76"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" style="8" min="1" max="1"/>
+    <col width="70" customWidth="1" style="8" min="2" max="2"/>
+    <col width="15" customWidth="1" style="8" min="3" max="5"/>
   </cols>
   <sheetData>
-    <row r="2">
-      <c r="C2" s="1" t="inlineStr">
+    <row r="2" ht="19.7" customHeight="1" s="9">
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>PRODUCT BACKLOG</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="8" t="inlineStr">
         <is>
           <t>NOMBRE EQUIPO ---</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="8" t="inlineStr">
         <is>
           <t>Johan Posada y Juan Pablo Fonseca</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="F3" t="inlineStr">
+    <row r="3" ht="15" customHeight="1" s="9">
+      <c r="F3" s="8" t="inlineStr">
         <is>
           <t>PROYECTO ---</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="8" t="inlineStr">
         <is>
           <t>HoneyMetrics 2.0</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="25" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="6" ht="24.75" customHeight="1" s="9">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>CODIGO PB</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>CARACTERÍSTICA</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>PRIORIDAD</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>ESTADO</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>SPRINT</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
+    <row r="7" ht="30" customHeight="1" s="9">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>PB-HM-01</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>Visualizar página de inicio pública (Landing Page) — El sistema debe mostrar una página de bienvenida profesional que explique el propósito de HoneyMetrics y ofrezca el punto de acceso (Login). Incluye navbar, sección hero, muestra de código y mapa de calor ilustrativo.</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>Sin empezar</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>Sin empezar</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
+    <row r="8" ht="30" customHeight="1" s="9">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>PB-HM-02</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>Iniciar sesión con credenciales institucionales — El usuario debe poder autenticarse en la plataforma usando su correo @ucundinamarca.edu.co y contraseña. El sistema debe validar credenciales, identificar el rol y redirigir al dashboard correspondiente.</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Sin empezar</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>Sin empezar</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
+    <row r="9" ht="30" customHeight="1" s="9">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>PB-HM-03</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>Bloquear acceso por credenciales inválidas — El sistema debe rechazar el ingreso cuando el correo o contraseña sean incorrectos, mostrando un mensaje de error claro sin revelar cuál campo falló (anti-enumeración).</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Sin empezar</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>Sin empezar</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
+    <row r="10" ht="30" customHeight="1" s="9">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>PB-HM-04</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>Forzar cambio de contraseña en primer inicio de sesión — Al detectar que el usuario tiene contraseña temporal, el sistema debe redirigirlo obligatoriamente a una vista de cambio de clave antes de permitir el acceso al dashboard.</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="12" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>Sin empezar</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>Sin empezar</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+    <row r="11" ht="30" customHeight="1" s="9">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>PB-HM-05</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>Cambiar contraseña voluntariamente (usuario autenticado) — Cualquier usuario con sesión activa debe poder actualizar su contraseña desde su perfil, verificando la clave actual y cumpliendo los criterios de seguridad (min. 8 caracteres, no común, alfanumérica).</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>Sin empezar</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>Sin empezar</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
+    <row r="12" ht="30" customHeight="1" s="9">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>PB-HM-06</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t>Restablecer contraseña olvidada vía correo electrónico — Un usuario que no pueda iniciar sesión debe poder solicitar un enlace de restablecimiento enviado a su correo institucional. El token debe ser de un solo uso y expirar en 24 horas.</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="12" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>Sin empezar</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>Sin empezar</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
+    <row r="13" ht="30" customHeight="1" s="9">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>PB-HM-07</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>Autenticar con segundo factor (2FA-OTP) — Después de ingresar usuario y contraseña correctamente, el sistema debe solicitar un código OTP de 6 dígitos generado por Google Authenticator para completar el acceso.</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="12" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>Sin empezar</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>Sin empezar</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="14" ht="30" customHeight="1" s="9">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>PB-HM-08</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="13" t="inlineStr">
         <is>
           <t>Vincular Google Authenticator en el primer inicio — Si el usuario no ha configurado el 2FA previamente, el sistema debe mostrar un código QR para que escanee con su app autenticadora, verificando la sincronización antes de conceder acceso.</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="12" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>Sin empezar</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>Sin empezar</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
+    <row r="15" ht="30" customHeight="1" s="9">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>PB-HM-09</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="13" t="inlineStr">
         <is>
           <t>Cerrar sesión de forma segura — El usuario debe poder finalizar su sesión desde cualquier vista del dashboard. El sistema debe invalidar el token JWT en el servidor y limpiar el almacenamiento local del navegador, impidiendo re-acceso con el botón "Atrás".</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="12" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>Sin empezar</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>Sin empezar</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
+    <row r="16" ht="30" customHeight="1" s="9">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>PB-HM-10</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="13" t="inlineStr">
         <is>
           <t>Redireccionar al login al acceder a rutas protegidas sin sesión — Cualquier intento de acceso a rutas del dashboard sin token de sesión válido debe resultar en redirección automática al Login.</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="12" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>Sin empezar</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>Sin empezar</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
+    <row r="17" ht="30" customHeight="1" s="9">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t>PB-HM-11</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="13" t="inlineStr">
         <is>
           <t>Mostrar banner informativo a usuarios sin rol asignado — Si un usuario se autentica correctamente pero no tiene ningún rol asignado, el sistema debe mostrarlo con acceso mínimo y un mensaje informativo indicando que debe solicitar permisos al Administrador.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="12" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>Sin empezar</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>Sin empezar</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
+    <row r="18" ht="30" customHeight="1" s="9">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>PB-HM-12</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="13" t="inlineStr">
         <is>
           <t>Acceder al panel de administración del sistema — El Administrador debe poder acceder desde el frontend al panel de administración profunda haciendo clic en "Gestión", sin necesidad de escribir la URL manualmente.</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="12" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>Sin empezar</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>Sin empezar</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
+    <row r="19" ht="30" customHeight="1" s="9">
+      <c r="A19" s="12" t="inlineStr">
         <is>
           <t>PB-HM-13</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" s="13" t="inlineStr">
         <is>
           <t>Crear un nuevo Rol/Grupo de permisos — El Administrador debe poder crear nuevos grupos de permisos con nombre único (ej. "Consultor de Ciberseguridad") y asignarles los permisos específicos disponibles en el sistema.</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" s="12" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>Sin empezar</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>Sin empezar</t>
+        </is>
+      </c>
+      <c r="E19" s="12" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
+    <row r="20" ht="30" customHeight="1" s="9">
+      <c r="A20" s="12" t="inlineStr">
         <is>
           <t>PB-HM-14</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B20" s="13" t="inlineStr">
         <is>
           <t>Consultar la lista de Roles/Grupos existentes — El Administrador debe poder visualizar todos los grupos de permisos registrados en el sistema, con su nombre y la cantidad de usuarios asociados.</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" s="12" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>Sin empezar</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>Sin empezar</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
+    <row r="21" ht="30" customHeight="1" s="9">
+      <c r="A21" s="12" t="inlineStr">
         <is>
           <t>PB-HM-15</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" s="13" t="inlineStr">
         <is>
           <t>Modificar un Rol/Grupo de permisos existente — El Administrador debe poder editar el nombre o los permisos asignados a un grupo. Los cambios deben aplicarse inmediatamente a todos los usuarios que posean ese rol.</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C21" s="12" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>Sin empezar</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>Sin empezar</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="3" t="inlineStr">
+    <row r="22" ht="30" customHeight="1" s="9">
+      <c r="A22" s="12" t="inlineStr">
         <is>
           <t>PB-HM-16</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B22" s="13" t="inlineStr">
         <is>
           <t>Eliminar un Rol/Grupo de permisos — El Administrador debe poder borrar permanentemente un grupo del sistema, previo aviso de cuántos usuarios quedarán sin ese rol. La eliminación debe requerir confirmación explícita.</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C22" s="12" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>Sin empezar</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>Sin empezar</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
+    <row r="23" ht="30" customHeight="1" s="9">
+      <c r="A23" s="12" t="inlineStr">
         <is>
           <t>PB-HM-17</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B23" s="13" t="inlineStr">
         <is>
           <t>Crear cuenta de nuevo usuario — El Administrador debe poder registrar a un nuevo miembro del equipo (Directivo, Consultor o Analista) con nombre, correo institucional, contraseña temporal y rol asignado (máximo uno).</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C23" s="12" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>Sin empezar</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>Sin empezar</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="3" t="inlineStr">
+    <row r="24" ht="30" customHeight="1" s="9">
+      <c r="A24" s="12" t="inlineStr">
         <is>
           <t>PB-HM-18</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B24" s="13" t="inlineStr">
         <is>
           <t>Consultar la lista de usuarios registrados — El Administrador debe poder visualizar todos los usuarios del sistema en una tabla con columnas de: nombre, correo, rol y estado (activo/inactivo), con búsqueda y filtros.</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C24" s="12" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>Sin empezar</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>Sin empezar</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
+    <row r="25" ht="30" customHeight="1" s="9">
+      <c r="A25" s="12" t="inlineStr">
         <is>
           <t>PB-HM-19</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B25" s="13" t="inlineStr">
         <is>
           <t>Modificar datos de un usuario existente — El Administrador debe poder editar la información de perfil de cualquier usuario (nombre, correo, rol asignado) sin necesidad de eliminar y recrear la cuenta.</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C25" s="12" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>Sin empezar</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>Sin empezar</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
+    <row r="26" ht="30" customHeight="1" s="9">
+      <c r="A26" s="12" t="inlineStr">
         <is>
           <t>PB-HM-20</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B26" s="13" t="inlineStr">
         <is>
           <t>Eliminar un usuario del sistema — El Administrador debe poder borrar definitivamente un usuario y todos sus datos relacionados (en cascada), previo aviso detallado de los objetos que serán eliminados y confirmación explícita.</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C26" s="12" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>Sin empezar</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>Sin empezar</t>
+        </is>
+      </c>
+      <c r="E26" s="12" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
+    <row r="27" ht="30" customHeight="1" s="9">
+      <c r="A27" s="12" t="inlineStr">
         <is>
           <t>PB-HM-21</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B27" s="13" t="inlineStr">
         <is>
           <t>Visualizar y editar perfil de usuario propio — Cualquier usuario debe poder acceder a su perfil personal para ver su rol, zona horaria, cambiar su foto de perfil (JPG/PNG, máx. 2MB) y su preferencia de tema (claro/oscuro).</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C27" s="12" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>Sin empezar</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>Sin empezar</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="3" t="inlineStr">
+    <row r="28" ht="30" customHeight="1" s="9">
+      <c r="A28" s="12" t="inlineStr">
         <is>
           <t>PB-HM-22</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B28" s="13" t="inlineStr">
         <is>
           <t>Consultar la Lista Negra de IPs — Todos los roles deben poder visualizar el repositorio de IPs marcadas como amenaza en una tabla interactiva con paginación del lado del servidor (10 registros/página por defecto), búsqueda global y columnas de: IP, tipo, país, ataque y usuario reportador.</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C28" s="12" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>Sin empezar</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>Sin empezar</t>
+        </is>
+      </c>
+      <c r="E28" s="12" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
+    <row r="29" ht="30" customHeight="1" s="9">
+      <c r="A29" s="12" t="inlineStr">
         <is>
           <t>PB-HM-23</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B29" s="13" t="inlineStr">
         <is>
           <t>Agregar una IP a la Lista Negra — Los usuarios con rol operativo (Administrador, Consultor, Analista) deben poder registrar una nueva IP amenaza mediante un formulario modal, con validación de formato IPv4/IPv6 y asignación automática del usuario en sesión como creador.</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C29" s="12" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>Sin empezar</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>Sin empezar</t>
+        </is>
+      </c>
+      <c r="E29" s="12" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="3" t="inlineStr">
+    <row r="30" ht="30" customHeight="1" s="9">
+      <c r="A30" s="12" t="inlineStr">
         <is>
           <t>PB-HM-24</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B30" s="13" t="inlineStr">
         <is>
           <t>Eliminar una IP de la Lista Negra — Los usuarios con rol operativo deben poder remover un registro de la lista negra directamente desde la fila de la tabla, con confirmación previa para evitar borrados accidentales.</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C30" s="12" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>Sin empezar</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>Sin empezar</t>
+        </is>
+      </c>
+      <c r="E30" s="12" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="3" t="inlineStr">
+    <row r="31" ht="30" customHeight="1" s="9">
+      <c r="A31" s="12" t="inlineStr">
         <is>
           <t>PB-HM-25</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B31" s="13" t="inlineStr">
         <is>
           <t>Exportar la Lista Negra de IPs (CSV / Excel) — Los usuarios deben poder descargar la lista negra completa o filtrada en formato CSV o Excel (.xlsx), respetando los filtros activos al momento de la exportación. El botón de exportación debe deshabilitarse si no hay datos.</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C31" s="12" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>Sin empezar</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>Sin empezar</t>
+        </is>
+      </c>
+      <c r="E31" s="12" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="3" t="inlineStr">
+    <row r="32" ht="30" customHeight="1" s="9">
+      <c r="A32" s="12" t="inlineStr">
         <is>
           <t>PB-HM-26</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B32" s="13" t="inlineStr">
         <is>
           <t>Visualizar el Dashboard principal de ataques y estadísticas — Los usuarios deben poder ver un dashboard operativo con KPIs (total alertas, severidad promedio) y cuatro gráficos dinámicos: distribución por módulo (torta), histórico temporal (líneas), top agentes afectados (barras) y top eventos frecuentes (barras). El rango por defecto es la última semana.</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C32" s="12" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>Sin empezar</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
+      <c r="D32" s="12" t="inlineStr">
+        <is>
+          <t>Sin empezar</t>
+        </is>
+      </c>
+      <c r="E32" s="12" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="30" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
+    <row r="33" ht="30" customHeight="1" s="9">
+      <c r="A33" s="12" t="inlineStr">
         <is>
           <t>PB-HM-27</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B33" s="13" t="inlineStr">
         <is>
           <t>Filtrar el Dashboard por rango de fechas — Los usuarios deben poder cambiar el rango temporal de los gráficos del dashboard (ej. últimas 24h, última semana, último mes) y ver los KPIs y gráficos actualizarse instantáneamente.</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C33" s="12" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>Sin empezar</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="D33" s="12" t="inlineStr">
+        <is>
+          <t>Sin empezar</t>
+        </is>
+      </c>
+      <c r="E33" s="12" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="3" t="inlineStr">
+    <row r="34" ht="30" customHeight="1" s="9">
+      <c r="A34" s="12" t="inlineStr">
         <is>
           <t>PB-HM-28</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B34" s="13" t="inlineStr">
         <is>
           <t>Visualizar el Mapa de Calor Interactivo de ataques — Los usuarios deben poder visualizar un mapa mundial interactivo que muestre la procedencia geográfica de los ataques con escala de colores (verde a rojo según intensidad), tooltips por país y tabla "Top 10 Países Atacantes".</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="C34" s="12" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>Sin empezar</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
+      <c r="D34" s="12" t="inlineStr">
+        <is>
+          <t>Sin empezar</t>
+        </is>
+      </c>
+      <c r="E34" s="12" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="3" t="inlineStr">
+    <row r="35" ht="30" customHeight="1" s="9">
+      <c r="A35" s="12" t="inlineStr">
         <is>
           <t>PB-HM-29</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B35" s="13" t="inlineStr">
         <is>
           <t>Filtrar el Mapa de Calor por tipo de ataque — Los usuarios deben poder seleccionar un tipo de ataque específico (ej. "Fuerza Bruta SSH") y ver el mapa de calor actualizarse mostrando únicamente los ataques de ese tipo.</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C35" s="12" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>Sin empezar</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>Sin empezar</t>
+        </is>
+      </c>
+      <c r="E35" s="12" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="3" t="inlineStr">
+    <row r="36" ht="30" customHeight="1" s="9">
+      <c r="A36" s="12" t="inlineStr">
         <is>
           <t>PB-HM-30</t>
         </is>
       </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B36" s="13" t="inlineStr">
         <is>
           <t>Ver panel de detalle de país al hacer clic en el mapa — Al hacer clic en un país del mapa de calor, el sistema debe desplegar un panel lateral con el desglose de IPs, tipos de ataque y períodos de actividad para ese territorio.</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="C36" s="12" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>Sin empezar</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr">
+      <c r="D36" s="12" t="inlineStr">
+        <is>
+          <t>Sin empezar</t>
+        </is>
+      </c>
+      <c r="E36" s="12" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="30" customHeight="1">
-      <c r="A37" s="3" t="inlineStr">
+    <row r="37" ht="30" customHeight="1" s="9">
+      <c r="A37" s="12" t="inlineStr">
         <is>
           <t>PB-HM-31</t>
         </is>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B37" s="13" t="inlineStr">
         <is>
           <t>Visualizar Medidas de Tendencia Central (Estadística Descriptiva) — Los usuarios autorizados deben poder ver una vista de estadísticas con media, mediana, moda, desviación estándar y varianza de las variables de ataque, junto con un histograma de frecuencia y un diagrama de caja (boxplot).</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="C37" s="12" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>Sin empezar</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
+      <c r="D37" s="12" t="inlineStr">
+        <is>
+          <t>Sin empezar</t>
+        </is>
+      </c>
+      <c r="E37" s="12" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="30" customHeight="1">
-      <c r="A38" s="3" t="inlineStr">
+    <row r="38" ht="30" customHeight="1" s="9">
+      <c r="A38" s="12" t="inlineStr">
         <is>
           <t>PB-HM-32</t>
         </is>
       </c>
-      <c r="B38" s="4" t="inlineStr">
+      <c r="B38" s="13" t="inlineStr">
         <is>
           <t>Filtrar estadísticas descriptivas por variable de análisis y rango de fechas — Los usuarios deben poder seleccionar qué variable analizar y un rango de fechas, actualizando automáticamente todas las métricas y gráficos estadísticos.</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="C38" s="12" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>Sin empezar</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="inlineStr">
+      <c r="D38" s="12" t="inlineStr">
+        <is>
+          <t>Sin empezar</t>
+        </is>
+      </c>
+      <c r="E38" s="12" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="30" customHeight="1">
-      <c r="A39" s="3" t="inlineStr">
+    <row r="39" ht="30" customHeight="1" s="9">
+      <c r="A39" s="12" t="inlineStr">
         <is>
           <t>PB-HM-33</t>
         </is>
       </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B39" s="13" t="inlineStr">
         <is>
           <t>Exportar tabla de estadísticas descriptivas en CSV — El Analista debe poder descargar la tabla de medidas estadísticas en formato CSV con un solo clic.</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="C39" s="12" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>Sin empezar</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
+      <c r="D39" s="12" t="inlineStr">
+        <is>
+          <t>Sin empezar</t>
+        </is>
+      </c>
+      <c r="E39" s="12" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="30" customHeight="1">
-      <c r="A40" s="3" t="inlineStr">
+    <row r="40" ht="30" customHeight="1" s="9">
+      <c r="A40" s="12" t="inlineStr">
         <is>
           <t>PB-HM-34</t>
         </is>
       </c>
-      <c r="B40" s="4" t="inlineStr">
+      <c r="B40" s="13" t="inlineStr">
         <is>
           <t>Visualizar Matriz de Confusión interactiva del modelo de IA — Los usuarios autorizados deben poder ver la matriz de confusión (VP, FP, VN, FN) comparando predicciones del modelo de IA vs. clasificaciones reales, con indicadores derivados (Accuracy, Precision, Recall, F1-Score) y tooltips explicativos por celda.</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
+      <c r="C40" s="12" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>Sin empezar</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="inlineStr">
+      <c r="D40" s="12" t="inlineStr">
+        <is>
+          <t>Sin empezar</t>
+        </is>
+      </c>
+      <c r="E40" s="12" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="30" customHeight="1">
-      <c r="A41" s="3" t="inlineStr">
+    <row r="41" ht="30" customHeight="1" s="9">
+      <c r="A41" s="12" t="inlineStr">
         <is>
           <t>PB-HM-35</t>
         </is>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B41" s="13" t="inlineStr">
         <is>
           <t>Filtrar la Matriz de Confusión por tipo de ataque y rango de fechas — Los usuarios deben poder filtrar la matriz de confusión para un tipo de ataque específico y un período de tiempo, recalculando todos los indicadores de rendimiento.</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="C41" s="12" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>Sin empezar</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
+      <c r="D41" s="12" t="inlineStr">
+        <is>
+          <t>Sin empezar</t>
+        </is>
+      </c>
+      <c r="E41" s="12" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="30" customHeight="1">
-      <c r="A42" s="3" t="inlineStr">
+    <row r="42" ht="30" customHeight="1" s="9">
+      <c r="A42" s="12" t="inlineStr">
         <is>
           <t>PB-HM-36</t>
         </is>
       </c>
-      <c r="B42" s="4" t="inlineStr">
+      <c r="B42" s="13" t="inlineStr">
         <is>
           <t>Ver tabla de detalle al hacer clic en una celda de la Matriz — Al hacer clic en una celda de la matriz (ej. "Falsos Positivos"), el sistema debe desplegar una tabla expandible con los registros específicos (IP, fecha, tipo predicho, clasificación real, confianza del modelo).</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
+      <c r="C42" s="12" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>Sin empezar</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="inlineStr">
+      <c r="D42" s="12" t="inlineStr">
+        <is>
+          <t>Sin empezar</t>
+        </is>
+      </c>
+      <c r="E42" s="12" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="30" customHeight="1">
-      <c r="A43" s="3" t="inlineStr">
+    <row r="43" ht="30" customHeight="1" s="9">
+      <c r="A43" s="12" t="inlineStr">
         <is>
           <t>PB-HM-37</t>
         </is>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B43" s="13" t="inlineStr">
         <is>
           <t>Solicitar descarga de logs crudos (JSONL) — Los usuarios autorizados deben poder seleccionar un rango de fechas y solicitar la extracción de eventos del Wazuh Indexer. El sistema procesa la petición en segundo plano (asincrónico) y notifica al usuario cuando el archivo esté listo.</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C43" s="12" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>Sin empezar</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
+      <c r="D43" s="12" t="inlineStr">
+        <is>
+          <t>Sin empezar</t>
+        </is>
+      </c>
+      <c r="E43" s="12" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="30" customHeight="1">
-      <c r="A44" s="3" t="inlineStr">
+    <row r="44" ht="30" customHeight="1" s="9">
+      <c r="A44" s="12" t="inlineStr">
         <is>
           <t>PB-HM-38</t>
         </is>
       </c>
-      <c r="B44" s="4" t="inlineStr">
+      <c r="B44" s="13" t="inlineStr">
         <is>
           <t>Consultar historial de solicitudes de descarga de logs — Los usuarios deben poder visualizar una tabla con todas sus solicitudes de descarga previas: ID, rango de fechas, cantidad de registros, estado (Pendiente, Procesando, Listo, Rechazada, Fallida) y fecha. La tabla se actualiza automáticamente cada 10 segundos.</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
+      <c r="C44" s="12" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t>Sin empezar</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="inlineStr">
+      <c r="D44" s="12" t="inlineStr">
+        <is>
+          <t>Sin empezar</t>
+        </is>
+      </c>
+      <c r="E44" s="12" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="30" customHeight="1">
-      <c r="A45" s="3" t="inlineStr">
+    <row r="45" ht="30" customHeight="1" s="9">
+      <c r="A45" s="12" t="inlineStr">
         <is>
           <t>PB-HM-39</t>
         </is>
       </c>
-      <c r="B45" s="4" t="inlineStr">
+      <c r="B45" s="13" t="inlineStr">
         <is>
           <t>Descargar archivo JSONL de logs generado — Una vez que el archivo de logs está en estado "Listo", el usuario debe poder descargarlo con un clic. El archivo tiene una vigencia de 7 días y es eliminado automáticamente después de ese período.</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="C45" s="12" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t>Sin empezar</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="inlineStr">
+      <c r="D45" s="12" t="inlineStr">
+        <is>
+          <t>Sin empezar</t>
+        </is>
+      </c>
+      <c r="E45" s="12" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="30" customHeight="1">
-      <c r="A46" s="3" t="inlineStr">
+    <row r="46" ht="30" customHeight="1" s="9">
+      <c r="A46" s="12" t="inlineStr">
         <is>
           <t>PB-HM-40</t>
         </is>
       </c>
-      <c r="B46" s="4" t="inlineStr">
+      <c r="B46" s="13" t="inlineStr">
         <is>
           <t>Solicitar descarga masiva que requiere aprobación del Administrador — Si la solicitud de logs supera el umbral de 50.000 registros, el sistema debe bloquear la descarga directa, crear una solicitud con estado "Pendiente" y notificar al Administrador vía Telegram con botones de Aprobar/Rechazar.</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
+      <c r="C46" s="12" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t>Sin empezar</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="inlineStr">
+      <c r="D46" s="12" t="inlineStr">
+        <is>
+          <t>Sin empezar</t>
+        </is>
+      </c>
+      <c r="E46" s="12" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="30" customHeight="1">
-      <c r="A47" s="3" t="inlineStr">
+    <row r="47" ht="30" customHeight="1" s="9">
+      <c r="A47" s="12" t="inlineStr">
         <is>
           <t>PB-HM-41</t>
         </is>
       </c>
-      <c r="B47" s="4" t="inlineStr">
+      <c r="B47" s="13" t="inlineStr">
         <is>
           <t>Aprobar o rechazar solicitud de descarga masiva (vía Telegram) — El Administrador debe poder aprobar o rechazar solicitudes masivas directamente desde el Bot de Telegram de HoneyMetrics, con el sistema validando su identidad y actuando conforme a la decisión.</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr">
+      <c r="C47" s="12" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>Sin empezar</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="inlineStr">
+      <c r="D47" s="12" t="inlineStr">
+        <is>
+          <t>Sin empezar</t>
+        </is>
+      </c>
+      <c r="E47" s="12" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="30" customHeight="1">
-      <c r="A48" s="3" t="inlineStr">
+    <row r="48" ht="30" customHeight="1" s="9">
+      <c r="A48" s="12" t="inlineStr">
         <is>
           <t>PB-HM-42</t>
         </is>
       </c>
-      <c r="B48" s="4" t="inlineStr">
+      <c r="B48" s="13" t="inlineStr">
         <is>
           <t>Generar y descargar el Diccionario de Datos en PDF — El Analista debe poder generar, desde la vista de Logs, un documento PDF con el esquema técnico completo de los campos del evento Wazuh (atributo, tipo, descripción para ML), con logotipo de HoneyMetrics y marca de tiempo. Generado en el navegador del usuario (client-side).</t>
         </is>
       </c>
-      <c r="C48" s="3" t="inlineStr">
+      <c r="C48" s="12" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="D48" s="3" t="inlineStr">
-        <is>
-          <t>Sin empezar</t>
-        </is>
-      </c>
-      <c r="E48" s="3" t="inlineStr">
+      <c r="D48" s="12" t="inlineStr">
+        <is>
+          <t>Sin empezar</t>
+        </is>
+      </c>
+      <c r="E48" s="12" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="30" customHeight="1">
-      <c r="A49" s="3" t="inlineStr">
+    <row r="49" ht="30" customHeight="1" s="9">
+      <c r="A49" s="12" t="inlineStr">
         <is>
           <t>PB-HM-43</t>
         </is>
       </c>
-      <c r="B49" s="4" t="inlineStr">
+      <c r="B49" s="13" t="inlineStr">
         <is>
           <t>Generar y descargar informes ejecutivos y de rendimiento — Los usuarios autorizados deben poder generar informes en formato CSV o Excel seleccionando un rango de fechas y tipo de informe (Ejecutivo u Operativo). La generación se realiza en segundo plano con barra de progreso. Peso máximo: 50 MB.</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr">
+      <c r="C49" s="12" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t>Sin empezar</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="inlineStr">
+      <c r="D49" s="12" t="inlineStr">
+        <is>
+          <t>Sin empezar</t>
+        </is>
+      </c>
+      <c r="E49" s="12" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="30" customHeight="1">
-      <c r="A50" s="3" t="inlineStr">
+    <row r="50" ht="30" customHeight="1" s="9">
+      <c r="A50" s="12" t="inlineStr">
         <is>
           <t>PB-HM-44</t>
         </is>
       </c>
-      <c r="B50" s="4" t="inlineStr">
+      <c r="B50" s="13" t="inlineStr">
         <is>
           <t>Recibir alertas emergentes ante anomalías críticas en pantalla — El sistema debe detectar automáticamente anomalías críticas (picos de ataque &gt;300%) y mostrar una ventana emergente clasificada por severidad (Roja/Naranja/Amarilla) con el resumen del evento, botón "Ver Detalle" y botón "Descartar". Máximo una alerta cada 30 segundos.</t>
         </is>
       </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="C50" s="12" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="D50" s="3" t="inlineStr">
-        <is>
-          <t>Sin empezar</t>
-        </is>
-      </c>
-      <c r="E50" s="3" t="inlineStr">
+      <c r="D50" s="12" t="inlineStr">
+        <is>
+          <t>Sin empezar</t>
+        </is>
+      </c>
+      <c r="E50" s="12" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="30" customHeight="1">
-      <c r="A51" s="3" t="inlineStr">
+    <row r="51" ht="30" customHeight="1" s="9">
+      <c r="A51" s="12" t="inlineStr">
         <is>
           <t>PB-HM-45</t>
         </is>
       </c>
-      <c r="B51" s="4" t="inlineStr">
+      <c r="B51" s="13" t="inlineStr">
         <is>
           <t>Consultar historial de alertas recibidas — El Consultor debe poder acceder a un panel lateral con todas las alertas generadas en las últimas 24 horas, su estado (Atendida, Descartada, Ignorada) y detalles del evento.</t>
         </is>
       </c>
-      <c r="C51" s="3" t="inlineStr">
+      <c r="C51" s="12" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t>Sin empezar</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="inlineStr">
+      <c r="D51" s="12" t="inlineStr">
+        <is>
+          <t>Sin empezar</t>
+        </is>
+      </c>
+      <c r="E51" s="12" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="30" customHeight="1">
-      <c r="A52" s="3" t="inlineStr">
+    <row r="52" ht="30" customHeight="1" s="9">
+      <c r="A52" s="12" t="inlineStr">
         <is>
           <t>PB-HM-46</t>
         </is>
       </c>
-      <c r="B52" s="4" t="inlineStr">
+      <c r="B52" s="13" t="inlineStr">
         <is>
           <t>Ver detalle completo de una anomalía detectada — Al hacer clic en "Ver Detalle" de una alerta, el sistema debe mostrar: tabla de registros asociados, historial de la IP, gráfico temporal de la anomalía y botones de acción ("Agregar a Lista Negra" y "Marcar como Falso Positivo").</t>
         </is>
       </c>
-      <c r="C52" s="3" t="inlineStr">
+      <c r="C52" s="12" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="D52" s="3" t="inlineStr">
-        <is>
-          <t>Sin empezar</t>
-        </is>
-      </c>
-      <c r="E52" s="3" t="inlineStr">
+      <c r="D52" s="12" t="inlineStr">
+        <is>
+          <t>Sin empezar</t>
+        </is>
+      </c>
+      <c r="E52" s="12" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="30" customHeight="1">
-      <c r="A53" s="3" t="inlineStr">
+    <row r="53" ht="30" customHeight="1" s="9">
+      <c r="A53" s="12" t="inlineStr">
         <is>
           <t>PB-HM-47</t>
         </is>
       </c>
-      <c r="B53" s="4" t="inlineStr">
+      <c r="B53" s="13" t="inlineStr">
         <is>
           <t>Marcar una alerta como Falso Positivo — El Consultor debe poder clasificar un evento detectado como falso positivo con confirmación del sistema, lo que debe actualizar el estado de la alerta y etiquetar el registro para el reentrenamiento futuro de la IA.</t>
         </is>
       </c>
-      <c r="C53" s="3" t="inlineStr">
+      <c r="C53" s="12" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="D53" s="3" t="inlineStr">
-        <is>
-          <t>Sin empezar</t>
-        </is>
-      </c>
-      <c r="E53" s="3" t="inlineStr">
+      <c r="D53" s="12" t="inlineStr">
+        <is>
+          <t>Sin empezar</t>
+        </is>
+      </c>
+      <c r="E53" s="12" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="30" customHeight="1">
-      <c r="A54" s="3" t="inlineStr">
+    <row r="54" ht="30" customHeight="1" s="9">
+      <c r="A54" s="12" t="inlineStr">
         <is>
           <t>PB-HM-48</t>
         </is>
       </c>
-      <c r="B54" s="4" t="inlineStr">
+      <c r="B54" s="13" t="inlineStr">
         <is>
           <t>Visualizar el Resumen de Rendimiento de Algoritmos de ML — El Analista debe poder ver un dashboard técnico con métricas del modelo vigente: KPIs (Accuracy, Precision, Recall, F1, ROC AUC), curva ROC, gráfico comparativo entre versiones y tiempos de ejecución.</t>
         </is>
       </c>
-      <c r="C54" s="3" t="inlineStr">
+      <c r="C54" s="12" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="D54" s="3" t="inlineStr">
-        <is>
-          <t>Sin empezar</t>
-        </is>
-      </c>
-      <c r="E54" s="3" t="inlineStr">
+      <c r="D54" s="12" t="inlineStr">
+        <is>
+          <t>Sin empezar</t>
+        </is>
+      </c>
+      <c r="E54" s="12" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="30" customHeight="1">
-      <c r="A55" s="3" t="inlineStr">
+    <row r="55" ht="30" customHeight="1" s="9">
+      <c r="A55" s="12" t="inlineStr">
         <is>
           <t>PB-HM-49</t>
         </is>
       </c>
-      <c r="B55" s="4" t="inlineStr">
+      <c r="B55" s="13" t="inlineStr">
         <is>
           <t>Comparar el rendimiento entre múltiples versiones del modelo de IA — El Analista debe poder seleccionar dos o más versiones del modelo y ver sus métricas de rendimiento comparadas en un gráfico de barras actualizado.</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr">
+      <c r="C55" s="12" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t>Sin empezar</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="inlineStr">
+      <c r="D55" s="12" t="inlineStr">
+        <is>
+          <t>Sin empezar</t>
+        </is>
+      </c>
+      <c r="E55" s="12" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="30" customHeight="1">
-      <c r="A56" s="3" t="inlineStr">
+    <row r="56" ht="30" customHeight="1" s="9">
+      <c r="A56" s="12" t="inlineStr">
         <is>
           <t>PB-HM-50</t>
         </is>
       </c>
-      <c r="B56" s="4" t="inlineStr">
+      <c r="B56" s="13" t="inlineStr">
         <is>
           <t>Exportar métricas de rendimiento de algoritmos en CSV — El Analista debe poder descargar el historial completo de métricas de rendimiento de los modelos en formato CSV.</t>
         </is>
       </c>
-      <c r="C56" s="3" t="inlineStr">
+      <c r="C56" s="12" t="inlineStr">
         <is>
           <t>Baja</t>
         </is>
       </c>
-      <c r="D56" s="3" t="inlineStr">
-        <is>
-          <t>Sin empezar</t>
-        </is>
-      </c>
-      <c r="E56" s="3" t="inlineStr">
+      <c r="D56" s="12" t="inlineStr">
+        <is>
+          <t>Sin empezar</t>
+        </is>
+      </c>
+      <c r="E56" s="12" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="30" customHeight="1">
-      <c r="A57" s="3" t="inlineStr">
+    <row r="57" ht="30" customHeight="1" s="9">
+      <c r="A57" s="12" t="inlineStr">
         <is>
           <t>PB-HM-51</t>
         </is>
       </c>
-      <c r="B57" s="4" t="inlineStr">
+      <c r="B57" s="13" t="inlineStr">
         <is>
           <t>Guardar filtros predeterminados de Lista Negra (Analista) — El Analista debe poder guardar combinaciones de filtros recurrentes sobre la Lista Negra (hasta 10 por usuario) con nombre único y reutilizarlos rápidamente para preparar datasets de entrenamiento.</t>
         </is>
       </c>
-      <c r="C57" s="3" t="inlineStr">
+      <c r="C57" s="12" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="D57" s="3" t="inlineStr">
-        <is>
-          <t>Sin empezar</t>
-        </is>
-      </c>
-      <c r="E57" s="3" t="inlineStr">
+      <c r="D57" s="12" t="inlineStr">
+        <is>
+          <t>Sin empezar</t>
+        </is>
+      </c>
+      <c r="E57" s="12" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="30" customHeight="1">
-      <c r="A58" s="3" t="inlineStr">
+    <row r="58" ht="30" customHeight="1" s="9">
+      <c r="A58" s="12" t="inlineStr">
         <is>
           <t>PB-HM-52</t>
         </is>
       </c>
-      <c r="B58" s="4" t="inlineStr">
+      <c r="B58" s="13" t="inlineStr">
         <is>
           <t>Consultar filtros guardados de Lista Negra — El Analista debe poder ver su lista de filtros guardados y aplicar cualquiera con un solo clic para cargar automáticamente la configuración en la tabla de Lista Negra.</t>
         </is>
       </c>
-      <c r="C58" s="3" t="inlineStr">
+      <c r="C58" s="12" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="D58" s="3" t="inlineStr">
-        <is>
-          <t>Sin empezar</t>
-        </is>
-      </c>
-      <c r="E58" s="3" t="inlineStr">
+      <c r="D58" s="12" t="inlineStr">
+        <is>
+          <t>Sin empezar</t>
+        </is>
+      </c>
+      <c r="E58" s="12" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="30" customHeight="1">
-      <c r="A59" s="3" t="inlineStr">
+    <row r="59" ht="30" customHeight="1" s="9">
+      <c r="A59" s="12" t="inlineStr">
         <is>
           <t>PB-HM-53</t>
         </is>
       </c>
-      <c r="B59" s="4" t="inlineStr">
+      <c r="B59" s="13" t="inlineStr">
         <is>
           <t>Eliminar un filtro predeterminado guardado — El Analista debe poder borrar un filtro guardado que ya no necesite, con confirmación previa del sistema.</t>
         </is>
       </c>
-      <c r="C59" s="3" t="inlineStr">
+      <c r="C59" s="12" t="inlineStr">
         <is>
           <t>Baja</t>
         </is>
       </c>
-      <c r="D59" s="3" t="inlineStr">
-        <is>
-          <t>Sin empezar</t>
-        </is>
-      </c>
-      <c r="E59" s="3" t="inlineStr">
+      <c r="D59" s="12" t="inlineStr">
+        <is>
+          <t>Sin empezar</t>
+        </is>
+      </c>
+      <c r="E59" s="12" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="30" customHeight="1">
-      <c r="A60" s="3" t="inlineStr">
+    <row r="60" ht="30" customHeight="1" s="9">
+      <c r="A60" s="12" t="inlineStr">
         <is>
           <t>PB-HM-54</t>
         </is>
       </c>
-      <c r="B60" s="4" t="inlineStr">
+      <c r="B60" s="13" t="inlineStr">
         <is>
           <t>Monitorear el estado de recursos del Honeypot en tiempo real — El Administrador y el Consultor deben poder visualizar el rendimiento actual del hardware de la Orange Pi 5: CPU (gráfico de anillo), RAM (barras) y almacenamiento (gauge). Los gráficos se actualizan automáticamente cada 60 segundos.</t>
         </is>
       </c>
-      <c r="C60" s="3" t="inlineStr">
+      <c r="C60" s="12" t="inlineStr">
         <is>
           <t>Baja</t>
         </is>
       </c>
-      <c r="D60" s="3" t="inlineStr">
-        <is>
-          <t>Sin empezar</t>
-        </is>
-      </c>
-      <c r="E60" s="3" t="inlineStr">
+      <c r="D60" s="12" t="inlineStr">
+        <is>
+          <t>Sin empezar</t>
+        </is>
+      </c>
+      <c r="E60" s="12" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="30" customHeight="1">
-      <c r="A61" s="3" t="inlineStr">
+    <row r="61" ht="30" customHeight="1" s="9">
+      <c r="A61" s="12" t="inlineStr">
         <is>
           <t>PB-HM-55</t>
         </is>
       </c>
-      <c r="B61" s="4" t="inlineStr">
+      <c r="B61" s="13" t="inlineStr">
         <is>
           <t>Alertar cuando el Honeypot pierde conectividad — Si el sistema no recibe telemetría nueva del Honeypot en 5 minutos, debe mostrar una alerta roja persistente indicando la pérdida de comunicación con la Orange Pi 5.</t>
         </is>
       </c>
-      <c r="C61" s="3" t="inlineStr">
+      <c r="C61" s="12" t="inlineStr">
         <is>
           <t>Baja</t>
         </is>
       </c>
-      <c r="D61" s="3" t="inlineStr">
-        <is>
-          <t>Sin empezar</t>
-        </is>
-      </c>
-      <c r="E61" s="3" t="inlineStr">
+      <c r="D61" s="12" t="inlineStr">
+        <is>
+          <t>Sin empezar</t>
+        </is>
+      </c>
+      <c r="E61" s="12" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="30" customHeight="1">
-      <c r="A62" s="3" t="inlineStr">
+    <row r="62" ht="30" customHeight="1" s="9">
+      <c r="A62" s="12" t="inlineStr">
         <is>
           <t>PB-HM-56</t>
         </is>
       </c>
-      <c r="B62" s="4" t="inlineStr">
+      <c r="B62" s="13" t="inlineStr">
         <is>
           <t>Aplicar cierre automático de sesión por inactividad (30 min) — Si un usuario deja la plataforma abierta sin interacción (mouse/teclado) durante 30 minutos, el sistema debe cerrar la sesión automáticamente y redirigir al Login.</t>
         </is>
       </c>
-      <c r="C62" s="3" t="inlineStr">
+      <c r="C62" s="12" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="D62" s="3" t="inlineStr">
-        <is>
-          <t>Sin empezar</t>
-        </is>
-      </c>
-      <c r="E62" s="3" t="inlineStr">
+      <c r="D62" s="12" t="inlineStr">
+        <is>
+          <t>Sin empezar</t>
+        </is>
+      </c>
+      <c r="E62" s="12" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="30" customHeight="1">
-      <c r="A63" s="3" t="inlineStr">
+    <row r="63" ht="30" customHeight="1" s="9">
+      <c r="A63" s="12" t="inlineStr">
         <is>
           <t>PB-HM-57</t>
         </is>
       </c>
-      <c r="B63" s="4" t="inlineStr">
+      <c r="B63" s="13" t="inlineStr">
         <is>
           <t>Mostrar mensajes de error del sistema en lenguaje natural — Todos los errores de sistema, datos inválidos o fallos de conexión deben mostrarse con alertas de colores (rojo error, amarillo precaución) en español, sin revelar trazas de código al usuario.</t>
         </is>
       </c>
-      <c r="C63" s="3" t="inlineStr">
+      <c r="C63" s="12" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="D63" s="3" t="inlineStr">
-        <is>
-          <t>Sin empezar</t>
-        </is>
-      </c>
-      <c r="E63" s="3" t="inlineStr">
+      <c r="D63" s="12" t="inlineStr">
+        <is>
+          <t>Sin empezar</t>
+        </is>
+      </c>
+      <c r="E63" s="12" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="30" customHeight="1">
-      <c r="A64" s="3" t="inlineStr">
+    <row r="64" ht="30" customHeight="1" s="9">
+      <c r="A64" s="12" t="inlineStr">
         <is>
           <t>PB-HM-58</t>
         </is>
       </c>
-      <c r="B64" s="4" t="inlineStr">
+      <c r="B64" s="13" t="inlineStr">
         <is>
           <t>Soportar modo oscuro y modo claro en toda la interfaz — La plataforma debe ofrecer al usuario la opción de alternar entre tema claro y oscuro desde su perfil. La preferencia debe persistir entre sesiones. Los gráficos deben adaptarse automáticamente al tema activo.</t>
         </is>
       </c>
-      <c r="C64" s="3" t="inlineStr">
+      <c r="C64" s="12" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="D64" s="3" t="inlineStr">
-        <is>
-          <t>Sin empezar</t>
-        </is>
-      </c>
-      <c r="E64" s="3" t="inlineStr">
+      <c r="D64" s="12" t="inlineStr">
+        <is>
+          <t>Sin empezar</t>
+        </is>
+      </c>
+      <c r="E64" s="12" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="30" customHeight="1">
-      <c r="A65" s="3" t="inlineStr">
+    <row r="65" ht="30" customHeight="1" s="9">
+      <c r="A65" s="12" t="inlineStr">
         <is>
           <t>PB-HM-59</t>
         </is>
       </c>
-      <c r="B65" s="4" t="inlineStr">
+      <c r="B65" s="13" t="inlineStr">
         <is>
           <t>Notificar al usuario vía Telegram cuando su descarga está lista — Al finalizar el procesamiento de logs en segundo plano, el sistema debe enviar un mensaje de notificación al identificador de Telegram registrado en el perfil del usuario.</t>
         </is>
       </c>
-      <c r="C65" s="3" t="inlineStr">
+      <c r="C65" s="12" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="D65" s="3" t="inlineStr">
-        <is>
-          <t>Sin empezar</t>
-        </is>
-      </c>
-      <c r="E65" s="3" t="inlineStr">
+      <c r="D65" s="12" t="inlineStr">
+        <is>
+          <t>Sin empezar</t>
+        </is>
+      </c>
+      <c r="E65" s="12" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="30" customHeight="1">
-      <c r="A66" s="3" t="inlineStr">
+    <row r="66" ht="30" customHeight="1" s="9">
+      <c r="A66" s="12" t="inlineStr">
         <is>
           <t>PB-HM-60</t>
         </is>
       </c>
-      <c r="B66" s="4" t="inlineStr">
+      <c r="B66" s="13" t="inlineStr">
         <is>
           <t>Eliminar automáticamente archivos de logs expirados (7 días) — El sistema debe ejecutar una tarea programada periódica que elimine del servidor todos los archivos JSONL que superen los 7 días de vigencia, liberando espacio en disco de forma autónoma.</t>
         </is>
       </c>
-      <c r="C66" s="3" t="inlineStr">
+      <c r="C66" s="12" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="D66" s="3" t="inlineStr">
-        <is>
-          <t>Sin empezar</t>
-        </is>
-      </c>
-      <c r="E66" s="3" t="inlineStr">
+      <c r="D66" s="12" t="inlineStr">
+        <is>
+          <t>Sin empezar</t>
+        </is>
+      </c>
+      <c r="E66" s="12" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="30" customHeight="1">
-      <c r="A67" s="3" t="inlineStr">
+    <row r="67" ht="30" customHeight="1" s="9">
+      <c r="A67" s="12" t="inlineStr">
         <is>
           <t>PB-HM-61</t>
         </is>
       </c>
-      <c r="B67" s="4" t="inlineStr">
+      <c r="B67" s="13" t="inlineStr">
         <is>
           <t>Listar IPs registradas en el Intelligence Center con su Threat Score dinámico (0-100).</t>
         </is>
       </c>
-      <c r="C67" s="3" t="inlineStr">
+      <c r="C67" s="12" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="D67" s="3" t="inlineStr">
-        <is>
-          <t>Sin empezar</t>
-        </is>
-      </c>
-      <c r="E67" s="3" t="inlineStr">
+      <c r="D67" s="12" t="inlineStr">
+        <is>
+          <t>Sin empezar</t>
+        </is>
+      </c>
+      <c r="E67" s="12" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="30" customHeight="1">
-      <c r="A68" s="3" t="inlineStr">
+    <row r="68" ht="30" customHeight="1" s="9">
+      <c r="A68" s="12" t="inlineStr">
         <is>
           <t>PB-HM-62</t>
         </is>
       </c>
-      <c r="B68" s="4" t="inlineStr">
+      <c r="B68" s="13" t="inlineStr">
         <is>
           <t>Identificar y alertar sobre ataques coordinados (Botnets) agrupando IPs por subred CIDR /24.</t>
         </is>
       </c>
-      <c r="C68" s="3" t="inlineStr">
+      <c r="C68" s="12" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="D68" s="3" t="inlineStr">
-        <is>
-          <t>Sin empezar</t>
-        </is>
-      </c>
-      <c r="E68" s="3" t="inlineStr">
+      <c r="D68" s="12" t="inlineStr">
+        <is>
+          <t>Sin empezar</t>
+        </is>
+      </c>
+      <c r="E68" s="12" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="30" customHeight="1">
-      <c r="A69" s="3" t="inlineStr">
+    <row r="69" ht="30" customHeight="1" s="9">
+      <c r="A69" s="12" t="inlineStr">
         <is>
           <t>PB-HM-63</t>
         </is>
       </c>
-      <c r="B69" s="4" t="inlineStr">
+      <c r="B69" s="13" t="inlineStr">
         <is>
           <t>Clasificar a los atacantes como Bot (automatizado rápido) o Humano (dirigido lento) según su velocidad de ataque.</t>
         </is>
       </c>
-      <c r="C69" s="3" t="inlineStr">
+      <c r="C69" s="12" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="D69" s="3" t="inlineStr">
-        <is>
-          <t>Sin empezar</t>
-        </is>
-      </c>
-      <c r="E69" s="3" t="inlineStr">
+      <c r="D69" s="12" t="inlineStr">
+        <is>
+          <t>Sin empezar</t>
+        </is>
+      </c>
+      <c r="E69" s="12" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="30" customHeight="1">
-      <c r="A70" s="3" t="inlineStr">
+    <row r="70" ht="30" customHeight="1" s="9">
+      <c r="A70" s="12" t="inlineStr">
         <is>
           <t>PB-HM-64</t>
         </is>
       </c>
-      <c r="B70" s="4" t="inlineStr">
+      <c r="B70" s="13" t="inlineStr">
         <is>
           <t>Visualizar panel de priorización de vulnerabilidades (Patch Intelligence) que cruza CVEs críticos sin parche con ataques reales.</t>
         </is>
       </c>
-      <c r="C70" s="3" t="inlineStr">
+      <c r="C70" s="12" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="D70" s="3" t="inlineStr">
-        <is>
-          <t>Sin empezar</t>
-        </is>
-      </c>
-      <c r="E70" s="3" t="inlineStr">
+      <c r="D70" s="12" t="inlineStr">
+        <is>
+          <t>Sin empezar</t>
+        </is>
+      </c>
+      <c r="E70" s="12" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="30" customHeight="1">
-      <c r="A71" s="3" t="inlineStr">
+    <row r="71" ht="30" customHeight="1" s="9">
+      <c r="A71" s="12" t="inlineStr">
         <is>
           <t>PB-HM-65</t>
         </is>
       </c>
-      <c r="B71" s="4" t="inlineStr">
+      <c r="B71" s="13" t="inlineStr">
         <is>
           <t>Consultar diccionario de usuarios más probados por atacantes (Honeypot Advisor) para predecir vectores de fuerza bruta.</t>
         </is>
       </c>
-      <c r="C71" s="3" t="inlineStr">
+      <c r="C71" s="12" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="D71" s="3" t="inlineStr">
-        <is>
-          <t>Sin empezar</t>
-        </is>
-      </c>
-      <c r="E71" s="3" t="inlineStr">
+      <c r="D71" s="12" t="inlineStr">
+        <is>
+          <t>Sin empezar</t>
+        </is>
+      </c>
+      <c r="E71" s="12" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="30" customHeight="1">
-      <c r="A72" s="3" t="inlineStr">
+    <row r="72" ht="30" customHeight="1" s="9">
+      <c r="A72" s="12" t="inlineStr">
         <is>
           <t>PB-HM-66</t>
         </is>
       </c>
-      <c r="B72" s="4" t="inlineStr">
+      <c r="B72" s="13" t="inlineStr">
         <is>
           <t>Visualizar línea de tiempo de integridad (FIM) para cruzar temporalmente accesos de atacantes con alteraciones de archivos.</t>
         </is>
       </c>
-      <c r="C72" s="3" t="inlineStr">
+      <c r="C72" s="12" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="D72" s="3" t="inlineStr">
-        <is>
-          <t>Sin empezar</t>
-        </is>
-      </c>
-      <c r="E72" s="3" t="inlineStr">
+      <c r="D72" s="12" t="inlineStr">
+        <is>
+          <t>Sin empezar</t>
+        </is>
+      </c>
+      <c r="E72" s="12" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="30" customHeight="1">
-      <c r="A73" s="3" t="inlineStr">
+    <row r="73" ht="30" customHeight="1" s="9">
+      <c r="A73" s="12" t="inlineStr">
         <is>
           <t>PB-HM-67</t>
         </is>
       </c>
-      <c r="B73" s="4" t="inlineStr">
+      <c r="B73" s="13" t="inlineStr">
         <is>
           <t>Visualizar diagrama del ciclo de ataque completo de una amenaza mapeando sus acciones a las tácticas de MITRE ATT&amp;CK.</t>
         </is>
       </c>
-      <c r="C73" s="3" t="inlineStr">
+      <c r="C73" s="12" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="D73" s="3" t="inlineStr">
-        <is>
-          <t>Sin empezar</t>
-        </is>
-      </c>
-      <c r="E73" s="3" t="inlineStr">
+      <c r="D73" s="12" t="inlineStr">
+        <is>
+          <t>Sin empezar</t>
+        </is>
+      </c>
+      <c r="E73" s="12" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="30" customHeight="1">
-      <c r="A74" s="3" t="inlineStr">
+    <row r="74" ht="30" customHeight="1" s="9">
+      <c r="A74" s="12" t="inlineStr">
         <is>
           <t>PB-HM-68</t>
         </is>
       </c>
-      <c r="B74" s="4" t="inlineStr">
+      <c r="B74" s="13" t="inlineStr">
         <is>
           <t>Validar manualmente (HITL) las alertas de archivos comprometidos para re-entrenar el modelo de detección.</t>
         </is>
       </c>
-      <c r="C74" s="3" t="inlineStr">
+      <c r="C74" s="12" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="D74" s="3" t="inlineStr">
-        <is>
-          <t>Sin empezar</t>
-        </is>
-      </c>
-      <c r="E74" s="3" t="inlineStr">
+      <c r="D74" s="12" t="inlineStr">
+        <is>
+          <t>Sin empezar</t>
+        </is>
+      </c>
+      <c r="E74" s="12" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="30" customHeight="1">
-      <c r="A75" s="3" t="inlineStr">
+    <row r="75" ht="30" customHeight="1" s="9">
+      <c r="A75" s="12" t="inlineStr">
         <is>
           <t>PB-HM-69</t>
         </is>
       </c>
-      <c r="B75" s="4" t="inlineStr">
+      <c r="B75" s="13" t="inlineStr">
         <is>
           <t>Consultar panel de cumplimiento de seguridad (CIS Benchmark) para obtener recomendaciones exactas de remediación de hardening.</t>
         </is>
       </c>
-      <c r="C75" s="3" t="inlineStr">
+      <c r="C75" s="12" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="D75" s="3" t="inlineStr">
-        <is>
-          <t>Sin empezar</t>
-        </is>
-      </c>
-      <c r="E75" s="3" t="inlineStr">
+      <c r="D75" s="12" t="inlineStr">
+        <is>
+          <t>Sin empezar</t>
+        </is>
+      </c>
+      <c r="E75" s="12" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="30" customHeight="1">
-      <c r="A76" s="3" t="inlineStr">
+    <row r="76" ht="30" customHeight="1" s="9">
+      <c r="A76" s="12" t="inlineStr">
         <is>
           <t>PB-HM-70</t>
         </is>
       </c>
-      <c r="B76" s="4" t="inlineStr">
+      <c r="B76" s="13" t="inlineStr">
         <is>
           <t>Visualizar mapa de calor predictivo de horarios de ataque (días vs horas) para anticipar picos de carga.</t>
         </is>
       </c>
-      <c r="C76" s="3" t="inlineStr">
+      <c r="C76" s="12" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="D76" s="3" t="inlineStr">
-        <is>
-          <t>Sin empezar</t>
-        </is>
-      </c>
-      <c r="E76" s="3" t="inlineStr">
+      <c r="D76" s="12" t="inlineStr">
+        <is>
+          <t>Sin empezar</t>
+        </is>
+      </c>
+      <c r="E76" s="12" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
+  <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="A2:G75"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="45" customWidth="1" min="4" max="4"/>
-    <col width="55" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" style="8" min="1" max="2"/>
+    <col width="40" customWidth="1" style="8" min="3" max="3"/>
+    <col width="45" customWidth="1" style="8" min="4" max="4"/>
+    <col width="55" customWidth="1" style="8" min="5" max="5"/>
+    <col width="15" customWidth="1" style="8" min="6" max="7"/>
   </cols>
   <sheetData>
-    <row r="2">
-      <c r="C2" s="1" t="inlineStr">
+    <row r="2" ht="19.7" customHeight="1" s="9">
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>HISTORIAS DE USUARIO</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>NOMBRE EQUIPO ---</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="8" t="inlineStr">
         <is>
           <t>Johan Posada y Juan Pablo Fonseca</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="D3" t="inlineStr">
+    <row r="3" ht="15" customHeight="1" s="9">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>PROYECTO ---</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>HoneyMetrics 2.0</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+    <row r="5" ht="24.75" customHeight="1" s="9">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>CODIGO PB</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>CODIGO HU</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>DESCRIPCIÓN DETALLADA HU</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="14" t="inlineStr">
         <is>
           <t>TAREAS</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="14" t="inlineStr">
         <is>
           <t>CRITERIOS DE ACEPTACIÓN</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="14" t="inlineStr">
         <is>
           <t>PUNTOS DE HISTORIA DE USUARIO</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="14" t="inlineStr">
         <is>
           <t>MOCKUP</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="120" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
+    <row r="6" ht="120" customHeight="1" s="9">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>PB-HM-01</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>PB-HM-01.1</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>Como Visitante quiero visualizar la página de inicio pública para conocer el propósito de HoneyMetrics y acceder al sistema.</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>- [ ] Diseñar e implementar el componente UI necesario
 - [ ] Establecer lógica de estado (React hooks) y validaciones
 - [ ] Conectar la interfaz con la API Backend correspondiente</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>[Escenario 1:]
-- **Escenario 1:** Dado que ingreso a la raíz del sitio, Cuando carga la página, Entonces veo un navbar, sección hero, muestra de código y el mapa de calor ilustrativo.
-[Escenario 2:]
-- **Escenario 2:** Dado que estoy en la Landing Page, Cuando hago clic en el punto de acceso, Entonces soy redirigido al formulario de Login.</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 1:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que ingreso a la raíz del sitio, Cuando carga la página, Entonces veo un navbar, sección hero, muestra de código y el mapa de calor ilustrativo.
+- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 2:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que estoy en la Landing Page, Cuando hago clic en el punto de acceso, Entonces soy redirigido al formulario de Login.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>[Pendiente screenshot]</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="120" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>[Pendiente screenshot]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="120" customHeight="1" s="9">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>PB-HM-02</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>PB-HM-02.1</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="13" t="inlineStr">
         <is>
           <t>Como Usuario quiero iniciar sesión con credenciales institucionales para acceder al dashboard que me corresponde.</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t>- [ ] Diseñar y maquetar formulario de interfaz en React con validación de entradas (Email/Password).
 - [ ] Integrar consumo del endpoint de autenticación (`POST /api/v1/auth/login`) y almacenar JWT en `httpOnly cookie` o `localStorage` con manejo de error 401.
 - [ ] [Fix ZTNA - Punto Ciego 1] Configurar Cloudflare Zero Trust Access para el dominio `api.johan-d3v.site`: crear una Application de tipo "Self-hosted", definir una Policy de acceso restringiendo a correos del equipo. Esto actúa como un firewall de identidad antes de FastAPI.</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>[Escenario 1:]
-- **Escenario 1:** Dado que tengo credenciales válidas, Cuando ingreso mi correo @ucundinamarca.edu.co y contraseña, Entonces el sistema identifica mi rol y me redirige al dashboard.
-[Escenario 2:]
-- **Escenario 2:** Dado que inicio sesión exitosamente, Cuando el sistema procesa mi petición, Entonces se me asigna un token JWT de sesión válido.</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 1:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que tengo credenciales válidas, Cuando ingreso mi correo @ucundinamarca.edu.co y contraseña, Entonces el sistema identifica mi rol y me redirige al dashboard.
+- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 2:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que inicio sesión exitosamente, Cuando el sistema procesa mi petición, Entonces se me asigna un token JWT de sesión válido.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F7" s="12" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>[Pendiente screenshot]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="120" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="G7" s="12" t="inlineStr">
+        <is>
+          <t>[Pendiente screenshot]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="120" customHeight="1" s="9">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>PB-HM-03</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>PB-HM-03.1</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="13" t="inlineStr">
         <is>
           <t>Como Usuario quiero que se bloquee el acceso por credenciales inválidas para mantener la seguridad de mi cuenta.</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="13" t="inlineStr">
         <is>
           <t>- [ ] Diseñar e implementar el componente UI de error de login (mensaje genérico anti-enumeración, sin revelar si falló email o password).
 - [ ] Establecer lógica de estado (React hooks): contador de intentos fallidos en frontend, deshabilitar botón "Ingresar" por 30 segundos tras 5 fallos consecutivos.
 - [ ] [Fix ZTNA - Punto Ciego 2] Implementar Rate Limiting en FastAPI con la librería `slowapi`: decorar el endpoint `POST /api/v1/auth/login` con `@limiter.limit("5/minute")` por IP. Configurar respuesta HTTP 429 con header `Retry-After`. Documentar la dependencia en `requirements.txt`.</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>[Escenario 1:]
-- **Escenario 1:** Dado que estoy en el formulario de Login, Cuando ingreso una contraseña incorrecta, Entonces el sistema rechaza el ingreso mostrando un mensaje genérico.
-[Escenario 2:]
-- **Escenario 2:** Dado que el sistema rechaza el acceso, Cuando muestra el mensaje de error, Entonces no revela si el fallo fue en el correo o en la contraseña (anti-enumeración).</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 1:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que estoy en el formulario de Login, Cuando ingreso una contraseña incorrecta, Entonces el sistema rechaza el ingreso mostrando un mensaje genérico.
+- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 2:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que el sistema rechaza el acceso, Cuando muestra el mensaje de error, Entonces no revela si el fallo fue en el correo o en la contraseña (anti-enumeración).</t>
+          </r>
+        </is>
+      </c>
+      <c r="F8" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>[Pendiente screenshot]</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="120" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="G8" s="12" t="inlineStr">
+        <is>
+          <t>[Pendiente screenshot]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="120" customHeight="1" s="9">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>PB-HM-04</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>PB-HM-04.1</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
         <is>
           <t>Como Usuario quiero forzar el cambio de contraseña en mi primer inicio de sesión para asegurar que no quede con la clave temporal.</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>- [ ] Diseñar y maquetar formulario de interfaz en React
 - [ ] Configurar validación de entradas (Email/Password)
 - [ ] Integrar consumo del endpoint de autenticación</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>[Escenario 1:]
-- **Escenario 1:** Dado que es mi primer inicio de sesión, Cuando ingreso con mi contraseña temporal, Entonces soy redirigido obligatoriamente a la vista de cambio de clave antes del dashboard.
-[Escenario 2:]
-- **Escenario 2:** Dado que estoy en la vista forzada de cambio de clave, Cuando intento navegar a otra ruta, Entonces el sistema me bloquea hasta actualizar la contraseña.</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 1:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que es mi primer inicio de sesión, Cuando ingreso con mi contraseña temporal, Entonces soy redirigido obligatoriamente a la vista de cambio de clave antes del dashboard.
+- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 2:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que estoy en la vista forzada de cambio de clave, Cuando intento navegar a otra ruta, Entonces el sistema me bloquea hasta actualizar la contraseña.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>[Pendiente screenshot]</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="120" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="G9" s="12" t="inlineStr">
+        <is>
+          <t>[Pendiente screenshot]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="120" customHeight="1" s="9">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>PB-HM-05</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>PB-HM-05.1</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="13" t="inlineStr">
         <is>
           <t>Como Usuario autenticado quiero cambiar mi contraseña voluntariamente para mantener la seguridad de mi cuenta actualizada.</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="13" t="inlineStr">
         <is>
           <t>- [ ] Diseñar e implementar el componente UI necesario
 - [ ] Establecer lógica de estado (React hooks) y validaciones
 - [ ] Conectar la interfaz con la API Backend correspondiente</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>[Escenario 1:]
-- **Escenario 1:** Dado que estoy en mi perfil, Cuando solicito cambiar mi contraseña ingresando una que cumple los criterios de seguridad (min. 8, no común, alfanumérica), Entonces la contraseña se actualiza exitosamente verificando la clave actual.
-[Escenario 2:]
-- **Escenario 2:** Dado que ingreso una nueva contraseña, Cuando esta no cumple la longitud de 8 caracteres o no es alfanumérica, Entonces el sistema rechaza el cambio y me muestra un error.</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 1:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que estoy en mi perfil, Cuando solicito cambiar mi contraseña ingresando una que cumple los criterios de seguridad (min. 8, no común, alfanumérica), Entonces la contraseña se actualiza exitosamente verificando la clave actual.
+- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 2:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que ingreso una nueva contraseña, Cuando esta no cumple la longitud de 8 caracteres o no es alfanumérica, Entonces el sistema rechaza el cambio y me muestra un error.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>[Pendiente screenshot]</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="120" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="G10" s="12" t="inlineStr">
+        <is>
+          <t>[Pendiente screenshot]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="120" customHeight="1" s="9">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>PB-HM-06</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <t>PB-HM-06.1</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>Como Usuario quiero restablecer mi contraseña olvidada vía correo electrónico para recuperar el acceso a mi cuenta.</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="13" t="inlineStr">
         <is>
           <t>- [ ] Configurar proveedor de correos transaccionales (Resend) y verificar dominio `johan-d3v.site` en Cloudflare (registros SPF, DKIM, DMARC).
 - [ ] Plan de Contingencia (Opción B): Si fallan los filtros universitarios, documentar e implementar envío de correos vía Microsoft Graph API usando un entorno M365 Developer.
@@ -2764,2708 +2794,3878 @@
 - [ ] [Fix ZTNA - Punto Ciego 3] Documentar en el `README.md` del repositorio frontend que la variable `VITE_API_URL` queda expuesta en el bundle de producción (característica de Vite). Confirmar que las capas de Cloudflare Access (Fix 1) y Rate Limiting (Fix 2) son la defensa en profundidad para mitigar abuso.</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>[Escenario 1:]
-- **Escenario 1:** Dado que olvidé mi contraseña, Cuando solicito restablecerla, Entonces recibo un enlace de uso único en mi correo institucional.
-[Escenario 2:]
-- **Escenario 2:** Dado que recibí el enlace, Cuando intento usarlo después de 1 hora, Entonces el sistema me indica que el token expiró y debo solicitar otro.</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 1:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que olvidé mi contraseña, Cuando solicito restablecerla, Entonces recibo un enlace de uso único en mi correo institucional.
+- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 2:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que recibí el enlace, Cuando intento usarlo después de 1 hora, Entonces el sistema me indica que el token expiró y debo solicitar otro.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F11" s="12" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>[Pendiente screenshot]</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="120" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="G11" s="12" t="inlineStr">
+        <is>
+          <t>[Pendiente screenshot]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="120" customHeight="1" s="9">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>PB-HM-07</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t>PB-HM-07.1</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
         <is>
           <t>Como Usuario quiero autenticar con un segundo factor (2FA-OTP) condicional para agregar una capa extra de seguridad.</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="13" t="inlineStr">
         <is>
           <t>- [ ] Diseñar e implementar el componente UI necesario
 - [ ] Establecer lógica de estado (React hooks) y validaciones
 - [ ] Conectar la interfaz con la API Backend correspondiente</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>[Escenario 1:]
-- **Escenario 1:** Dado que ya configuré el 2FA en el pasado, Cuando ingreso usuario y contraseña correctamente, Entonces el sistema solo me pide el input de 6 dígitos OTP de forma condicional.
-[Escenario 2:]
-- **Escenario 2:** Dado que ingreso el código OTP correcto, Cuando el sistema lo valida con Google Authenticator, Entonces se completa el acceso al dashboard.</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 1:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que ya configuré el 2FA en el pasado, Cuando ingreso usuario y contraseña correctamente, Entonces el sistema solo me pide el input de 6 dígitos OTP de forma condicional.
+- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 2:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que ingreso el código OTP correcto, Cuando el sistema lo valida con Google Authenticator, Entonces se completa el acceso al dashboard.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>[Pendiente screenshot]</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="120" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="G12" s="12" t="inlineStr">
+        <is>
+          <t>[Pendiente screenshot]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="120" customHeight="1" s="9">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>PB-HM-08</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="15" t="inlineStr">
         <is>
           <t>PB-HM-08.1</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="13" t="inlineStr">
         <is>
           <t>Como Usuario quiero vincular Google Authenticator en mi primer inicio para habilitar el 2FA.</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="13" t="inlineStr">
         <is>
           <t>- [ ] Diseñar e implementar el componente UI necesario
 - [ ] Establecer lógica de estado (React hooks) y validaciones
 - [ ] Conectar la interfaz con la API Backend correspondiente</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>[Escenario 1:]
-- **Escenario 1:** Dado que no he configurado 2FA previamente (OTP condicional), Cuando ingreso mis credenciales válidas, Entonces el sistema muestra un código QR para que configure el autenticador.
-[Escenario 2:]
-- **Escenario 2:** Dado que escaneo el código QR, Cuando ingreso el primer token OTP generado, Entonces el sistema verifica la sincronización y me concede el acceso.</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 1:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que no he configurado 2FA previamente (OTP condicional), Cuando ingreso mis credenciales válidas, Entonces el sistema muestra un código QR para que configure el autenticador.
+- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 2:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que escaneo el código QR, Cuando ingreso el primer token OTP generado, Entonces el sistema verifica la sincronización y me concede el acceso.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F13" s="12" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>[Pendiente screenshot]</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="120" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="G13" s="12" t="inlineStr">
+        <is>
+          <t>[Pendiente screenshot]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="120" customHeight="1" s="9">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>PB-HM-09</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="15" t="inlineStr">
         <is>
           <t>PB-HM-09.1</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="13" t="inlineStr">
         <is>
           <t>Como Usuario quiero cerrar sesión de forma segura para evitar accesos no autorizados a mi cuenta.</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="13" t="inlineStr">
         <is>
           <t>- [ ] Diseñar y maquetar formulario de interfaz en React
 - [ ] Configurar validación de entradas (Email/Password)
 - [ ] Integrar consumo del endpoint de autenticación</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>[Escenario 1:]
-- **Escenario 1:** Dado que estoy en el dashboard, Cuando hago clic en cerrar sesión, Entonces el sistema invalida el token JWT en el servidor y limpia el almacenamiento local.
-[Escenario 2:]
-- **Escenario 2:** Dado que cerré mi sesión, Cuando intento usar el botón "Atrás" del navegador, Entonces el sistema me bloquea y me exige iniciar sesión nuevamente.</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="E14" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 1:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que estoy en el dashboard, Cuando hago clic en cerrar sesión, Entonces el sistema invalida el token JWT en el servidor y limpia el almacenamiento local.
+- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 2:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que cerré mi sesión, Cuando intento usar el botón "Atrás" del navegador, Entonces el sistema me bloquea y me exige iniciar sesión nuevamente.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F14" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>[Pendiente screenshot]</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="120" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="G14" s="12" t="inlineStr">
+        <is>
+          <t>[Pendiente screenshot]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="120" customHeight="1" s="9">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>PB-HM-10</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="15" t="inlineStr">
         <is>
           <t>PB-HM-10.1</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="13" t="inlineStr">
         <is>
           <t>Como Usuario quiero que el sistema me redireccione al login al acceder a rutas protegidas sin sesión para mantener el control de acceso.</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t>- [ ] Diseñar y maquetar formulario de interfaz en React
 - [ ] Configurar validación de entradas (Email/Password)
 - [ ] Integrar consumo del endpoint de autenticación</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>[Escenario 1:]
-- **Escenario 1:** Dado que no tengo un token de sesión válido, Cuando intento acceder a una ruta protegida del dashboard, Entonces soy redirigido automáticamente al Login.
-[Escenario 2:]
-- **Escenario 2:** Dado que mi sesión expiró, Cuando intento recargar una vista del dashboard, Entonces el sistema detecta la falta de sesión y me envía al Login.</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 1:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que no tengo un token de sesión válido, Cuando intento acceder a una ruta protegida del dashboard, Entonces soy redirigido automáticamente al Login.
+- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 2:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que mi sesión expiró, Cuando intento recargar una vista del dashboard, Entonces el sistema detecta la falta de sesión y me envía al Login.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F15" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>[Pendiente screenshot]</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="120" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="G15" s="12" t="inlineStr">
+        <is>
+          <t>[Pendiente screenshot]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="120" customHeight="1" s="9">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>PB-HM-11</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B16" s="15" t="inlineStr">
         <is>
           <t>PB-HM-11.1</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="13" t="inlineStr">
         <is>
           <t>Como Usuario sin rol asignado quiero ver un banner informativo para saber que debo solicitar permisos al Administrador.</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="13" t="inlineStr">
         <is>
           <t>- [ ] Diseñar e implementar el componente UI necesario
 - [ ] Establecer lógica de estado (React hooks) y validaciones
 - [ ] Conectar la interfaz con la API Backend correspondiente</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>[Escenario 1:]
-- **Escenario 1:** Dado que me autentico correctamente pero no tengo rol asignado, Cuando ingreso al sistema, Entonces veo una interfaz con acceso mínimo.
-[Escenario 2:]
-- **Escenario 2:** Dado que tengo acceso mínimo, Cuando reviso la pantalla, Entonces veo un banner informativo indicando que debo solicitar permisos al Administrador.</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 1:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que me autentico correctamente pero no tengo rol asignado, Cuando ingreso al sistema, Entonces veo una interfaz con acceso mínimo.
+- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 2:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que tengo acceso mínimo, Cuando reviso la pantalla, Entonces veo un banner informativo indicando que debo solicitar permisos al Administrador.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F16" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>[Pendiente screenshot]</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="120" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>[Pendiente screenshot]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="120" customHeight="1" s="9">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t>PB-HM-12</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="15" t="inlineStr">
         <is>
           <t>PB-HM-12.1</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="13" t="inlineStr">
         <is>
           <t>Como Administrador quiero acceder al panel de administración profunda desde el frontend para gestionar el sistema sin escribir URLs manualmente.</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="13" t="inlineStr">
         <is>
           <t>- [ ] Diseñar e implementar el componente UI necesario
 - [ ] Establecer lógica de estado (React hooks) y validaciones
 - [ ] Conectar la interfaz con la API Backend correspondiente</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>[Escenario 1:]
-- **Escenario 1:** Dado que tengo el rol de Administrador, Cuando hago clic en el botón "Gestión", Entonces accedo directamente al panel de administración.
-[Escenario 2:]
-- **Escenario 2:** Dado que un usuario sin rol de Administrador intenta ver el botón "Gestión", Cuando carga el navbar, Entonces el botón no es visible.</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 1:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que tengo el rol de Administrador, Cuando hago clic en el botón "Gestión", Entonces accedo directamente al panel de administración.
+- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 2:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que un usuario sin rol de Administrador intenta ver el botón "Gestión", Cuando carga el navbar, Entonces el botón no es visible.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F17" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>[Pendiente screenshot]</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="120" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>[Pendiente screenshot]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="120" customHeight="1" s="9">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>PB-HM-13</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="15" t="inlineStr">
         <is>
           <t>PB-HM-13.1</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" s="13" t="inlineStr">
         <is>
           <t>Como Administrador quiero crear un nuevo Rol/Grupo de permisos para estructurar mejor el control de accesos.</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="13" t="inlineStr">
         <is>
           <t>- [ ] Desarrollar formulario/modal para la acción
 - [ ] Validar permisos del rol en el frontend
 - [ ] Conectar endpoint CRUD y mostrar notificación de resultado</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>[Escenario 1:]
-- **Escenario 1:** Dado que estoy en el panel de Gestión, Cuando creo un nuevo rol con nombre único y le asigno permisos, Entonces se registra exitosamente en el sistema.
-[Escenario 2:]
-- **Escenario 2:** Dado que intento crear un rol, Cuando uso un nombre que ya existe (ej. Consultor de Ciberseguridad repetido), Entonces el sistema muestra un error impidiendo la duplicidad.</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="E18" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 1:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que estoy en el panel de Gestión, Cuando creo un nuevo rol con nombre único y le asigno permisos, Entonces se registra exitosamente en el sistema.
+- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 2:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que intento crear un rol, Cuando uso un nombre que ya existe (ej. Consultor de Ciberseguridad repetido), Entonces el sistema muestra un error impidiendo la duplicidad.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>[Pendiente screenshot]</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="120" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t>[Pendiente screenshot]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="120" customHeight="1" s="9">
+      <c r="A19" s="12" t="inlineStr">
         <is>
           <t>PB-HM-14</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B19" s="15" t="inlineStr">
         <is>
           <t>PB-HM-14.1</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" s="13" t="inlineStr">
         <is>
           <t>Como Administrador quiero consultar la lista de Roles/Grupos existentes para ver cómo están distribuidos los usuarios.</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D19" s="13" t="inlineStr">
         <is>
           <t>- [ ] Diseñar e implementar el componente UI necesario
 - [ ] Establecer lógica de estado (React hooks) y validaciones
 - [ ] Conectar la interfaz con la API Backend correspondiente</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>[Escenario 1:]
-- **Escenario 1:** Dado que accedo a la sección de Roles, Cuando carga la vista, Entonces veo todos los grupos registrados y la cantidad de usuarios asociados.
-[Escenario 2:]
-- **Escenario 2:** Dado que la lista se muestra en pantalla, Cuando reviso los registros, Entonces puedo identificar claramente el nombre de cada grupo existente.</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 1:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que accedo a la sección de Roles, Cuando carga la vista, Entonces veo todos los grupos registrados y la cantidad de usuarios asociados.
+- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 2:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que la lista se muestra en pantalla, Cuando reviso los registros, Entonces puedo identificar claramente el nombre de cada grupo existente.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F19" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>[Pendiente screenshot]</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="120" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="G19" s="12" t="inlineStr">
+        <is>
+          <t>[Pendiente screenshot]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="120" customHeight="1" s="9">
+      <c r="A20" s="12" t="inlineStr">
         <is>
           <t>PB-HM-15</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B20" s="15" t="inlineStr">
         <is>
           <t>PB-HM-15.1</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" s="13" t="inlineStr">
         <is>
           <t>Como Administrador quiero modificar un Rol/Grupo de permisos existente para ajustar sus capacidades en el sistema.</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D20" s="13" t="inlineStr">
         <is>
           <t>- [ ] Desarrollar formulario/modal para la acción
 - [ ] Validar permisos del rol en el frontend
 - [ ] Conectar endpoint CRUD y mostrar notificación de resultado</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>[Escenario 1:]
-- **Escenario 1:** Dado que selecciono un rol existente, Cuando edito su nombre o permisos asignados, Entonces los cambios se guardan correctamente.
-[Escenario 2:]
-- **Escenario 2:** Dado que edité un rol, Cuando un usuario con ese rol realiza una acción, Entonces los nuevos permisos se aplican inmediatamente.</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="E20" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 1:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que selecciono un rol existente, Cuando edito su nombre o permisos asignados, Entonces los cambios se guardan correctamente.
+- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 2:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que edité un rol, Cuando un usuario con ese rol realiza una acción, Entonces los nuevos permisos se aplican inmediatamente.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F20" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>[Pendiente screenshot]</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="120" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="G20" s="12" t="inlineStr">
+        <is>
+          <t>[Pendiente screenshot]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="120" customHeight="1" s="9">
+      <c r="A21" s="12" t="inlineStr">
         <is>
           <t>PB-HM-16</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B21" s="15" t="inlineStr">
         <is>
           <t>PB-HM-16.1</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" s="13" t="inlineStr">
         <is>
           <t>Como Administrador quiero eliminar un Rol/Grupo de permisos para limpiar el sistema de grupos obsoletos.</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D21" s="13" t="inlineStr">
         <is>
           <t>- [ ] Desarrollar formulario/modal para la acción
 - [ ] Validar permisos del rol en el frontend
 - [ ] Conectar endpoint CRUD y mostrar notificación de resultado</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>[Escenario 1:]
-- **Escenario 1:** Dado que intento borrar un grupo, Cuando solicito la eliminación, Entonces el sistema me avisa cuántos usuarios quedarán sin rol.
-[Escenario 2:]
-- **Escenario 2:** Dado que veo la advertencia, Cuando confirmo explícitamente, Entonces el grupo se borra permanentemente del sistema.</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 1:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que intento borrar un grupo, Cuando solicito la eliminación, Entonces el sistema me avisa cuántos usuarios quedarán sin rol.
+- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 2:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que veo la advertencia, Cuando confirmo explícitamente, Entonces el grupo se borra permanentemente del sistema.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F21" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>[Pendiente screenshot]</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="120" customHeight="1">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="G21" s="12" t="inlineStr">
+        <is>
+          <t>[Pendiente screenshot]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="120" customHeight="1" s="9">
+      <c r="A22" s="12" t="inlineStr">
         <is>
           <t>PB-HM-17</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B22" s="15" t="inlineStr">
         <is>
           <t>PB-HM-17.1</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C22" s="13" t="inlineStr">
         <is>
           <t>Como Administrador quiero crear la cuenta de un nuevo usuario para integrar nuevos miembros al equipo.</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D22" s="13" t="inlineStr">
         <is>
           <t>- [ ] Desarrollar formulario/modal para la acción
 - [ ] Validar permisos del rol en el frontend
 - [ ] Conectar endpoint CRUD y mostrar notificación de resultado</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>[Escenario 1:]
-- **Escenario 1:** Dado que estoy en la gestión de usuarios, Cuando ingreso nombre, correo institucional, clave temporal y asigno un único rol (Directivo, Consultor o Analista), Entonces se registra el nuevo usuario.
-[Escenario 2:]
-- **Escenario 2:** Dado que intento crear un usuario, Cuando intento asignar más de un rol simultáneamente, Entonces el sistema me bloquea.</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 1:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que estoy en la gestión de usuarios, Cuando ingreso nombre, correo institucional, clave temporal y asigno un único rol (Directivo, Consultor o Analista), Entonces se registra el nuevo usuario.
+- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 2:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que intento crear un usuario, Cuando intento asignar más de un rol simultáneamente, Entonces el sistema me bloquea.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F22" s="12" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>[Pendiente screenshot]</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="120" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="G22" s="12" t="inlineStr">
+        <is>
+          <t>[Pendiente screenshot]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="120" customHeight="1" s="9">
+      <c r="A23" s="12" t="inlineStr">
         <is>
           <t>PB-HM-18</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B23" s="15" t="inlineStr">
         <is>
           <t>PB-HM-18.1</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C23" s="13" t="inlineStr">
         <is>
           <t>Como Administrador quiero consultar la lista de usuarios registrados para administrar las cuentas activas e inactivas.</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D23" s="13" t="inlineStr">
         <is>
           <t>- [ ] Diseñar e implementar el componente UI necesario
 - [ ] Establecer lógica de estado (React hooks) y validaciones
 - [ ] Conectar la interfaz con la API Backend correspondiente</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>[Escenario 1:]
-- **Escenario 1:** Dado que accedo a la sección de Usuarios, Cuando visualizo la tabla, Entonces veo columnas de nombre, correo, rol y estado.
-[Escenario 2:]
-- **Escenario 2:** Dado que la tabla tiene registros, Cuando uso la barra de búsqueda o filtros, Entonces puedo encontrar un usuario específico rápidamente.</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
+      <c r="E23" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 1:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que accedo a la sección de Usuarios, Cuando visualizo la tabla, Entonces veo columnas de nombre, correo, rol y estado.
+- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 2:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que la tabla tiene registros, Cuando uso la barra de búsqueda o filtros, Entonces puedo encontrar un usuario específico rápidamente.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F23" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>[Pendiente screenshot]</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="120" customHeight="1">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="G23" s="12" t="inlineStr">
+        <is>
+          <t>[Pendiente screenshot]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="120" customHeight="1" s="9">
+      <c r="A24" s="12" t="inlineStr">
         <is>
           <t>PB-HM-19</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B24" s="15" t="inlineStr">
         <is>
           <t>PB-HM-19.1</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C24" s="13" t="inlineStr">
         <is>
           <t>Como Administrador quiero modificar los datos de un usuario existente para mantener su perfil actualizado sin recrear su cuenta.</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D24" s="13" t="inlineStr">
         <is>
           <t>- [ ] Desarrollar formulario/modal para la acción
 - [ ] Validar permisos del rol en el frontend
 - [ ] Conectar endpoint CRUD y mostrar notificación de resultado</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>[Escenario 1:]
-- **Escenario 1:** Dado que selecciono un usuario, Cuando edito su nombre, correo o rol asignado, Entonces la información se actualiza correctamente.
-[Escenario 2:]
-- **Escenario 2:** Dado que modifico el rol de un usuario, Cuando este intenta acceder, Entonces se le aplican sus nuevos permisos inmediatamente sin eliminar su cuenta.</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
+      <c r="E24" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 1:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que selecciono un usuario, Cuando edito su nombre, correo o rol asignado, Entonces la información se actualiza correctamente.
+- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 2:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que modifico el rol de un usuario, Cuando este intenta acceder, Entonces se le aplican sus nuevos permisos inmediatamente sin eliminar su cuenta.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F24" s="12" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>[Pendiente screenshot]</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="120" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="G24" s="12" t="inlineStr">
+        <is>
+          <t>[Pendiente screenshot]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="120" customHeight="1" s="9">
+      <c r="A25" s="12" t="inlineStr">
         <is>
           <t>PB-HM-20</t>
         </is>
       </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="B25" s="15" t="inlineStr">
         <is>
           <t>PB-HM-20.1</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C25" s="13" t="inlineStr">
         <is>
           <t>Como Administrador quiero eliminar un usuario del sistema de forma segura para remover el acceso de miembros que ya no pertenecen al equipo.</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D25" s="13" t="inlineStr">
         <is>
           <t>- [ ] Desarrollar formulario/modal para la acción
 - [ ] Validar permisos del rol en el frontend
 - [ ] Conectar endpoint CRUD y mostrar notificación de resultado</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>[Escenario 1:]
-- **Escenario 1:** Dado que solicito borrar un usuario, Cuando inicio el proceso, Entonces el sistema muestra un aviso detallado de los datos en cascada que serán eliminados.
-[Escenario 2:]
-- **Escenario 2:** Dado que reviso la advertencia, Cuando realizo la confirmación explícita, Entonces el usuario se elimina definitivamente y permanentemente.</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
+      <c r="E25" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 1:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que solicito borrar un usuario, Cuando inicio el proceso, Entonces el sistema muestra un aviso detallado de los datos en cascada que serán eliminados.
+- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 2:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que reviso la advertencia, Cuando realizo la confirmación explícita, Entonces el usuario se elimina definitivamente y permanentemente.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F25" s="12" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>[Pendiente screenshot]</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="120" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="G25" s="12" t="inlineStr">
+        <is>
+          <t>[Pendiente screenshot]</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="120" customHeight="1" s="9">
+      <c r="A26" s="12" t="inlineStr">
         <is>
           <t>PB-HM-21</t>
         </is>
       </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="B26" s="15" t="inlineStr">
         <is>
           <t>PB-HM-21.1</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C26" s="13" t="inlineStr">
         <is>
           <t>Como Usuario quiero visualizar y editar mi perfil propio para personalizar mi experiencia y gestionar mi información.</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D26" s="13" t="inlineStr">
         <is>
           <t>- [ ] Diseñar e implementar el componente UI necesario
 - [ ] Establecer lógica de estado (React hooks) y validaciones
 - [ ] Conectar la interfaz con la API Backend correspondiente</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>[Escenario 1:]
-- **Escenario 1:** Dado que accedo a mi perfil, Cuando visualizo mis datos, Entonces puedo ver mi rol y cambiar mi zona horaria.
-[Escenario 2:]
-- **Escenario 2:** Dado que edito mis preferencias, Cuando subo una foto (JPG/PNG máx. 2MB) o cambio entre tema claro/oscuro, Entonces los cambios se guardan con éxito.</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
+      <c r="E26" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 1:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que accedo a mi perfil, Cuando visualizo mis datos, Entonces puedo ver mi rol y cambiar mi zona horaria.
+- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 2:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que edito mis preferencias, Cuando subo una foto (JPG/PNG máx. 2MB) o cambio entre tema claro/oscuro, Entonces los cambios se guardan con éxito.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F26" s="12" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>[Pendiente screenshot]</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="120" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="G26" s="12" t="inlineStr">
+        <is>
+          <t>[Pendiente screenshot]</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="120" customHeight="1" s="9">
+      <c r="A27" s="12" t="inlineStr">
         <is>
           <t>PB-HM-22</t>
         </is>
       </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="B27" s="15" t="inlineStr">
         <is>
           <t>PB-HM-22.1</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C27" s="13" t="inlineStr">
         <is>
           <t>Como Usuario quiero consultar la Lista Negra de IPs para identificar las amenazas registradas de manera interactiva.</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D27" s="13" t="inlineStr">
         <is>
           <t>- [ ] Crear componente de tabla interactiva (paginación/filtros)
 - [ ] Implementar petición GET para listar registros
 - [ ] Validar renderizado condicional de acciones según rol</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>[Escenario 1:]
-- **Escenario 1:** Dado que accedo a la Lista Negra, Cuando se carga la tabla mediante Fetch DataTables (paginación del servidor a 10 por página), Entonces veo las columnas de IP, tipo, país, ataque y reportador.
-[Escenario 2:]
-- **Escenario 2:** Dado que visualizo los registros, Cuando reviso las IPs, Entonces veo insignias visuales de IP Pública/Privada, y si soy "Directivo de T.I.", veo candados visuales indicando solo lectura.</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
+      <c r="E27" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 1:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que accedo a la Lista Negra, Cuando se carga la tabla mediante Fetch DataTables (paginación del servidor a 10 por página), Entonces veo las columnas de IP, tipo, país, ataque y reportador.
+- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 2:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que visualizo los registros, Cuando reviso las IPs, Entonces veo insignias visuales de IP Pública/Privada, y si soy "Directivo de T.I.", veo candados visuales indicando solo lectura.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F27" s="12" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>[Pendiente screenshot]</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="120" customHeight="1">
-      <c r="A28" s="3" t="inlineStr">
+      <c r="G27" s="12" t="inlineStr">
+        <is>
+          <t>[Pendiente screenshot]</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="120" customHeight="1" s="9">
+      <c r="A28" s="12" t="inlineStr">
         <is>
           <t>PB-HM-23</t>
         </is>
       </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="B28" s="15" t="inlineStr">
         <is>
           <t>PB-HM-23.1</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C28" s="13" t="inlineStr">
         <is>
           <t>Como Usuario Operativo quiero agregar una IP a la Lista Negra para reportar nuevas amenazas en el sistema con un modal.</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D28" s="13" t="inlineStr">
         <is>
           <t>- [ ] Crear componente de tabla interactiva (paginación/filtros)
 - [ ] Implementar petición GET para listar registros
 - [ ] Validar renderizado condicional de acciones según rol</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>[Escenario 1:]
-- **Escenario 1:** Dado que uso el formulario modal, Cuando ingreso una IP, Entonces el sistema valida su formato (IPv4/IPv6) y calcula la insignia de IP Pública/Privada.
-[Escenario 2:]
-- **Escenario 2:** Dado que completo el formulario correctamente, Cuando lo guardo, Entonces el sistema asigna automáticamente al usuario en sesión como creador del reporte.</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
+      <c r="E28" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 1:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que uso el formulario modal, Cuando ingreso una IP, Entonces el sistema valida su formato (IPv4/IPv6) y calcula la insignia de IP Pública/Privada.
+- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 2:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que completo el formulario correctamente, Cuando lo guardo, Entonces el sistema asigna automáticamente al usuario en sesión como creador del reporte.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F28" s="12" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>[Pendiente screenshot]</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="120" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="G28" s="12" t="inlineStr">
+        <is>
+          <t>[Pendiente screenshot]</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="120" customHeight="1" s="9">
+      <c r="A29" s="12" t="inlineStr">
         <is>
           <t>PB-HM-24</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B29" s="15" t="inlineStr">
         <is>
           <t>PB-HM-24.1</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C29" s="13" t="inlineStr">
         <is>
           <t>Como Usuario Operativo quiero eliminar una IP de la Lista Negra para corregir falsos positivos o remover IPs limpias.</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D29" s="13" t="inlineStr">
         <is>
           <t>- [ ] Crear componente de tabla interactiva (paginación/filtros)
 - [ ] Implementar petición GET para listar registros
 - [ ] Validar renderizado condicional de acciones según rol</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>[Escenario 1:]
-- **Escenario 1:** Dado que estoy viendo la tabla de Lista Negra, Cuando selecciono la opción de remover en una fila, Entonces el sistema pide confirmación explícita para evitar borrados accidentales.
-[Escenario 2:]
-- **Escenario 2:** Dado que confirmo la eliminación, Cuando se procesa, Entonces el registro desaparece permanentemente de la lista de amenazas.</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
+      <c r="E29" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 1:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que estoy viendo la tabla de Lista Negra, Cuando selecciono la opción de remover en una fila, Entonces el sistema pide confirmación explícita para evitar borrados accidentales.
+- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 2:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que confirmo la eliminación, Cuando se procesa, Entonces el registro desaparece permanentemente de la lista de amenazas.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F29" s="12" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>[Pendiente screenshot]</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="120" customHeight="1">
-      <c r="A30" s="3" t="inlineStr">
+      <c r="G29" s="12" t="inlineStr">
+        <is>
+          <t>[Pendiente screenshot]</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="120" customHeight="1" s="9">
+      <c r="A30" s="12" t="inlineStr">
         <is>
           <t>PB-HM-25</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B30" s="15" t="inlineStr">
         <is>
           <t>PB-HM-25.1</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C30" s="13" t="inlineStr">
         <is>
           <t>Como Usuario quiero exportar la Lista Negra de IPs para analizar los datos en herramientas externas.</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D30" s="13" t="inlineStr">
         <is>
           <t>- [ ] Crear componente de tabla interactiva (paginación/filtros)
 - [ ] Implementar petición GET para listar registros
 - [ ] Validar renderizado condicional de acciones según rol</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>[Escenario 1:]
-- **Escenario 1:** Dado que la tabla contiene datos y tiene filtros activos, Cuando hago clic en exportar a CSV/Excel, Entonces el sistema descarga el archivo respetando dichos filtros.
-[Escenario 2:]
-- **Escenario 2:** Dado que la tabla no contiene ningún dato, Cuando intento exportar, Entonces el botón de exportación se encuentra deshabilitado visualmente.</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 1:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que la tabla contiene datos y tiene filtros activos, Cuando hago clic en exportar a CSV/Excel, Entonces el sistema descarga el archivo respetando dichos filtros.
+- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 2:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que la tabla no contiene ningún dato, Cuando intento exportar, Entonces el botón de exportación se encuentra deshabilitado visualmente.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F30" s="12" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t>[Pendiente screenshot]</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="120" customHeight="1">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="G30" s="12" t="inlineStr">
+        <is>
+          <t>[Pendiente screenshot]</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="120" customHeight="1" s="9">
+      <c r="A31" s="12" t="inlineStr">
         <is>
           <t>PB-HM-61</t>
         </is>
       </c>
-      <c r="B31" s="6" t="inlineStr">
+      <c r="B31" s="15" t="inlineStr">
         <is>
           <t>PB-HM-61.1</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C31" s="13" t="inlineStr">
         <is>
           <t>Como Analista quiero visualizar un Threat Score Dinámico para cada IP con el fin de evaluar su nivel de peligrosidad.</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D31" s="13" t="inlineStr">
         <is>
           <t>- [ ] Diseñar e implementar el componente UI necesario
 - [ ] Establecer lógica de estado (React hooks) y validaciones
 - [ ] Conectar la interfaz con la API Backend correspondiente</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>[Escenario 1:]
-- **Escenario 1:** Dado que observo una IP en el Threat Intelligence Center, Cuando el sistema procesa sus métricas, Entonces veo un Threat Score dinámico de 0 a 100 calculado por volumen, persistencia, tácticas y severidad.
-[Escenario 2:]
-- **Escenario 2:** Dado que la IP recibe su puntaje dinámico, Cuando rebasa los umbrales configurados, Entonces se le asigna una categoría adecuada (Ej. APT, Botnet, Scanner) visible en pantalla.</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
+      <c r="E31" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 1:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que observo una IP en el Threat Intelligence Center, Cuando el sistema procesa sus métricas, Entonces veo un Threat Score dinámico de 0 a 100 calculado por volumen, persistencia, tácticas y severidad.
+- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 2:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que la IP recibe su puntaje dinámico, Cuando rebasa los umbrales configurados, Entonces se le asigna una categoría adecuada (Ej. APT, Botnet, Scanner) visible en pantalla.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F31" s="12" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>[Pendiente screenshot]</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="120" customHeight="1">
-      <c r="A32" s="3" t="inlineStr">
+      <c r="G31" s="12" t="inlineStr">
+        <is>
+          <t>[Pendiente screenshot]</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="120" customHeight="1" s="9">
+      <c r="A32" s="12" t="inlineStr">
         <is>
           <t>PB-HM-26</t>
         </is>
       </c>
-      <c r="B32" s="6" t="inlineStr">
+      <c r="B32" s="15" t="inlineStr">
         <is>
           <t>PB-HM-26.1</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C32" s="13" t="inlineStr">
         <is>
           <t>Como usuario autorizado quiero visualizar un dashboard principal con KPIs y cuatro gráficos dinámicos (torta para distribución por módulo, líneas spline para histórico, y barras horizontales max 40 caracteres para top agentes y eventos) para monitorear el estado general de las amenazas de forma rápida.</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D32" s="13" t="inlineStr">
         <is>
           <t>- [ ] Preparar componente contenedor de la visualización
 - [ ] Integrar librería Plotly.js / Chart.js
 - [ ] Conectar endpoint para inyección dinámica de datos</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>[Escenario 1:]
-- **Escenario 1:** Dado que ingreso al sistema exitosamente, Cuando navego a la vista de "Dashboard", Entonces el sistema carga por defecto los datos de los últimos 7 días.
-[Escenario 2:]
-- **Escenario 2:** Dado que visualizo los gráficos de "Top Agentes" y "Top Eventos", Cuando los nombres exceden la longitud permitida, Entonces el sistema recorta el texto a un máximo de 40 caracteres con puntos suspensivos en los gráficos de barras horizontales.</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
+      <c r="E32" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 1:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que ingreso al sistema exitosamente, Cuando navego a la vista de "Dashboard", Entonces el sistema carga por defecto los datos de los últimos 7 días.
+- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 2:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que visualizo los gráficos de "Top Agentes" y "Top Eventos", Cuando los nombres exceden la longitud permitida, Entonces el sistema recorta el texto a un máximo de 40 caracteres con puntos suspensivos en los gráficos de barras horizontales.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F32" s="12" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t>[Pendiente screenshot]</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="120" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="G32" s="12" t="inlineStr">
+        <is>
+          <t>[Pendiente screenshot]</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="120" customHeight="1" s="9">
+      <c r="A33" s="12" t="inlineStr">
         <is>
           <t>PB-HM-27</t>
         </is>
       </c>
-      <c r="B33" s="6" t="inlineStr">
+      <c r="B33" s="15" t="inlineStr">
         <is>
           <t>PB-HM-27.1</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C33" s="13" t="inlineStr">
         <is>
           <t>Como usuario quiero filtrar la información del dashboard principal por rangos de fechas definidos (ej. now-7d/d) para analizar períodos específicos de actividad maliciosa.</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D33" s="13" t="inlineStr">
         <is>
           <t>- [ ] Preparar componente contenedor de la visualización
 - [ ] Integrar librería Plotly.js / Chart.js
 - [ ] Conectar endpoint para inyección dinámica de datos</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>[Escenario 1:]
-- **Escenario 1:** Dado que me encuentro en el dashboard principal, Cuando selecciono el filtro de "Últimas 24 horas", Entonces todos los gráficos y KPIs se actualizan instantáneamente sin recargar la página completa.
-[Escenario 2:]
-- **Escenario 2:** Dado que selecciono un rango de fechas personalizado, Cuando el rango no tiene datos registrados, Entonces los gráficos muestran un mensaje amigable indicando "No hay datos disponibles para el rango seleccionado".</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
+      <c r="E33" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 1:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que me encuentro en el dashboard principal, Cuando selecciono el filtro de "Últimas 24 horas", Entonces todos los gráficos y KPIs se actualizan instantáneamente sin recargar la página completa.
+- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 2:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que selecciono un rango de fechas personalizado, Cuando el rango no tiene datos registrados, Entonces los gráficos muestran un mensaje amigable indicando "No hay datos disponibles para el rango seleccionado".</t>
+          </r>
+        </is>
+      </c>
+      <c r="F33" s="12" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>[Pendiente screenshot]</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="120" customHeight="1">
-      <c r="A34" s="3" t="inlineStr">
+      <c r="G33" s="12" t="inlineStr">
+        <is>
+          <t>[Pendiente screenshot]</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="120" customHeight="1" s="9">
+      <c r="A34" s="12" t="inlineStr">
         <is>
           <t>PB-HM-28</t>
         </is>
       </c>
-      <c r="B34" s="6" t="inlineStr">
+      <c r="B34" s="15" t="inlineStr">
         <is>
           <t>PB-HM-28.1</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C34" s="13" t="inlineStr">
         <is>
           <t>Como usuario quiero visualizar un Mapa de Calor Interactivo mundial para identificar visualmente de qué países provienen la mayor cantidad de ataques.</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D34" s="13" t="inlineStr">
         <is>
           <t>- [ ] Diseñar e implementar el componente UI necesario
 - [ ] Establecer lógica de estado (React hooks) y validaciones
 - [ ] Conectar la interfaz con la API Backend correspondiente</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>[Escenario 1:]
-- **Escenario 1:** Dado que ingreso a la sección del mapa de calor, Cuando el mapa termina de cargar, Entonces los países atacantes se pintan en una escala de verde a rojo dependiendo de la intensidad del ataque y se muestra una tabla de "Top 10 Países Atacantes".
-[Escenario 2:]
-- **Escenario 2:** Dado que observo el mapa interactivo, Cuando paso el cursor (hover) sobre un país en rojo, Entonces aparece un tooltip mostrando el nombre del país y la cantidad total de eventos registrados.</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="inlineStr">
+      <c r="E34" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 1:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que ingreso a la sección del mapa de calor, Cuando el mapa termina de cargar, Entonces los países atacantes se pintan en una escala de verde a rojo dependiendo de la intensidad del ataque y se muestra una tabla de "Top 10 Países Atacantes".
+- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 2:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que observo el mapa interactivo, Cuando paso el cursor (hover) sobre un país en rojo, Entonces aparece un tooltip mostrando el nombre del país y la cantidad total de eventos registrados.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F34" s="12" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="G34" s="3" t="inlineStr">
-        <is>
-          <t>[Pendiente screenshot]</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="120" customHeight="1">
-      <c r="A35" s="3" t="inlineStr">
+      <c r="G34" s="12" t="inlineStr">
+        <is>
+          <t>[Pendiente screenshot]</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="120" customHeight="1" s="9">
+      <c r="A35" s="12" t="inlineStr">
         <is>
           <t>PB-HM-29</t>
         </is>
       </c>
-      <c r="B35" s="6" t="inlineStr">
+      <c r="B35" s="15" t="inlineStr">
         <is>
           <t>PB-HM-29.1</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C35" s="13" t="inlineStr">
         <is>
           <t>Como usuario quiero filtrar el Mapa de Calor por tipo de ataque específico para entender la distribución geográfica de amenazas particulares.</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D35" s="13" t="inlineStr">
         <is>
           <t>- [ ] Crear componente de tabla interactiva (paginación/filtros)
 - [ ] Implementar petición GET para listar registros
 - [ ] Validar renderizado condicional de acciones según rol</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>[Escenario 1:]
-- **Escenario 1:** Dado que visualizo el mapa de calor, Cuando selecciono "Fuerza Bruta SSH" en el selector de tipo de ataque, Entonces el mapa y el ranking se recalculan únicamente con los datos de ese tipo de ataque.
-[Escenario 2:]
-- **Escenario 2:** Dado que aplico un filtro de ataque, Cuando deseo ver todos los ataques nuevamente, Entonces puedo limpiar el filtro y el mapa restaura la vista global original.</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
+      <c r="E35" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 1:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que visualizo el mapa de calor, Cuando selecciono "Fuerza Bruta SSH" en el selector de tipo de ataque, Entonces el mapa y el ranking se recalculan únicamente con los datos de ese tipo de ataque.
+- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 2:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que aplico un filtro de ataque, Cuando deseo ver todos los ataques nuevamente, Entonces puedo limpiar el filtro y el mapa restaura la vista global original.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F35" s="12" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t>[Pendiente screenshot]</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="120" customHeight="1">
-      <c r="A36" s="3" t="inlineStr">
+      <c r="G35" s="12" t="inlineStr">
+        <is>
+          <t>[Pendiente screenshot]</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="120" customHeight="1" s="9">
+      <c r="A36" s="12" t="inlineStr">
         <is>
           <t>PB-HM-30</t>
         </is>
       </c>
-      <c r="B36" s="6" t="inlineStr">
+      <c r="B36" s="15" t="inlineStr">
         <is>
           <t>PB-HM-30.1</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="C36" s="13" t="inlineStr">
         <is>
           <t>Como usuario quiero ver un panel lateral con información detallada al seleccionar un país en el mapa de calor para obtener un desglose profundo de los incidentes provenientes de esa región.</t>
         </is>
       </c>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="D36" s="13" t="inlineStr">
         <is>
           <t>- [ ] Diseñar e implementar el componente UI necesario
 - [ ] Establecer lógica de estado (React hooks) y validaciones
 - [ ] Conectar la interfaz con la API Backend correspondiente</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>[Escenario 1:]
-- **Escenario 1:** Dado que navego en el mapa de calor, Cuando hago clic izquierdo sobre "Rusia", Entonces se despliega un panel lateral derecho mostrando el top de IPs, los tipos de ataque y los periodos de actividad de ese país.
-[Escenario 2:]
-- **Escenario 2:** Dado que tengo el panel lateral abierto, Cuando hago clic fuera del panel o en el botón "Cerrar", Entonces el panel se oculta y puedo seguir interactuando con el mapa mundial completo.</t>
-        </is>
-      </c>
-      <c r="F36" s="3" t="inlineStr">
+      <c r="E36" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 1:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que navego en el mapa de calor, Cuando hago clic izquierdo sobre "Rusia", Entonces se despliega un panel lateral derecho mostrando el top de IPs, los tipos de ataque y los periodos de actividad de ese país.
+- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 2:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que tengo el panel lateral abierto, Cuando hago clic fuera del panel o en el botón "Cerrar", Entonces el panel se oculta y puedo seguir interactuando con el mapa mundial completo.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F36" s="12" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t>[Pendiente screenshot]</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="120" customHeight="1">
-      <c r="A37" s="3" t="inlineStr">
+      <c r="G36" s="12" t="inlineStr">
+        <is>
+          <t>[Pendiente screenshot]</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="120" customHeight="1" s="9">
+      <c r="A37" s="12" t="inlineStr">
         <is>
           <t>PB-HM-31</t>
         </is>
       </c>
-      <c r="B37" s="6" t="inlineStr">
+      <c r="B37" s="15" t="inlineStr">
         <is>
           <t>PB-HM-31.1</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C37" s="13" t="inlineStr">
         <is>
           <t>Como usuario autorizado quiero acceder a una vista de Estadística Descriptiva (media, mediana, moda, varianza, histograma, boxplot) para analizar el comportamiento profundo de las variables numéricas de los ataques.</t>
         </is>
       </c>
-      <c r="D37" s="4" t="inlineStr">
+      <c r="D37" s="13" t="inlineStr">
         <is>
           <t>- [ ] Crear componente de tabla interactiva (paginación/filtros)
 - [ ] Implementar petición GET para listar registros
 - [ ] Validar renderizado condicional de acciones según rol</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>[Escenario 1:]
-- **Escenario 1:** Dado que ingreso a la vista de estadísticas descriptivas, Cuando selecciono la variable "Volumen de alertas por hora", Entonces se calculan la media, mediana, moda y desviación estándar, mostrándose un histograma de frecuencias.
-[Escenario 2:]
-- **Escenario 2:** Dado que analizo la misma variable, Cuando visualizo la sección inferior de la pantalla, Entonces observo un diagrama de caja (boxplot) que me permite identificar visualmente los valores atípicos (outliers).</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="inlineStr">
+      <c r="E37" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 1:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que ingreso a la vista de estadísticas descriptivas, Cuando selecciono la variable "Volumen de alertas por hora", Entonces se calculan la media, mediana, moda y desviación estándar, mostrándose un histograma de frecuencias.
+- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 2:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que analizo la misma variable, Cuando visualizo la sección inferior de la pantalla, Entonces observo un diagrama de caja (boxplot) que me permite identificar visualmente los valores atípicos (outliers).</t>
+          </r>
+        </is>
+      </c>
+      <c r="F37" s="12" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="G37" s="3" t="inlineStr">
-        <is>
-          <t>[Pendiente screenshot]</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="120" customHeight="1">
-      <c r="A38" s="3" t="inlineStr">
+      <c r="G37" s="12" t="inlineStr">
+        <is>
+          <t>[Pendiente screenshot]</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="120" customHeight="1" s="9">
+      <c r="A38" s="12" t="inlineStr">
         <is>
           <t>PB-HM-32</t>
         </is>
       </c>
-      <c r="B38" s="6" t="inlineStr">
+      <c r="B38" s="15" t="inlineStr">
         <is>
           <t>PB-HM-32.1</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
+      <c r="C38" s="13" t="inlineStr">
         <is>
           <t>Como usuario quiero filtrar las estadísticas descriptivas por diferentes variables y rangos de fecha para personalizar mi análisis según el contexto temporal requerido.</t>
         </is>
       </c>
-      <c r="D38" s="4" t="inlineStr">
+      <c r="D38" s="13" t="inlineStr">
         <is>
           <t>- [ ] Crear componente de tabla interactiva (paginación/filtros)
 - [ ] Implementar petición GET para listar registros
 - [ ] Validar renderizado condicional de acciones según rol</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>[Escenario 1:]
-- **Escenario 1:** Dado que estoy viendo estadísticas descriptivas, Cuando cambio la variable analizada a "Duración del ataque en segundos", Entonces todos los cálculos y gráficos se actualizan inmediatamente con la nueva variable.
-[Escenario 2:]
-- **Escenario 2:** Dado que ajusto el rango de fechas al "Mes pasado", Cuando se aplican los filtros, Entonces los resultados estadísticos reflejan de manera exacta únicamente los eventos que sucedieron en ese mes.</t>
-        </is>
-      </c>
-      <c r="F38" s="3" t="inlineStr">
+      <c r="E38" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 1:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que estoy viendo estadísticas descriptivas, Cuando cambio la variable analizada a "Duración del ataque en segundos", Entonces todos los cálculos y gráficos se actualizan inmediatamente con la nueva variable.
+- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 2:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que ajusto el rango de fechas al "Mes pasado", Cuando se aplican los filtros, Entonces los resultados estadísticos reflejan de manera exacta únicamente los eventos que sucedieron en ese mes.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F38" s="12" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G38" s="3" t="inlineStr">
-        <is>
-          <t>[Pendiente screenshot]</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="120" customHeight="1">
-      <c r="A39" s="3" t="inlineStr">
+      <c r="G38" s="12" t="inlineStr">
+        <is>
+          <t>[Pendiente screenshot]</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="120" customHeight="1" s="9">
+      <c r="A39" s="12" t="inlineStr">
         <is>
           <t>PB-HM-33</t>
         </is>
       </c>
-      <c r="B39" s="6" t="inlineStr">
+      <c r="B39" s="15" t="inlineStr">
         <is>
           <t>PB-HM-33.1</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C39" s="13" t="inlineStr">
         <is>
           <t>Como Analista quiero poder descargar la tabla de métricas estadísticas en formato CSV para poder integrar estos resultados en reportes externos o presentaciones de gestión.</t>
         </is>
       </c>
-      <c r="D39" s="4" t="inlineStr">
+      <c r="D39" s="13" t="inlineStr">
         <is>
           <t>- [ ] Implementar botón de exportación en la interfaz
 - [ ] Configurar manejo del Blob / archivo recibido
 - [ ] Notificar éxito o error de la descarga al usuario</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>[Escenario 1:]
-- **Escenario 1:** Dado que he calculado medidas estadísticas, Cuando hago clic en el botón "Exportar CSV", Entonces el sistema genera y descarga un archivo CSV con las métricas actualmente mostradas en pantalla.
-[Escenario 2:]
-- **Escenario 2:** Dado que no hay datos para el rango seleccionado, Cuando intento exportar, Entonces el botón de exportación se encuentra deshabilitado para evitar archivos vacíos.</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
+      <c r="E39" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 1:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que he calculado medidas estadísticas, Cuando hago clic en el botón "Exportar CSV", Entonces el sistema genera y descarga un archivo CSV con las métricas actualmente mostradas en pantalla.
+- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 2:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que no hay datos para el rango seleccionado, Cuando intento exportar, Entonces el botón de exportación se encuentra deshabilitado para evitar archivos vacíos.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F39" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>[Pendiente screenshot]</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="120" customHeight="1">
-      <c r="A40" s="3" t="inlineStr">
+      <c r="G39" s="12" t="inlineStr">
+        <is>
+          <t>[Pendiente screenshot]</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="120" customHeight="1" s="9">
+      <c r="A40" s="12" t="inlineStr">
         <is>
           <t>PB-HM-34</t>
         </is>
       </c>
-      <c r="B40" s="6" t="inlineStr">
+      <c r="B40" s="15" t="inlineStr">
         <is>
           <t>PB-HM-34.1</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="C40" s="13" t="inlineStr">
         <is>
           <t>Como usuario autorizado quiero visualizar una Matriz de Confusión interactiva (VP, FP, VN, FN) y sus indicadores derivados (Accuracy, Precision, Recall, F1) para evaluar la eficacia del modelo de IA en la detección.</t>
         </is>
       </c>
-      <c r="D40" s="4" t="inlineStr">
+      <c r="D40" s="13" t="inlineStr">
         <is>
           <t>- [ ] Diseñar e implementar el componente UI necesario
 - [ ] Establecer lógica de estado (React hooks) y validaciones
 - [ ] Conectar la interfaz con la API Backend correspondiente</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>[Escenario 1:]
-- **Escenario 1:** Dado que navego al panel de IA, Cuando el componente carga, Entonces visualizo una matriz 2x2 coloreada con tooltips explicativos que indican el significado de Verdaderos Positivos, Falsos Positivos, etc.
-[Escenario 2:]
-- **Escenario 2:** Dado que visualizo el panel de IA, Cuando observo la parte inferior, Entonces veo tarjetas (cards) resaltando los porcentajes de Accuracy, Precision, Recall y F1-Score calculados.</t>
-        </is>
-      </c>
-      <c r="F40" s="3" t="inlineStr">
+      <c r="E40" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 1:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que navego al panel de IA, Cuando el componente carga, Entonces visualizo una matriz 2x2 coloreada con tooltips explicativos que indican el significado de Verdaderos Positivos, Falsos Positivos, etc.
+- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 2:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que visualizo el panel de IA, Cuando observo la parte inferior, Entonces veo tarjetas (cards) resaltando los porcentajes de Accuracy, Precision, Recall y F1-Score calculados.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F40" s="12" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="G40" s="3" t="inlineStr">
-        <is>
-          <t>[Pendiente screenshot]</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="120" customHeight="1">
-      <c r="A41" s="3" t="inlineStr">
+      <c r="G40" s="12" t="inlineStr">
+        <is>
+          <t>[Pendiente screenshot]</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="120" customHeight="1" s="9">
+      <c r="A41" s="12" t="inlineStr">
         <is>
           <t>PB-HM-35</t>
         </is>
       </c>
-      <c r="B41" s="6" t="inlineStr">
+      <c r="B41" s="15" t="inlineStr">
         <is>
           <t>PB-HM-35.1</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C41" s="13" t="inlineStr">
         <is>
           <t>Como usuario quiero aplicar filtros temporales y de tipo de ataque a la Matriz de Confusión para medir cómo se comporta el modelo bajo condiciones y periodos específicos.</t>
         </is>
       </c>
-      <c r="D41" s="4" t="inlineStr">
+      <c r="D41" s="13" t="inlineStr">
         <is>
           <t>- [ ] Crear componente de tabla interactiva (paginación/filtros)
 - [ ] Implementar petición GET para listar registros
 - [ ] Validar renderizado condicional de acciones según rol</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>[Escenario 1:]
-- **Escenario 1:** Dado que estoy en el dashboard de la Matriz de Confusión, Cuando aplico el filtro de ataque "Inyección SQL", Entonces la matriz y las métricas F1/Recall se recalculan solo con los intentos de SQLi.
-[Escenario 2:]
-- **Escenario 2:** Dado que selecciono un rango muy pequeño donde no hay predicciones, Cuando se actualiza la matriz, Entonces el sistema muestra 0 en las celdas y N/A en las métricas de rendimiento.</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="inlineStr">
+      <c r="E41" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 1:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que estoy en el dashboard de la Matriz de Confusión, Cuando aplico el filtro de ataque "Inyección SQL", Entonces la matriz y las métricas F1/Recall se recalculan solo con los intentos de SQLi.
+- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 2:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que selecciono un rango muy pequeño donde no hay predicciones, Cuando se actualiza la matriz, Entonces el sistema muestra 0 en las celdas y N/A en las métricas de rendimiento.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F41" s="12" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t>[Pendiente screenshot]</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="120" customHeight="1">
-      <c r="A42" s="3" t="inlineStr">
+      <c r="G41" s="12" t="inlineStr">
+        <is>
+          <t>[Pendiente screenshot]</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="120" customHeight="1" s="9">
+      <c r="A42" s="12" t="inlineStr">
         <is>
           <t>PB-HM-36</t>
         </is>
       </c>
-      <c r="B42" s="6" t="inlineStr">
+      <c r="B42" s="15" t="inlineStr">
         <is>
           <t>PB-HM-36.1</t>
         </is>
       </c>
-      <c r="C42" s="4" t="inlineStr">
+      <c r="C42" s="13" t="inlineStr">
         <is>
           <t>Como Analista quiero hacer clic en una celda de la Matriz de Confusión (ej. Falsos Positivos) para desplegar una tabla con el detalle de las predicciones fallidas y analizarlas.</t>
         </is>
       </c>
-      <c r="D42" s="4" t="inlineStr">
+      <c r="D42" s="13" t="inlineStr">
         <is>
           <t>- [ ] Diseñar e implementar el componente UI necesario
 - [ ] Establecer lógica de estado (React hooks) y validaciones
 - [ ] Conectar la interfaz con la API Backend correspondiente</t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>[Escenario 1:]
-- **Escenario 1:** Dado que visualizo la matriz, Cuando hago clic en el cuadrante de "Falsos Positivos", Entonces se abre una tabla expansible listando la IP, fecha, clasificación real vs predicha y el % de confianza de la predicción.
-[Escenario 2:]
-- **Escenario 2:** Dado que estoy analizando la tabla de Falsos Positivos, Cuando termino la inspección, Entonces puedo contraer la tabla fácilmente pulsando el botón de cierre para volver a la matriz completa.</t>
-        </is>
-      </c>
-      <c r="F42" s="3" t="inlineStr">
+      <c r="E42" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 1:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que visualizo la matriz, Cuando hago clic en el cuadrante de "Falsos Positivos", Entonces se abre una tabla expansible listando la IP, fecha, clasificación real vs predicha y el % de confianza de la predicción.
+- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 2:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que estoy analizando la tabla de Falsos Positivos, Cuando termino la inspección, Entonces puedo contraer la tabla fácilmente pulsando el botón de cierre para volver a la matriz completa.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F42" s="12" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G42" s="3" t="inlineStr">
-        <is>
-          <t>[Pendiente screenshot]</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="120" customHeight="1">
-      <c r="A43" s="3" t="inlineStr">
+      <c r="G42" s="12" t="inlineStr">
+        <is>
+          <t>[Pendiente screenshot]</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="120" customHeight="1" s="9">
+      <c r="A43" s="12" t="inlineStr">
         <is>
           <t>PB-HM-37</t>
         </is>
       </c>
-      <c r="B43" s="6" t="inlineStr">
+      <c r="B43" s="15" t="inlineStr">
         <is>
           <t>PB-HM-37.1</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="C43" s="13" t="inlineStr">
         <is>
           <t>Como usuario quiero solicitar la extracción de logs crudos (JSONL) estableciendo un rango de fechas de manera que el sistema lo procese de forma asíncrona sin bloquear la interfaz.</t>
         </is>
       </c>
-      <c r="D43" s="4" t="inlineStr">
+      <c r="D43" s="13" t="inlineStr">
         <is>
           <t>- [ ] Diseñar e implementar el componente UI necesario
 - [ ] Establecer lógica de estado (React hooks) y validaciones
 - [ ] Conectar la interfaz con la API Backend correspondiente</t>
         </is>
       </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>[Escenario 1:]
-- **Escenario 1:** Dado que estoy en el panel de extracción de logs, Cuando solicito logs de la última semana y hago clic en "Procesar", Entonces el sistema registra la petición con estado "Procesando" y me permite seguir navegando por la web.
-[Escenario 2:]
-- **Escenario 2:** Dado que la solicitud se encuentra en segundo plano, Cuando el backend termina de construir el archivo JSONL, Entonces el estado de la tarea cambia automáticamente a "Listo".</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="inlineStr">
+      <c r="E43" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 1:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que estoy en el panel de extracción de logs, Cuando solicito logs de la última semana y hago clic en "Procesar", Entonces el sistema registra la petición con estado "Procesando" y me permite seguir navegando por la web.
+- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 2:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que la solicitud se encuentra en segundo plano, Cuando el backend termina de construir el archivo JSONL, Entonces el estado de la tarea cambia automáticamente a "Listo".</t>
+          </r>
+        </is>
+      </c>
+      <c r="F43" s="12" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="G43" s="3" t="inlineStr">
-        <is>
-          <t>[Pendiente screenshot]</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="120" customHeight="1">
-      <c r="A44" s="3" t="inlineStr">
+      <c r="G43" s="12" t="inlineStr">
+        <is>
+          <t>[Pendiente screenshot]</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="120" customHeight="1" s="9">
+      <c r="A44" s="12" t="inlineStr">
         <is>
           <t>PB-HM-38</t>
         </is>
       </c>
-      <c r="B44" s="6" t="inlineStr">
+      <c r="B44" s="15" t="inlineStr">
         <is>
           <t>PB-HM-38.1</t>
         </is>
       </c>
-      <c r="C44" s="4" t="inlineStr">
+      <c r="C44" s="13" t="inlineStr">
         <is>
           <t>Como usuario quiero consultar el historial de mis solicitudes de descarga de logs en una tabla que se actualiza periódicamente para rastrear cuáles están listas.</t>
         </is>
       </c>
-      <c r="D44" s="4" t="inlineStr">
+      <c r="D44" s="13" t="inlineStr">
         <is>
           <t>- [ ] Diseñar e implementar el componente UI necesario
 - [ ] Establecer lógica de estado (React hooks) y validaciones
 - [ ] Conectar la interfaz con la API Backend correspondiente</t>
         </is>
       </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>[Escenario 1:]
-- **Escenario 1:** Dado que abro la vista de historial de descargas, Cuando el componente carga, Entonces muestra mis solicitudes pasadas con ID, rango, total de registros, estado y fecha de creación.
-[Escenario 2:]
-- **Escenario 2:** Dado que tengo una extracción en estado "Procesando", Cuando mantengo la vista abierta por 10 segundos, Entonces el frontend realiza un chequeo silencioso (polling/SSE) y actualiza el estado a "Listo" si finalizó, sin necesidad de refrescar el navegador.</t>
-        </is>
-      </c>
-      <c r="F44" s="3" t="inlineStr">
+      <c r="E44" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 1:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que abro la vista de historial de descargas, Cuando el componente carga, Entonces muestra mis solicitudes pasadas con ID, rango, total de registros, estado y fecha de creación.
+- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 2:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que tengo una extracción en estado "Procesando", Cuando mantengo la vista abierta por 10 segundos, Entonces el frontend realiza un chequeo silencioso (polling/SSE) y actualiza el estado a "Listo" si finalizó, sin necesidad de refrescar el navegador.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F44" s="12" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G44" s="3" t="inlineStr">
-        <is>
-          <t>[Pendiente screenshot]</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="120" customHeight="1">
-      <c r="A45" s="3" t="inlineStr">
+      <c r="G44" s="12" t="inlineStr">
+        <is>
+          <t>[Pendiente screenshot]</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="120" customHeight="1" s="9">
+      <c r="A45" s="12" t="inlineStr">
         <is>
           <t>PB-HM-39</t>
         </is>
       </c>
-      <c r="B45" s="6" t="inlineStr">
+      <c r="B45" s="15" t="inlineStr">
         <is>
           <t>PB-HM-39.1</t>
         </is>
       </c>
-      <c r="C45" s="4" t="inlineStr">
+      <c r="C45" s="13" t="inlineStr">
         <is>
           <t>Como usuario quiero descargar el archivo de logs JSONL una vez procesado haciendo clic en un botón para almacenarlo en mi equipo local.</t>
         </is>
       </c>
-      <c r="D45" s="4" t="inlineStr">
+      <c r="D45" s="13" t="inlineStr">
         <is>
           <t>- [ ] Implementar botón de exportación en la interfaz
 - [ ] Configurar manejo del Blob / archivo recibido
 - [ ] Notificar éxito o error de la descarga al usuario</t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>[Escenario 1:]
-- **Escenario 1:** Dado que tengo una solicitud en estado "Listo", Cuando presiono el icono de descarga, Entonces el navegador inicia la descarga del archivo .jsonl y el sistema me advierte que expirará en 7 días.
-[Escenario 2:]
-- **Escenario 2:** Dado que una solicitud lleva más de 7 días lista, Cuando intento verla, Entonces el sistema la marca como "Expirada" y el botón de descarga desaparece, informando que el archivo fue eliminado para liberar espacio.</t>
-        </is>
-      </c>
-      <c r="F45" s="3" t="inlineStr">
+      <c r="E45" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 1:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que tengo una solicitud en estado "Listo", Cuando presiono el icono de descarga, Entonces el navegador inicia la descarga del archivo .jsonl y el sistema me advierte que expirará en 7 días.
+- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 2:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que una solicitud lleva más de 7 días lista, Cuando intento verla, Entonces el sistema la marca como "Expirada" y el botón de descarga desaparece, informando que el archivo fue eliminado para liberar espacio.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F45" s="12" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G45" s="3" t="inlineStr">
-        <is>
-          <t>[Pendiente screenshot]</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="120" customHeight="1">
-      <c r="A46" s="3" t="inlineStr">
+      <c r="G45" s="12" t="inlineStr">
+        <is>
+          <t>[Pendiente screenshot]</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="120" customHeight="1" s="9">
+      <c r="A46" s="12" t="inlineStr">
         <is>
           <t>PB-HM-40</t>
         </is>
       </c>
-      <c r="B46" s="6" t="inlineStr">
+      <c r="B46" s="15" t="inlineStr">
         <is>
           <t>PB-HM-40.1</t>
         </is>
       </c>
-      <c r="C46" s="4" t="inlineStr">
+      <c r="C46" s="13" t="inlineStr">
         <is>
           <t>Como Analista quiero que las solicitudes de descarga de logs masivos (&gt;50,000 registros) queden "Pendientes" y envíen una alerta al Administrador vía Telegram para obtener aprobación y evitar abusos del sistema.</t>
         </is>
       </c>
-      <c r="D46" s="4" t="inlineStr">
+      <c r="D46" s="13" t="inlineStr">
         <is>
           <t>- [ ] Diseñar e implementar el componente UI necesario
 - [ ] Establecer lógica de estado (React hooks) y validaciones
 - [ ] Conectar la interfaz con la API Backend correspondiente</t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t>[Escenario 1:]
-- **Escenario 1:** Dado que configuro una solicitud de logs que abarcará 75,000 eventos, Cuando hago clic en "Procesar", Entonces la UI me avisa que requiere aprobación manual y el estado inicial es "Pendiente de Aprobación".
-[Escenario 2:]
-- **Escenario 2:** Dado que la solicitud supera el umbral crítico, Cuando se registra en base de datos, Entonces el backend despacha instantáneamente un webhook o mensaje al bot de Telegram del Administrador informando de los detalles de la solicitud y botones interactivos.</t>
-        </is>
-      </c>
-      <c r="F46" s="3" t="inlineStr">
+      <c r="E46" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 1:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que configuro una solicitud de logs que abarcará 75,000 eventos, Cuando hago clic en "Procesar", Entonces la UI me avisa que requiere aprobación manual y el estado inicial es "Pendiente de Aprobación".
+- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 2:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que la solicitud supera el umbral crítico, Cuando se registra en base de datos, Entonces el backend despacha instantáneamente un webhook o mensaje al bot de Telegram del Administrador informando de los detalles de la solicitud y botones interactivos.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F46" s="12" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="G46" s="3" t="inlineStr">
-        <is>
-          <t>[Pendiente screenshot]</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="120" customHeight="1">
-      <c r="A47" s="3" t="inlineStr">
+      <c r="G46" s="12" t="inlineStr">
+        <is>
+          <t>[Pendiente screenshot]</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="120" customHeight="1" s="9">
+      <c r="A47" s="12" t="inlineStr">
         <is>
           <t>PB-HM-41</t>
         </is>
       </c>
-      <c r="B47" s="6" t="inlineStr">
+      <c r="B47" s="15" t="inlineStr">
         <is>
           <t>PB-HM-41.1</t>
         </is>
       </c>
-      <c r="C47" s="4" t="inlineStr">
+      <c r="C47" s="13" t="inlineStr">
         <is>
           <t>Como Administrador quiero poder aprobar o rechazar desde Telegram (mediante el Bot interactivo) las descargas masivas de logs para tener control inmediato sin necesidad de entrar a la plataforma web.</t>
         </is>
       </c>
-      <c r="D47" s="4" t="inlineStr">
+      <c r="D47" s="13" t="inlineStr">
         <is>
           <t>- [ ] Diseñar e implementar el componente UI necesario
 - [ ] Establecer lógica de estado (React hooks) y validaciones
 - [ ] Conectar la interfaz con la API Backend correspondiente</t>
         </is>
       </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>[Escenario 1:]
-- **Escenario 1:** Dado que recibo el mensaje de alerta en Telegram, Cuando presiono el botón "Aprobar", Entonces el backend valida mi cuenta de Telegram, marca la solicitud como "Aprobada" y encola la generación asíncrona del archivo JSONL.
-[Escenario 2:]
-- **Escenario 2:** Dado que determino que la petición es sospechosa o muy costosa computacionalmente, Cuando presiono "Rechazar" en Telegram, Entonces el estado en el frontend cambia a "Rechazada" y la descarga se bloquea.</t>
-        </is>
-      </c>
-      <c r="F47" s="3" t="inlineStr">
+      <c r="E47" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 1:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que recibo el mensaje de alerta en Telegram, Cuando presiono el botón "Aprobar", Entonces el backend valida mi cuenta de Telegram, marca la solicitud como "Aprobada" y encola la generación asíncrona del archivo JSONL.
+- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 2:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que determino que la petición es sospechosa o muy costosa computacionalmente, Cuando presiono "Rechazar" en Telegram, Entonces el estado en el frontend cambia a "Rechazada" y la descarga se bloquea.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F47" s="12" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="G47" s="3" t="inlineStr">
-        <is>
-          <t>[Pendiente screenshot]</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="120" customHeight="1">
-      <c r="A48" s="3" t="inlineStr">
+      <c r="G47" s="12" t="inlineStr">
+        <is>
+          <t>[Pendiente screenshot]</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="120" customHeight="1" s="9">
+      <c r="A48" s="12" t="inlineStr">
         <is>
           <t>PB-HM-42</t>
         </is>
       </c>
-      <c r="B48" s="6" t="inlineStr">
+      <c r="B48" s="15" t="inlineStr">
         <is>
           <t>PB-HM-42.1</t>
         </is>
       </c>
-      <c r="C48" s="4" t="inlineStr">
+      <c r="C48" s="13" t="inlineStr">
         <is>
           <t>Como Analista quiero generar client-side un Diccionario de Datos en PDF con el esquema de campos Wazuh para tener documentación estandarizada lista para presentar o para entrenar modelos.</t>
         </is>
       </c>
-      <c r="D48" s="4" t="inlineStr">
+      <c r="D48" s="13" t="inlineStr">
         <is>
           <t>- [ ] Diseñar e implementar el componente UI necesario
 - [ ] Establecer lógica de estado (React hooks) y validaciones
 - [ ] Conectar la interfaz con la API Backend correspondiente</t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr">
-        <is>
-          <t>[Escenario 1:]
-- **Escenario 1:** Dado que estoy en la vista de Logs, Cuando hago clic en "Generar Diccionario PDF", Entonces la aplicación web (React) construye en local el documento utilizando jsPDF + AutoTable y lanza la descarga de forma rápida.
-[Escenario 2:]
-- **Escenario 2:** Dado que abro el PDF descargado, Cuando reviso el contenido, Entonces el documento incluye logotipo de HoneyMetrics, marca de tiempo de la generación, y una tabla describiendo el atributo, tipo de dato y descripción del modelo Wazuh.</t>
-        </is>
-      </c>
-      <c r="F48" s="3" t="inlineStr">
+      <c r="E48" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 1:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que estoy en la vista de Logs, Cuando hago clic en "Generar Diccionario PDF", Entonces la aplicación web (React) construye en local el documento utilizando jsPDF + AutoTable y lanza la descarga de forma rápida.
+- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 2:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que abro el PDF descargado, Cuando reviso el contenido, Entonces el documento incluye logotipo de HoneyMetrics, marca de tiempo de la generación, y una tabla describiendo el atributo, tipo de dato y descripción del modelo Wazuh.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F48" s="12" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G48" s="3" t="inlineStr">
-        <is>
-          <t>[Pendiente screenshot]</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="120" customHeight="1">
-      <c r="A49" s="3" t="inlineStr">
+      <c r="G48" s="12" t="inlineStr">
+        <is>
+          <t>[Pendiente screenshot]</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="120" customHeight="1" s="9">
+      <c r="A49" s="12" t="inlineStr">
         <is>
           <t>PB-HM-43</t>
         </is>
       </c>
-      <c r="B49" s="6" t="inlineStr">
+      <c r="B49" s="15" t="inlineStr">
         <is>
           <t>PB-HM-43.1</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
+      <c r="C49" s="13" t="inlineStr">
         <is>
           <t>Como usuario quiero generar informes ejecutivos en CSV o Excel de manera asíncrona, con barra de progreso, para poder consolidar el resumen gerencial de incidentes de un periodo dado.</t>
         </is>
       </c>
-      <c r="D49" s="4" t="inlineStr">
+      <c r="D49" s="13" t="inlineStr">
         <is>
           <t>- [ ] Diseñar e implementar el componente UI necesario
 - [ ] Establecer lógica de estado (React hooks) y validaciones
 - [ ] Conectar la interfaz con la API Backend correspondiente</t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr">
-        <is>
-          <t>[Escenario 1:]
-- **Escenario 1:** Dado que selecciono un informe de tipo "Ejecutivo", Cuando pulso en "Generar Reporte", Entonces se muestra una barra de progreso que consulta el estado asíncrono y, al finalizar, me entrega el .xlsx listo.
-[Escenario 2:]
-- **Escenario 2:** Dado que la solicitud del reporte implica un archivo extremadamente pesado, Cuando el servidor finaliza la construcción, Entonces el peso final no debe superar el límite duro configurado de 50 MB, informando en caso de truncamiento.</t>
-        </is>
-      </c>
-      <c r="F49" s="3" t="inlineStr">
+      <c r="E49" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 1:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que selecciono un informe de tipo "Ejecutivo", Cuando pulso en "Generar Reporte", Entonces se muestra una barra de progreso que consulta el estado asíncrono y, al finalizar, me entrega el .xlsx listo.
+- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 2:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que la solicitud del reporte implica un archivo extremadamente pesado, Cuando el servidor finaliza la construcción, Entonces el peso final no debe superar el límite duro configurado de 50 MB, informando en caso de truncamiento.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F49" s="12" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="G49" s="3" t="inlineStr">
-        <is>
-          <t>[Pendiente screenshot]</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="120" customHeight="1">
-      <c r="A50" s="3" t="inlineStr">
+      <c r="G49" s="12" t="inlineStr">
+        <is>
+          <t>[Pendiente screenshot]</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="120" customHeight="1" s="9">
+      <c r="A50" s="12" t="inlineStr">
         <is>
           <t>PB-HM-44</t>
         </is>
       </c>
-      <c r="B50" s="6" t="inlineStr">
+      <c r="B50" s="15" t="inlineStr">
         <is>
           <t>PB-HM-44.1</t>
         </is>
       </c>
-      <c r="C50" s="4" t="inlineStr">
+      <c r="C50" s="13" t="inlineStr">
         <is>
           <t>Como Consultor quiero recibir alertas emergentes en pantalla cada vez que el sistema detecte anomalías críticas (ej. pico &gt;300%) para poder actuar inmediatamente frente a ráfagas de ataques.</t>
         </is>
       </c>
-      <c r="D50" s="4" t="inlineStr">
+      <c r="D50" s="13" t="inlineStr">
         <is>
           <t>- [ ] Diseñar e implementar el componente UI necesario
 - [ ] Establecer lógica de estado (React hooks) y validaciones
 - [ ] Conectar la interfaz con la API Backend correspondiente</t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>[Escenario 1:]
-- **Escenario 1:** Dado que el backend identifica un pico anómalo de severidad máxima, Cuando el frontend recibe el evento (via WebSocket/SSE), Entonces lanza un pop-up rojo persistente en mi pantalla con resumen y los botones "Ver Detalle" y "Descartar".
-[Escenario 2:]
-- **Escenario 2:** Dado que hay múltiples anomalías sucesivas, Cuando el sistema lanza alertas, Entonces se aplica una política de "Debounce" que asegura que no haya más de un pop-up crítico cada 30 segundos para evitar saturación de la interfaz (alert fatigue).</t>
-        </is>
-      </c>
-      <c r="F50" s="3" t="inlineStr">
+      <c r="E50" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 1:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que el backend identifica un pico anómalo de severidad máxima, Cuando el frontend recibe el evento (via WebSocket/SSE), Entonces lanza un pop-up rojo persistente en mi pantalla con resumen y los botones "Ver Detalle" y "Descartar".
+- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 2:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que hay múltiples anomalías sucesivas, Cuando el sistema lanza alertas, Entonces se aplica una política de "Debounce" que asegura que no haya más de un pop-up crítico cada 30 segundos para evitar saturación de la interfaz (alert fatigue).</t>
+          </r>
+        </is>
+      </c>
+      <c r="F50" s="12" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="G50" s="3" t="inlineStr">
-        <is>
-          <t>[Pendiente screenshot]</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="120" customHeight="1">
-      <c r="A51" s="3" t="inlineStr">
+      <c r="G50" s="12" t="inlineStr">
+        <is>
+          <t>[Pendiente screenshot]</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="120" customHeight="1" s="9">
+      <c r="A51" s="12" t="inlineStr">
         <is>
           <t>PB-HM-45</t>
         </is>
       </c>
-      <c r="B51" s="6" t="inlineStr">
+      <c r="B51" s="15" t="inlineStr">
         <is>
           <t>PB-HM-45.1</t>
         </is>
       </c>
-      <c r="C51" s="4" t="inlineStr">
+      <c r="C51" s="13" t="inlineStr">
         <is>
           <t>Como Consultor quiero tener un panel lateral con el historial de alertas críticas recibidas en las últimas 24 horas para revisar eventos que pude haber descartado o ignorado rápidamente.</t>
         </is>
       </c>
-      <c r="D51" s="4" t="inlineStr">
+      <c r="D51" s="13" t="inlineStr">
         <is>
           <t>- [ ] Diseñar e implementar el componente UI necesario
 - [ ] Establecer lógica de estado (React hooks) y validaciones
 - [ ] Conectar la interfaz con la API Backend correspondiente</t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>[Escenario 1:]
-- **Escenario 1:** Dado que abro el Drawer/Panel lateral de notificaciones, Cuando cargo la vista, Entonces veo la lista de anomalías del último día con estado claro (Atendida, Descartada, Ignorada).
-[Escenario 2:]
-- **Escenario 2:** Dado que busco una alerta del día anterior, Cuando han pasado más de 24 horas, Entonces dicha alerta ya no figura en el panel lateral de "alertas rápidas" (aunque siga registrada en base de datos).</t>
-        </is>
-      </c>
-      <c r="F51" s="3" t="inlineStr">
+      <c r="E51" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 1:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que abro el Drawer/Panel lateral de notificaciones, Cuando cargo la vista, Entonces veo la lista de anomalías del último día con estado claro (Atendida, Descartada, Ignorada).
+- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 2:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que busco una alerta del día anterior, Cuando han pasado más de 24 horas, Entonces dicha alerta ya no figura en el panel lateral de "alertas rápidas" (aunque siga registrada en base de datos).</t>
+          </r>
+        </is>
+      </c>
+      <c r="F51" s="12" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G51" s="3" t="inlineStr">
-        <is>
-          <t>[Pendiente screenshot]</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="120" customHeight="1">
-      <c r="A52" s="3" t="inlineStr">
+      <c r="G51" s="12" t="inlineStr">
+        <is>
+          <t>[Pendiente screenshot]</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="120" customHeight="1" s="9">
+      <c r="A52" s="12" t="inlineStr">
         <is>
           <t>PB-HM-46</t>
         </is>
       </c>
-      <c r="B52" s="6" t="inlineStr">
+      <c r="B52" s="15" t="inlineStr">
         <is>
           <t>PB-HM-46.1</t>
         </is>
       </c>
-      <c r="C52" s="4" t="inlineStr">
+      <c r="C52" s="13" t="inlineStr">
         <is>
           <t>Como Consultor quiero hacer clic en "Ver Detalle" de una alerta para acceder a la radiografía completa del evento y tomar decisiones operativas.</t>
         </is>
       </c>
-      <c r="D52" s="4" t="inlineStr">
+      <c r="D52" s="13" t="inlineStr">
         <is>
           <t>- [ ] Diseñar e implementar el componente UI necesario
 - [ ] Establecer lógica de estado (React hooks) y validaciones
 - [ ] Conectar la interfaz con la API Backend correspondiente</t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>[Escenario 1:]
-- **Escenario 1:** Dado que interactúo con una alerta crítica, Cuando presiono "Ver Detalle", Entonces se abre un modal con el historial de la IP, gráfico temporal y tabla de los eventos específicos involucrados.
-[Escenario 2:]
-- **Escenario 2:** Dado que analizo el detalle del evento en el modal, Cuando observo la parte inferior, Entonces el sistema me expone los botones rápidos "Agregar a Lista Negra" y "Marcar como Falso Positivo".</t>
-        </is>
-      </c>
-      <c r="F52" s="3" t="inlineStr">
+      <c r="E52" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 1:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que interactúo con una alerta crítica, Cuando presiono "Ver Detalle", Entonces se abre un modal con el historial de la IP, gráfico temporal y tabla de los eventos específicos involucrados.
+- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 2:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que analizo el detalle del evento en el modal, Cuando observo la parte inferior, Entonces el sistema me expone los botones rápidos "Agregar a Lista Negra" y "Marcar como Falso Positivo".</t>
+          </r>
+        </is>
+      </c>
+      <c r="F52" s="12" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G52" s="3" t="inlineStr">
-        <is>
-          <t>[Pendiente screenshot]</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="120" customHeight="1">
-      <c r="A53" s="3" t="inlineStr">
+      <c r="G52" s="12" t="inlineStr">
+        <is>
+          <t>[Pendiente screenshot]</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="120" customHeight="1" s="9">
+      <c r="A53" s="12" t="inlineStr">
         <is>
           <t>PB-HM-47</t>
         </is>
       </c>
-      <c r="B53" s="6" t="inlineStr">
+      <c r="B53" s="15" t="inlineStr">
         <is>
           <t>PB-HM-47.1</t>
         </is>
       </c>
-      <c r="C53" s="4" t="inlineStr">
+      <c r="C53" s="13" t="inlineStr">
         <is>
           <t>Como Consultor quiero marcar una alerta como Falso Positivo desde su panel de detalle para que el modelo de IA se reentrene y deje de catalogar tráfico benigno similar como ataque.</t>
         </is>
       </c>
-      <c r="D53" s="4" t="inlineStr">
+      <c r="D53" s="13" t="inlineStr">
         <is>
           <t>- [ ] Diseñar e implementar el componente UI necesario
 - [ ] Establecer lógica de estado (React hooks) y validaciones
 - [ ] Conectar la interfaz con la API Backend correspondiente</t>
         </is>
       </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>[Escenario 1:]
-- **Escenario 1:** Dado que verifico que la IP de la alerta es un escáner interno autorizado, Cuando hago clic en "Marcar como Falso Positivo", Entonces el sistema pide confirmación y actualiza el estado de la alerta.
-[Escenario 2:]
-- **Escenario 2:** Dado que se marca como Falso Positivo, Cuando la base de datos se actualiza, Entonces el registro es etiquetado internamente (flag) de manera que se excluya de métricas de riesgo y se envíe a la cola de "Dataset para Reentrenamiento".</t>
-        </is>
-      </c>
-      <c r="F53" s="3" t="inlineStr">
+      <c r="E53" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 1:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que verifico que la IP de la alerta es un escáner interno autorizado, Cuando hago clic en "Marcar como Falso Positivo", Entonces el sistema pide confirmación y actualiza el estado de la alerta.
+- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 2:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que se marca como Falso Positivo, Cuando la base de datos se actualiza, Entonces el registro es etiquetado internamente (flag) de manera que se excluya de métricas de riesgo y se envíe a la cola de "Dataset para Reentrenamiento".</t>
+          </r>
+        </is>
+      </c>
+      <c r="F53" s="12" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G53" s="3" t="inlineStr">
-        <is>
-          <t>[Pendiente screenshot]</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="120" customHeight="1">
-      <c r="A54" s="3" t="inlineStr">
+      <c r="G53" s="12" t="inlineStr">
+        <is>
+          <t>[Pendiente screenshot]</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="120" customHeight="1" s="9">
+      <c r="A54" s="12" t="inlineStr">
         <is>
           <t>PB-HM-62</t>
         </is>
       </c>
-      <c r="B54" s="6" t="inlineStr">
+      <c r="B54" s="15" t="inlineStr">
         <is>
           <t>PB-HM-62.1</t>
         </is>
       </c>
-      <c r="C54" s="4" t="inlineStr">
+      <c r="C54" s="13" t="inlineStr">
         <is>
           <t>Como Analista quiero que el sistema me sugiera el bloqueo de rangos CIDR (/24) tras identificar subredes (Botnets) que atacan coordinadamente para mitigar ataques distribuidos masivos más eficientemente.</t>
         </is>
       </c>
-      <c r="D54" s="4" t="inlineStr">
+      <c r="D54" s="13" t="inlineStr">
         <is>
           <t>- [ ] Diseñar e implementar el componente UI necesario
 - [ ] Establecer lógica de estado (React hooks) y validaciones
 - [ ] Conectar la interfaz con la API Backend correspondiente</t>
         </is>
       </c>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>[Escenario 1:]
-- **Escenario 1:** Dado que el sistema analiza tráfico en tiempo real, Cuando detecta múltiples IPs de la misma subred (ej. 192.168.1.x/24) atacando el honeypot simultáneamente, Entonces genera una recomendación visual de bloqueo CIDR.
-[Escenario 2:]
-- **Escenario 2:** Dado que consulto la sugerencia, Cuando reviso el detalle, Entonces veo el volumen consolidado del bloque completo en lugar de ver registros aislados IP por IP.</t>
-        </is>
-      </c>
-      <c r="F54" s="3" t="inlineStr">
+      <c r="E54" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 1:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que el sistema analiza tráfico en tiempo real, Cuando detecta múltiples IPs de la misma subred (ej. 192.168.1.x/24) atacando el honeypot simultáneamente, Entonces genera una recomendación visual de bloqueo CIDR.
+- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 2:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que consulto la sugerencia, Cuando reviso el detalle, Entonces veo el volumen consolidado del bloque completo en lugar de ver registros aislados IP por IP.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F54" s="12" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G54" s="3" t="inlineStr">
-        <is>
-          <t>[Pendiente screenshot]</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="120" customHeight="1">
-      <c r="A55" s="3" t="inlineStr">
+      <c r="G54" s="12" t="inlineStr">
+        <is>
+          <t>[Pendiente screenshot]</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="120" customHeight="1" s="9">
+      <c r="A55" s="12" t="inlineStr">
         <is>
           <t>PB-HM-63</t>
         </is>
       </c>
-      <c r="B55" s="6" t="inlineStr">
+      <c r="B55" s="15" t="inlineStr">
         <is>
           <t>PB-HM-63.1</t>
         </is>
       </c>
-      <c r="C55" s="4" t="inlineStr">
+      <c r="C55" s="13" t="inlineStr">
         <is>
           <t>Como Analista quiero un clasificador de comportamiento que distinga entre Bots automatizados y Humanos manuales utilizando su velocidad de eventos para priorizar amenazas dirigidas.</t>
         </is>
       </c>
-      <c r="D55" s="4" t="inlineStr">
+      <c r="D55" s="13" t="inlineStr">
         <is>
           <t>- [ ] Diseñar e implementar el componente UI necesario
 - [ ] Establecer lógica de estado (React hooks) y validaciones
 - [ ] Conectar la interfaz con la API Backend correspondiente</t>
         </is>
       </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>[Escenario 1:]
-- **Escenario 1:** Dado que una IP dispara más de 100 eventos maliciosos por hora en el honeypot, Cuando es analizada por el sistema, Entonces se etiqueta automáticamente como "Bot".
-[Escenario 2:]
-- **Escenario 2:** Dado que una IP intenta accesos espaciados y lentos, Cuando la velocidad es inferior a los umbrales de ataque automatizado, Entonces el sistema la etiqueta como "Humano" y aumenta su prioridad en el dashboard de revisiones manuales.</t>
-        </is>
-      </c>
-      <c r="F55" s="3" t="inlineStr">
+      <c r="E55" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 1:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que una IP dispara más de 100 eventos maliciosos por hora en el honeypot, Cuando es analizada por el sistema, Entonces se etiqueta automáticamente como "Bot".
+- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 2:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que una IP intenta accesos espaciados y lentos, Cuando la velocidad es inferior a los umbrales de ataque automatizado, Entonces el sistema la etiqueta como "Humano" y aumenta su prioridad en el dashboard de revisiones manuales.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F55" s="12" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G55" s="3" t="inlineStr">
-        <is>
-          <t>[Pendiente screenshot]</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="120" customHeight="1">
-      <c r="A56" s="3" t="inlineStr">
+      <c r="G55" s="12" t="inlineStr">
+        <is>
+          <t>[Pendiente screenshot]</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="120" customHeight="1" s="9">
+      <c r="A56" s="12" t="inlineStr">
         <is>
           <t>PB-HM-70</t>
         </is>
       </c>
-      <c r="B56" s="6" t="inlineStr">
+      <c r="B56" s="15" t="inlineStr">
         <is>
           <t>PB-HM-70.1</t>
         </is>
       </c>
-      <c r="C56" s="4" t="inlineStr">
+      <c r="C56" s="13" t="inlineStr">
         <is>
           <t>Como usuario quiero visualizar un Heatmap de Riesgo Predictivo (días vs horas) para anticipar los horarios de mayor exposición y preparar defensas o ventanas de mantenimiento.</t>
         </is>
       </c>
-      <c r="D56" s="4" t="inlineStr">
+      <c r="D56" s="13" t="inlineStr">
         <is>
           <t>- [ ] Preparar componente contenedor de la visualización
 - [ ] Integrar librería Plotly.js / Chart.js
 - [ ] Conectar endpoint para inyección dinámica de datos</t>
         </is>
       </c>
-      <c r="E56" s="4" t="inlineStr">
-        <is>
-          <t>[Escenario 1:]
-- **Escenario 1:** Dado que ingreso al dashboard, Cuando visualizo la sección del Heatmap Predictivo, Entonces veo una cuadrícula que compara los 7 días de la semana contra las 24 horas del día.
-[Escenario 2:]
-- **Escenario 2:** Dado que el heatmap carga la historia, Cuando observo celdas coloreadas de rojo oscuro (Ej. Lunes de 11:00 a 12:00 UTC), Entonces interpreto que, según el patrón histórico, ese bloque de tiempo presentará el mayor volumen probable de ataques en el futuro.</t>
-        </is>
-      </c>
-      <c r="F56" s="3" t="inlineStr">
+      <c r="E56" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 1:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que ingreso al dashboard, Cuando visualizo la sección del Heatmap Predictivo, Entonces veo una cuadrícula que compara los 7 días de la semana contra las 24 horas del día.
+- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 2:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que el heatmap carga la historia, Cuando observo celdas coloreadas de rojo oscuro (Ej. Lunes de 11:00 a 12:00 UTC), Entonces interpreto que, según el patrón histórico, ese bloque de tiempo presentará el mayor volumen probable de ataques en el futuro.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F56" s="12" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G56" s="3" t="inlineStr">
-        <is>
-          <t>[Pendiente screenshot]</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="120" customHeight="1">
-      <c r="A57" s="3" t="inlineStr">
+      <c r="G56" s="12" t="inlineStr">
+        <is>
+          <t>[Pendiente screenshot]</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="120" customHeight="1" s="9">
+      <c r="A57" s="12" t="inlineStr">
         <is>
           <t>PB-HM-48</t>
         </is>
       </c>
-      <c r="B57" s="6" t="inlineStr">
+      <c r="B57" s="15" t="inlineStr">
         <is>
           <t>PB-HM-48.1</t>
         </is>
       </c>
-      <c r="C57" s="4" t="inlineStr">
+      <c r="C57" s="13" t="inlineStr">
         <is>
           <t>Como Analista quiero visualizar el resumen de rendimiento de algoritmos de ML en un dashboard técnico para evaluar de manera integral la efectividad del modelo de clasificación de amenazas vigente.</t>
         </is>
       </c>
-      <c r="D57" s="4" t="inlineStr">
+      <c r="D57" s="13" t="inlineStr">
         <is>
           <t>- [ ] Preparar componente contenedor de la visualización
 - [ ] Integrar librería Plotly.js / Chart.js
 - [ ] Conectar endpoint para inyección dinámica de datos</t>
         </is>
       </c>
-      <c r="E57" s="4" t="inlineStr">
-        <is>
-          <t>[Escenario 1:]
-- **Escenario 1:** Dado que accedo al dashboard técnico de ML, Cuando visualizo las métricas principales, Entonces veo los KPIs actualizados de Accuracy, Precision, Recall, F1-Score y ROC AUC.
-[Escenario 2:]
-- **Escenario 2:** Dado que necesito analizar la capacidad de discriminación del modelo, Cuando examino el dashboard en detalle, Entonces visualizo gráficamente la curva ROC y los promedios de tiempo de ejecución del algoritmo.</t>
-        </is>
-      </c>
-      <c r="F57" s="3" t="inlineStr">
+      <c r="E57" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 1:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que accedo al dashboard técnico de ML, Cuando visualizo las métricas principales, Entonces veo los KPIs actualizados de Accuracy, Precision, Recall, F1-Score y ROC AUC.
+- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 2:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que necesito analizar la capacidad de discriminación del modelo, Cuando examino el dashboard en detalle, Entonces visualizo gráficamente la curva ROC y los promedios de tiempo de ejecución del algoritmo.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F57" s="12" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="G57" s="3" t="inlineStr">
-        <is>
-          <t>[Pendiente screenshot]</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="120" customHeight="1">
-      <c r="A58" s="3" t="inlineStr">
+      <c r="G57" s="12" t="inlineStr">
+        <is>
+          <t>[Pendiente screenshot]</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="120" customHeight="1" s="9">
+      <c r="A58" s="12" t="inlineStr">
         <is>
           <t>PB-HM-49</t>
         </is>
       </c>
-      <c r="B58" s="6" t="inlineStr">
+      <c r="B58" s="15" t="inlineStr">
         <is>
           <t>PB-HM-49.1</t>
         </is>
       </c>
-      <c r="C58" s="4" t="inlineStr">
+      <c r="C58" s="13" t="inlineStr">
         <is>
           <t>Como Analista quiero comparar el rendimiento entre múltiples versiones del modelo de IA para identificar cuál de los modelos iterados es más efectivo frente a los patrones de ataque recientes.</t>
         </is>
       </c>
-      <c r="D58" s="4" t="inlineStr">
+      <c r="D58" s="13" t="inlineStr">
         <is>
           <t>- [ ] Crear componente de tabla interactiva (paginación/filtros)
 - [ ] Implementar petición GET para listar registros
 - [ ] Validar renderizado condicional de acciones según rol</t>
         </is>
       </c>
-      <c r="E58" s="4" t="inlineStr">
-        <is>
-          <t>[Escenario 1:]
-- **Escenario 1:** Dado que existen múltiples modelos entrenados, Cuando selecciono dos o más versiones en el menú, Entonces visualizo un gráfico de barras comparativo que contrapone sus métricas de rendimiento.
-[Escenario 2:]
-- **Escenario 2:** Dado que estoy viendo la gráfica comparativa, Cuando deselecciono una de las versiones, Entonces el gráfico se actualiza en tiempo real mostrando únicamente los modelos restantes.</t>
-        </is>
-      </c>
-      <c r="F58" s="3" t="inlineStr">
+      <c r="E58" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 1:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que existen múltiples modelos entrenados, Cuando selecciono dos o más versiones en el menú, Entonces visualizo un gráfico de barras comparativo que contrapone sus métricas de rendimiento.
+- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 2:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que estoy viendo la gráfica comparativa, Cuando deselecciono una de las versiones, Entonces el gráfico se actualiza en tiempo real mostrando únicamente los modelos restantes.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F58" s="12" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G58" s="3" t="inlineStr">
-        <is>
-          <t>[Pendiente screenshot]</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="120" customHeight="1">
-      <c r="A59" s="3" t="inlineStr">
+      <c r="G58" s="12" t="inlineStr">
+        <is>
+          <t>[Pendiente screenshot]</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="120" customHeight="1" s="9">
+      <c r="A59" s="12" t="inlineStr">
         <is>
           <t>PB-HM-50</t>
         </is>
       </c>
-      <c r="B59" s="6" t="inlineStr">
+      <c r="B59" s="15" t="inlineStr">
         <is>
           <t>PB-HM-50.1</t>
         </is>
       </c>
-      <c r="C59" s="4" t="inlineStr">
+      <c r="C59" s="13" t="inlineStr">
         <is>
           <t>Como Analista quiero exportar las métricas de rendimiento de algoritmos en formato CSV para integrarlas en informes externos, reportes académicos y llevar un control histórico detallado.</t>
         </is>
       </c>
-      <c r="D59" s="4" t="inlineStr">
+      <c r="D59" s="13" t="inlineStr">
         <is>
           <t>- [ ] Implementar botón de exportación en la interfaz
 - [ ] Configurar manejo del Blob / archivo recibido
 - [ ] Notificar éxito o error de la descarga al usuario</t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>[Escenario 1:]
-- **Escenario 1:** Dado que visualizo el panel con el historial de rendimiento de los modelos, Cuando hago clic en el botón de exportar, Entonces se descarga localmente un archivo CSV con todas las métricas en crudo.
-[Escenario 2:]
-- **Escenario 2:** Dado que aún no hay datos ni métricas de ML calculadas, Cuando visualizo el panel de exportación, Entonces el botón correspondiente se encuentra deshabilitado.</t>
-        </is>
-      </c>
-      <c r="F59" s="3" t="inlineStr">
+      <c r="E59" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 1:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que visualizo el panel con el historial de rendimiento de los modelos, Cuando hago clic en el botón de exportar, Entonces se descarga localmente un archivo CSV con todas las métricas en crudo.
+- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 2:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que aún no hay datos ni métricas de ML calculadas, Cuando visualizo el panel de exportación, Entonces el botón correspondiente se encuentra deshabilitado.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F59" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G59" s="3" t="inlineStr">
-        <is>
-          <t>[Pendiente screenshot]</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="120" customHeight="1">
-      <c r="A60" s="3" t="inlineStr">
+      <c r="G59" s="12" t="inlineStr">
+        <is>
+          <t>[Pendiente screenshot]</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="120" customHeight="1" s="9">
+      <c r="A60" s="12" t="inlineStr">
         <is>
           <t>PB-HM-51</t>
         </is>
       </c>
-      <c r="B60" s="6" t="inlineStr">
+      <c r="B60" s="15" t="inlineStr">
         <is>
           <t>PB-HM-51.1</t>
         </is>
       </c>
-      <c r="C60" s="4" t="inlineStr">
+      <c r="C60" s="13" t="inlineStr">
         <is>
           <t>Como Analista quiero guardar filtros predeterminados de la Lista Negra para reutilizarlos de forma ágil y facilitar la preparación de nuevos datasets de entrenamiento.</t>
         </is>
       </c>
-      <c r="D60" s="4" t="inlineStr">
+      <c r="D60" s="13" t="inlineStr">
         <is>
           <t>- [ ] Crear componente de tabla interactiva (paginación/filtros)
 - [ ] Implementar petición GET para listar registros
 - [ ] Validar renderizado condicional de acciones según rol</t>
         </is>
       </c>
-      <c r="E60" s="4" t="inlineStr">
-        <is>
-          <t>[Escenario 1:]
-- **Escenario 1:** Dado que apliqué una configuración específica de filtros a la Lista Negra, Cuando hago clic en "Guardar Filtros" y le asigno un nombre único, Entonces esa combinación queda guardada en mi perfil de usuario.
-[Escenario 2:]
-- **Escenario 2:** Dado que quiero guardar una nueva combinación, Cuando intento hacerlo y ya he alcanzado el límite de 10 filtros, Entonces el sistema me muestra un mensaje de advertencia indicando que debo eliminar uno existente.</t>
-        </is>
-      </c>
-      <c r="F60" s="3" t="inlineStr">
+      <c r="E60" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 1:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que apliqué una configuración específica de filtros a la Lista Negra, Cuando hago clic en "Guardar Filtros" y le asigno un nombre único, Entonces esa combinación queda guardada en mi perfil de usuario.
+- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 2:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que quiero guardar una nueva combinación, Cuando intento hacerlo y ya he alcanzado el límite de 10 filtros, Entonces el sistema me muestra un mensaje de advertencia indicando que debo eliminar uno existente.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F60" s="12" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G60" s="3" t="inlineStr">
-        <is>
-          <t>[Pendiente screenshot]</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="120" customHeight="1">
-      <c r="A61" s="3" t="inlineStr">
+      <c r="G60" s="12" t="inlineStr">
+        <is>
+          <t>[Pendiente screenshot]</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="120" customHeight="1" s="9">
+      <c r="A61" s="12" t="inlineStr">
         <is>
           <t>PB-HM-52</t>
         </is>
       </c>
-      <c r="B61" s="6" t="inlineStr">
+      <c r="B61" s="15" t="inlineStr">
         <is>
           <t>PB-HM-52.1</t>
         </is>
       </c>
-      <c r="C61" s="4" t="inlineStr">
+      <c r="C61" s="13" t="inlineStr">
         <is>
           <t>Como Analista quiero consultar mis filtros guardados de la Lista Negra para aplicar rápidamente configuraciones complejas sobre la tabla de amenazas con un solo clic.</t>
         </is>
       </c>
-      <c r="D61" s="4" t="inlineStr">
+      <c r="D61" s="13" t="inlineStr">
         <is>
           <t>- [ ] Crear componente de tabla interactiva (paginación/filtros)
 - [ ] Implementar petición GET para listar registros
 - [ ] Validar renderizado condicional de acciones según rol</t>
         </is>
       </c>
-      <c r="E61" s="4" t="inlineStr">
-        <is>
-          <t>[Escenario 1:]
-- **Escenario 1:** Dado que abro el panel de la Lista Negra, Cuando despliego el menú de filtros rápidos, Entonces visualizo la lista con los nombres de todos mis filtros previamente almacenados.
-[Escenario 2:]
-- **Escenario 2:** Dado que he localizado un filtro guardado específico en el menú, Cuando hago clic sobre su nombre, Entonces la tabla se recarga aplicando inmediatamente todos los parámetros de filtrado correspondientes.</t>
-        </is>
-      </c>
-      <c r="F61" s="3" t="inlineStr">
+      <c r="E61" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 1:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que abro el panel de la Lista Negra, Cuando despliego el menú de filtros rápidos, Entonces visualizo la lista con los nombres de todos mis filtros previamente almacenados.
+- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 2:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que he localizado un filtro guardado específico en el menú, Cuando hago clic sobre su nombre, Entonces la tabla se recarga aplicando inmediatamente todos los parámetros de filtrado correspondientes.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F61" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G61" s="3" t="inlineStr">
-        <is>
-          <t>[Pendiente screenshot]</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="120" customHeight="1">
-      <c r="A62" s="3" t="inlineStr">
+      <c r="G61" s="12" t="inlineStr">
+        <is>
+          <t>[Pendiente screenshot]</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="120" customHeight="1" s="9">
+      <c r="A62" s="12" t="inlineStr">
         <is>
           <t>PB-HM-53</t>
         </is>
       </c>
-      <c r="B62" s="6" t="inlineStr">
+      <c r="B62" s="15" t="inlineStr">
         <is>
           <t>PB-HM-53.1</t>
         </is>
       </c>
-      <c r="C62" s="4" t="inlineStr">
+      <c r="C62" s="13" t="inlineStr">
         <is>
           <t>Como Analista quiero eliminar un filtro predeterminado guardado que ya no utilizo para mantener limpia mi lista de filtros y liberar espacio (slots) para configuraciones más recientes.</t>
         </is>
       </c>
-      <c r="D62" s="4" t="inlineStr">
+      <c r="D62" s="13" t="inlineStr">
         <is>
           <t>- [ ] Desarrollar formulario/modal para la acción
 - [ ] Validar permisos del rol en el frontend
 - [ ] Conectar endpoint CRUD y mostrar notificación de resultado</t>
         </is>
       </c>
-      <c r="E62" s="4" t="inlineStr">
-        <is>
-          <t>[Escenario 1:]
-- **Escenario 1:** Dado que reviso mi lista de filtros guardados, Cuando selecciono la opción de borrar sobre uno de ellos, Entonces el sistema despliega un mensaje pidiendo mi confirmación antes de proceder.
-[Escenario 2:]
-- **Escenario 2:** Dado que he confirmado la acción de borrado, Cuando la operación finaliza, Entonces el filtro desaparece de la vista y el contador de mis filtros disponibles se incrementa en uno.</t>
-        </is>
-      </c>
-      <c r="F62" s="3" t="inlineStr">
+      <c r="E62" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 1:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que reviso mi lista de filtros guardados, Cuando selecciono la opción de borrar sobre uno de ellos, Entonces el sistema despliega un mensaje pidiendo mi confirmación antes de proceder.
+- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 2:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que he confirmado la acción de borrado, Cuando la operación finaliza, Entonces el filtro desaparece de la vista y el contador de mis filtros disponibles se incrementa en uno.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F62" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G62" s="3" t="inlineStr">
-        <is>
-          <t>[Pendiente screenshot]</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="120" customHeight="1">
-      <c r="A63" s="3" t="inlineStr">
+      <c r="G62" s="12" t="inlineStr">
+        <is>
+          <t>[Pendiente screenshot]</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="120" customHeight="1" s="9">
+      <c r="A63" s="12" t="inlineStr">
         <is>
           <t>PB-HM-54</t>
         </is>
       </c>
-      <c r="B63" s="6" t="inlineStr">
+      <c r="B63" s="15" t="inlineStr">
         <is>
           <t>PB-HM-54.1</t>
         </is>
       </c>
-      <c r="C63" s="4" t="inlineStr">
+      <c r="C63" s="13" t="inlineStr">
         <is>
           <t>Como Administrador / Consultor quiero monitorear el estado de recursos del Honeypot (Orange Pi 5) en tiempo real para verificar si el equipo cuenta con la capacidad de hardware necesaria para seguir registrando amenazas.</t>
         </is>
       </c>
-      <c r="D63" s="4" t="inlineStr">
+      <c r="D63" s="13" t="inlineStr">
         <is>
           <t>- [ ] Diseñar e implementar el componente UI necesario
 - [ ] Establecer lógica de estado (React hooks) y validaciones
 - [ ] Conectar la interfaz con la API Backend correspondiente</t>
         </is>
       </c>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
-          <t>[Escenario 1:]
-- **Escenario 1:** Dado que ingreso a la vista de monitoreo del Honeypot, Cuando finaliza la carga inicial, Entonces veo los gráficos de rendimiento: CPU (gráfico de anillo), RAM (barras) y almacenamiento (tipo gauge).
-[Escenario 2:]
-- **Escenario 2:** Dado que mantengo activa la pestaña del dashboard de recursos, Cuando transcurren 60 segundos, Entonces el sistema sondea la telemetría y actualiza todos los gráficos dinámicamente sin recargar la página.</t>
-        </is>
-      </c>
-      <c r="F63" s="3" t="inlineStr">
+      <c r="E63" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 1:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que ingreso a la vista de monitoreo del Honeypot, Cuando finaliza la carga inicial, Entonces veo los gráficos de rendimiento: CPU (gráfico de anillo), RAM (barras) y almacenamiento (tipo gauge).
+- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 2:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que mantengo activa la pestaña del dashboard de recursos, Cuando transcurren 60 segundos, Entonces el sistema sondea la telemetría y actualiza todos los gráficos dinámicamente sin recargar la página.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F63" s="12" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="G63" s="3" t="inlineStr">
-        <is>
-          <t>[Pendiente screenshot]</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="120" customHeight="1">
-      <c r="A64" s="3" t="inlineStr">
+      <c r="G63" s="12" t="inlineStr">
+        <is>
+          <t>[Pendiente screenshot]</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="120" customHeight="1" s="9">
+      <c r="A64" s="12" t="inlineStr">
         <is>
           <t>PB-HM-55</t>
         </is>
       </c>
-      <c r="B64" s="6" t="inlineStr">
+      <c r="B64" s="15" t="inlineStr">
         <is>
           <t>PB-HM-55.1</t>
         </is>
       </c>
-      <c r="C64" s="4" t="inlineStr">
+      <c r="C64" s="13" t="inlineStr">
         <is>
           <t>Como Administrador / Consultor quiero alertar cuando el Honeypot pierde conectividad para estar al tanto de posibles caídas críticas del hardware o denegaciones de servicio y poder gestionar la reactivación rápida.</t>
         </is>
       </c>
-      <c r="D64" s="4" t="inlineStr">
+      <c r="D64" s="13" t="inlineStr">
         <is>
           <t>- [ ] Diseñar e implementar el componente UI necesario
 - [ ] Establecer lógica de estado (React hooks) y validaciones
 - [ ] Conectar la interfaz con la API Backend correspondiente</t>
         </is>
       </c>
-      <c r="E64" s="4" t="inlineStr">
-        <is>
-          <t>[Escenario 1:]
-- **Escenario 1:** Dado que el agente de telemetría del Honeypot dejó de enviar datos, Cuando el sistema cuenta 5 minutos sin recibir paquetes nuevos, Entonces muestra una alerta roja global indicando que se ha perdido la comunicación con la Orange Pi 5.
-[Escenario 2:]
-- **Escenario 2:** Dado que la alerta de desconexión está activa, Cuando el hardware recupera la conexión y se reanuda el envío de métricas al servidor, Entonces el sistema detecta los paquetes y oculta automáticamente la alerta.</t>
-        </is>
-      </c>
-      <c r="F64" s="3" t="inlineStr">
+      <c r="E64" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 1:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que el agente de telemetría del Honeypot dejó de enviar datos, Cuando el sistema cuenta 5 minutos sin recibir paquetes nuevos, Entonces muestra una alerta roja global indicando que se ha perdido la comunicación con la Orange Pi 5.
+- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 2:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que la alerta de desconexión está activa, Cuando el hardware recupera la conexión y se reanuda el envío de métricas al servidor, Entonces el sistema detecta los paquetes y oculta automáticamente la alerta.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F64" s="12" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G64" s="3" t="inlineStr">
-        <is>
-          <t>[Pendiente screenshot]</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="120" customHeight="1">
-      <c r="A65" s="3" t="inlineStr">
+      <c r="G64" s="12" t="inlineStr">
+        <is>
+          <t>[Pendiente screenshot]</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="120" customHeight="1" s="9">
+      <c r="A65" s="12" t="inlineStr">
         <is>
           <t>PB-HM-56</t>
         </is>
       </c>
-      <c r="B65" s="6" t="inlineStr">
+      <c r="B65" s="15" t="inlineStr">
         <is>
           <t>PB-HM-56.1</t>
         </is>
       </c>
-      <c r="C65" s="4" t="inlineStr">
+      <c r="C65" s="13" t="inlineStr">
         <is>
           <t>Como usuario quiero aplicar el cierre automático de sesión por inactividad tras 30 minutos para garantizar la seguridad de mi cuenta y evitar exposiciones en caso de dejar el equipo desatendido.</t>
         </is>
       </c>
-      <c r="D65" s="4" t="inlineStr">
+      <c r="D65" s="13" t="inlineStr">
         <is>
           <t>- [ ] Diseñar y maquetar formulario de interfaz en React
 - [ ] Configurar validación de entradas (Email/Password)
 - [ ] Integrar consumo del endpoint de autenticación</t>
         </is>
       </c>
-      <c r="E65" s="4" t="inlineStr">
-        <is>
-          <t>[Escenario 1:]
-- **Escenario 1:** Dado que me encuentro autenticado en el sistema, Cuando registro un periodo ininterrumpido de 30 minutos sin realizar interacciones (mouse/teclado), Entonces el sistema invalida mi token y me redirige forzosamente a la pantalla de Login.
-[Escenario 2:]
-- **Escenario 2:** Dado que llevo 25 minutos inactivo, Cuando realizo un movimiento del mouse o pulsación de tecla, Entonces el temporizador interno del sistema se resetea inmediatamente a 0, evitando el cierre de mi sesión.</t>
-        </is>
-      </c>
-      <c r="F65" s="3" t="inlineStr">
+      <c r="E65" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 1:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que me encuentro autenticado en el sistema, Cuando registro un periodo ininterrumpido de 30 minutos sin realizar interacciones (mouse/teclado), Entonces el sistema invalida mi token y me redirige forzosamente a la pantalla de Login.
+- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 2:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que llevo 25 minutos inactivo, Cuando realizo un movimiento del mouse o pulsación de tecla, Entonces el temporizador interno del sistema se resetea inmediatamente a 0, evitando el cierre de mi sesión.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F65" s="12" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G65" s="3" t="inlineStr">
-        <is>
-          <t>[Pendiente screenshot]</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="120" customHeight="1">
-      <c r="A66" s="3" t="inlineStr">
+      <c r="G65" s="12" t="inlineStr">
+        <is>
+          <t>[Pendiente screenshot]</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="120" customHeight="1" s="9">
+      <c r="A66" s="12" t="inlineStr">
         <is>
           <t>PB-HM-57</t>
         </is>
       </c>
-      <c r="B66" s="6" t="inlineStr">
+      <c r="B66" s="15" t="inlineStr">
         <is>
           <t>PB-HM-57.1</t>
         </is>
       </c>
-      <c r="C66" s="4" t="inlineStr">
+      <c r="C66" s="13" t="inlineStr">
         <is>
           <t>Como usuario quiero visualizar los mensajes de error del sistema en lenguaje natural (español) para entender los problemas o advertencias sin ser confundido por texto técnico incomprensible ni detalles del código fuente.</t>
         </is>
       </c>
-      <c r="D66" s="4" t="inlineStr">
+      <c r="D66" s="13" t="inlineStr">
         <is>
           <t>- [ ] Diseñar e implementar el componente UI necesario
 - [ ] Establecer lógica de estado (React hooks) y validaciones
 - [ ] Conectar la interfaz con la API Backend correspondiente</t>
         </is>
       </c>
-      <c r="E66" s="4" t="inlineStr">
-        <is>
-          <t>[Escenario 1:]
-- **Escenario 1:** Dado que introduzco datos inválidos en un formulario, Cuando envío la información, Entonces aparece una alerta en español que me dice exactamente qué debo corregir, utilizando colores amigables (ej. amarillo/naranja).
-[Escenario 2:]
-- **Escenario 2:** Dado que ocurre una falla interna (Status 500) en los servidores del backend, Cuando el frontend procesa la respuesta, Entonces despliega un mensaje rojo estándar tipo "Ha ocurrido un error inesperado, contacte soporte" sin mostrar trazas del código ni tecnologías implicadas.</t>
-        </is>
-      </c>
-      <c r="F66" s="3" t="inlineStr">
+      <c r="E66" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 1:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que introduzco datos inválidos en un formulario, Cuando envío la información, Entonces aparece una alerta en español que me dice exactamente qué debo corregir, utilizando colores amigables (ej. amarillo/naranja).
+- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 2:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que ocurre una falla interna (Status 500) en los servidores del backend, Cuando el frontend procesa la respuesta, Entonces despliega un mensaje rojo estándar tipo "Ha ocurrido un error inesperado, contacte soporte" sin mostrar trazas del código ni tecnologías implicadas.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F66" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G66" s="3" t="inlineStr">
-        <is>
-          <t>[Pendiente screenshot]</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="120" customHeight="1">
-      <c r="A67" s="3" t="inlineStr">
+      <c r="G66" s="12" t="inlineStr">
+        <is>
+          <t>[Pendiente screenshot]</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="120" customHeight="1" s="9">
+      <c r="A67" s="12" t="inlineStr">
         <is>
           <t>PB-HM-58</t>
         </is>
       </c>
-      <c r="B67" s="6" t="inlineStr">
+      <c r="B67" s="15" t="inlineStr">
         <is>
           <t>PB-HM-58.1</t>
         </is>
       </c>
-      <c r="C67" s="4" t="inlineStr">
+      <c r="C67" s="13" t="inlineStr">
         <is>
           <t>Como usuario quiero tener soporte para modo oscuro y modo claro en toda la interfaz para adaptar la visualización de la plataforma a mi comodidad visual y condiciones lumínicas del entorno.</t>
         </is>
       </c>
-      <c r="D67" s="4" t="inlineStr">
+      <c r="D67" s="13" t="inlineStr">
         <is>
           <t>- [ ] Diseñar e implementar el componente UI necesario
 - [ ] Establecer lógica de estado (React hooks) y validaciones
 - [ ] Conectar la interfaz con la API Backend correspondiente</t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr">
-        <is>
-          <t>[Escenario 1:]
-- **Escenario 1:** Dado que me encuentro en las configuraciones de mi perfil, Cuando altero el switch a "Modo Oscuro", Entonces todas las vistas, fondos, tipografías y paletas de color de los gráficos se actualizan de forma instantánea.
-[Escenario 2:]
-- **Escenario 2:** Dado que he seleccionado una preferencia visual previamente, Cuando inicio una nueva sesión en un dispositivo distinto, Entonces la plataforma recuerda el tema que guardé y lo aplica desde el primer pantallazo de carga.</t>
-        </is>
-      </c>
-      <c r="F67" s="3" t="inlineStr">
+      <c r="E67" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 1:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que me encuentro en las configuraciones de mi perfil, Cuando altero el switch a "Modo Oscuro", Entonces todas las vistas, fondos, tipografías y paletas de color de los gráficos se actualizan de forma instantánea.
+- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 2:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que he seleccionado una preferencia visual previamente, Cuando inicio una nueva sesión en un dispositivo distinto, Entonces la plataforma recuerda el tema que guardé y lo aplica desde el primer pantallazo de carga.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F67" s="12" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G67" s="3" t="inlineStr">
-        <is>
-          <t>[Pendiente screenshot]</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="120" customHeight="1">
-      <c r="A68" s="3" t="inlineStr">
+      <c r="G67" s="12" t="inlineStr">
+        <is>
+          <t>[Pendiente screenshot]</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="120" customHeight="1" s="9">
+      <c r="A68" s="12" t="inlineStr">
         <is>
           <t>PB-HM-59</t>
         </is>
       </c>
-      <c r="B68" s="6" t="inlineStr">
+      <c r="B68" s="15" t="inlineStr">
         <is>
           <t>PB-HM-59.1</t>
         </is>
       </c>
-      <c r="C68" s="4" t="inlineStr">
+      <c r="C68" s="13" t="inlineStr">
         <is>
           <t>Como Consultor / Analista quiero recibir una notificación vía Telegram cuando mis descargas de logs o informes están listas para poder seguir trabajando sin tener que estar comprobando la plataforma manualmente.</t>
         </is>
       </c>
-      <c r="D68" s="4" t="inlineStr">
+      <c r="D68" s="13" t="inlineStr">
         <is>
           <t>- [ ] Diseñar e implementar el componente UI necesario
 - [ ] Establecer lógica de estado (React hooks) y validaciones
 - [ ] Conectar la interfaz con la API Backend correspondiente</t>
         </is>
       </c>
-      <c r="E68" s="4" t="inlineStr">
-        <is>
-          <t>[Escenario 1:]
-- **Escenario 1:** Dado que he solicitado una descarga asíncrona masiva de logs y tengo vinculado mi Telegram, Cuando el backend termina de generar el archivo, Entonces el Bot me envía un mensaje avisándome que está listo para ser descargado.
-[Escenario 2:]
-- **Escenario 2:** Dado que la solicitud de exportación falla a mitad de proceso, Cuando el backend cancela la tarea, Entonces el sistema envía una notificación vía Telegram indicando la falla y sugiriendo que intente de nuevo.</t>
-        </is>
-      </c>
-      <c r="F68" s="3" t="inlineStr">
+      <c r="E68" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 1:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que he solicitado una descarga asíncrona masiva de logs y tengo vinculado mi Telegram, Cuando el backend termina de generar el archivo, Entonces el Bot me envía un mensaje avisándome que está listo para ser descargado.
+- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 2:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que la solicitud de exportación falla a mitad de proceso, Cuando el backend cancela la tarea, Entonces el sistema envía una notificación vía Telegram indicando la falla y sugiriendo que intente de nuevo.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F68" s="12" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G68" s="3" t="inlineStr">
-        <is>
-          <t>[Pendiente screenshot]</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="120" customHeight="1">
-      <c r="A69" s="3" t="inlineStr">
+      <c r="G68" s="12" t="inlineStr">
+        <is>
+          <t>[Pendiente screenshot]</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="120" customHeight="1" s="9">
+      <c r="A69" s="12" t="inlineStr">
         <is>
           <t>PB-HM-60</t>
         </is>
       </c>
-      <c r="B69" s="6" t="inlineStr">
+      <c r="B69" s="15" t="inlineStr">
         <is>
           <t>PB-HM-60.1</t>
         </is>
       </c>
-      <c r="C69" s="4" t="inlineStr">
+      <c r="C69" s="13" t="inlineStr">
         <is>
           <t>Como Sistema quiero eliminar automáticamente los archivos de logs expirados pasados los 7 días para optimizar y asegurar la disponibilidad del espacio en disco del servidor de forma constante.</t>
         </is>
       </c>
-      <c r="D69" s="4" t="inlineStr">
+      <c r="D69" s="13" t="inlineStr">
         <is>
           <t>- [ ] Desarrollar formulario/modal para la acción
 - [ ] Validar permisos del rol en el frontend
 - [ ] Conectar endpoint CRUD y mostrar notificación de resultado</t>
         </is>
       </c>
-      <c r="E69" s="4" t="inlineStr">
-        <is>
-          <t>[Escenario 1:]
-- **Escenario 1:** Dado que existen archivos JSONL generados por descargas pasadas, Cuando el sistema ejecuta el cronjob programado de mantenimiento, Entonces evalúa su fecha de creación y borra permanentemente todos los que superan el límite de 7 días.
-[Escenario 2:]
-- **Escenario 2:** Dado que el cron evalúa un archivo generado hace 4 días, Cuando detecta su fecha, Entonces lo ignora y lo mantiene disponible en el volumen de almacenamiento sin realizar ninguna acción.</t>
-        </is>
-      </c>
-      <c r="F69" s="3" t="inlineStr">
+      <c r="E69" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 1:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que existen archivos JSONL generados por descargas pasadas, Cuando el sistema ejecuta el cronjob programado de mantenimiento, Entonces evalúa su fecha de creación y borra permanentemente todos los que superan el límite de 7 días.
+- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 2:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que el cron evalúa un archivo generado hace 4 días, Cuando detecta su fecha, Entonces lo ignora y lo mantiene disponible en el volumen de almacenamiento sin realizar ninguna acción.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F69" s="12" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G69" s="3" t="inlineStr">
-        <is>
-          <t>[Pendiente screenshot]</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="120" customHeight="1">
-      <c r="A70" s="3" t="inlineStr">
+      <c r="G69" s="12" t="inlineStr">
+        <is>
+          <t>[Pendiente screenshot]</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="120" customHeight="1" s="9">
+      <c r="A70" s="12" t="inlineStr">
         <is>
           <t>PB-HM-64</t>
         </is>
       </c>
-      <c r="B70" s="6" t="inlineStr">
+      <c r="B70" s="15" t="inlineStr">
         <is>
           <t>PB-HM-64.1</t>
         </is>
       </c>
-      <c r="C70" s="4" t="inlineStr">
+      <c r="C70" s="13" t="inlineStr">
         <is>
           <t>Como Analista / Administrador quiero contar con un panel de Patch Intelligence (Priorización CVEs) para cruzar los ataques reales recibidos con las vulnerabilidades reportadas y saber qué debo parchar con mayor urgencia.</t>
         </is>
       </c>
-      <c r="D70" s="4" t="inlineStr">
+      <c r="D70" s="13" t="inlineStr">
         <is>
           <t>- [ ] Diseñar e implementar el componente UI necesario
 - [ ] Establecer lógica de estado (React hooks) y validaciones
 - [ ] Conectar la interfaz con la API Backend correspondiente</t>
         </is>
       </c>
-      <c r="E70" s="4" t="inlineStr">
-        <is>
-          <t>[Escenario 1:]
-- **Escenario 1:** Dado que un CVE con severidad alta (&gt;7.0) está pendiente por parchar y Wazuh detecta eventos relacionados, Cuando consulto el panel, Entonces el sistema clasifica esta vulnerabilidad con una prioridad crítica como "Parchar HOY".
-[Escenario 2:]
-- **Escenario 2:** Dado que reviso los CVEs priorizados, Cuando hago clic en ver el detalle de uno, Entonces la interfaz me muestra el número de ataques externos recientes que han intentado explotar esa brecha específica de mi sistema.</t>
-        </is>
-      </c>
-      <c r="F70" s="3" t="inlineStr">
+      <c r="E70" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 1:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que un CVE con severidad alta (&gt;7.0) está pendiente por parchar y Wazuh detecta eventos relacionados, Cuando consulto el panel, Entonces el sistema clasifica esta vulnerabilidad con una prioridad crítica como "Parchar HOY".
+- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 2:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que reviso los CVEs priorizados, Cuando hago clic en ver el detalle de uno, Entonces la interfaz me muestra el número de ataques externos recientes que han intentado explotar esa brecha específica de mi sistema.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F70" s="12" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="G70" s="3" t="inlineStr">
-        <is>
-          <t>[Pendiente screenshot]</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="120" customHeight="1">
-      <c r="A71" s="3" t="inlineStr">
+      <c r="G70" s="12" t="inlineStr">
+        <is>
+          <t>[Pendiente screenshot]</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="120" customHeight="1" s="9">
+      <c r="A71" s="12" t="inlineStr">
         <is>
           <t>PB-HM-65</t>
         </is>
       </c>
-      <c r="B71" s="6" t="inlineStr">
+      <c r="B71" s="15" t="inlineStr">
         <is>
           <t>PB-HM-65.1</t>
         </is>
       </c>
-      <c r="C71" s="4" t="inlineStr">
+      <c r="C71" s="13" t="inlineStr">
         <is>
           <t>Como Consultor quiero disponer del Honeypot Advisor para visualizar los diccionarios SSH y nombres de usuario clasificados que emplean los atacantes con el fin de anticipar posibles amenazas dirigidas a perfiles específicos.</t>
         </is>
       </c>
-      <c r="D71" s="4" t="inlineStr">
+      <c r="D71" s="13" t="inlineStr">
         <is>
           <t>- [ ] Diseñar e implementar el componente UI necesario
 - [ ] Establecer lógica de estado (React hooks) y validaciones
 - [ ] Conectar la interfaz con la API Backend correspondiente</t>
         </is>
       </c>
-      <c r="E71" s="4" t="inlineStr">
-        <is>
-          <t>[Escenario 1:]
-- **Escenario 1:** Dado que los atacantes han intentado múltiples combinaciones de contraseñas por fuerza bruta, Cuando accedo al Advisor, Entonces se despliegan en listas estadísticas los nombres de usuario más probados en el periodo evaluado.
-[Escenario 2:]
-- **Escenario 2:** Dado que consulto la lista de usuarios atacados, Cuando reviso el desglose, Entonces veo la información clasificada y categorizada según la industria del software o su finalidad (Ej. nombres de Odoo, Jenkins, Bases de datos, etc.).</t>
-        </is>
-      </c>
-      <c r="F71" s="3" t="inlineStr">
+      <c r="E71" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 1:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que los atacantes han intentado múltiples combinaciones de contraseñas por fuerza bruta, Cuando accedo al Advisor, Entonces se despliegan en listas estadísticas los nombres de usuario más probados en el periodo evaluado.
+- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 2:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que consulto la lista de usuarios atacados, Cuando reviso el desglose, Entonces veo la información clasificada y categorizada según la industria del software o su finalidad (Ej. nombres de Odoo, Jenkins, Bases de datos, etc.).</t>
+          </r>
+        </is>
+      </c>
+      <c r="F71" s="12" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G71" s="3" t="inlineStr">
-        <is>
-          <t>[Pendiente screenshot]</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="120" customHeight="1">
-      <c r="A72" s="3" t="inlineStr">
+      <c r="G71" s="12" t="inlineStr">
+        <is>
+          <t>[Pendiente screenshot]</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="120" customHeight="1" s="9">
+      <c r="A72" s="12" t="inlineStr">
         <is>
           <t>PB-HM-66</t>
         </is>
       </c>
-      <c r="B72" s="6" t="inlineStr">
+      <c r="B72" s="15" t="inlineStr">
         <is>
           <t>PB-HM-66.1</t>
         </is>
       </c>
-      <c r="C72" s="4" t="inlineStr">
+      <c r="C72" s="13" t="inlineStr">
         <is>
           <t>Como Analista quiero visualizar un Timeline de Integridad (FIM Correlacionado) para rastrear de forma temporal los intentos de penetración y cruzarlos de inmediato con cualquier alteración anómala interna en archivos críticos.</t>
         </is>
       </c>
-      <c r="D72" s="4" t="inlineStr">
+      <c r="D72" s="13" t="inlineStr">
         <is>
           <t>- [ ] Diseñar e implementar el componente UI necesario
 - [ ] Establecer lógica de estado (React hooks) y validaciones
 - [ ] Conectar la interfaz con la API Backend correspondiente</t>
         </is>
       </c>
-      <c r="E72" s="4" t="inlineStr">
-        <is>
-          <t>[Escenario 1:]
-- **Escenario 1:** Dado que ha ocurrido un potencial compromiso post-explotación, Cuando accedo a la línea de tiempo FIM, Entonces puedo contrastar sincrónicamente sobre el mismo gráfico los intentos de acceso del atacante con la alteración detectada por dpkg.
-[Escenario 2:]
-- **Escenario 2:** Dado que encuentro un evento anómalo del sistema FIM en el timeline, Cuando clico sobre él, Entonces el panel expande el registro exacto mostrándome qué archivo crítico fue modificado por el posible atacante.</t>
-        </is>
-      </c>
-      <c r="F72" s="3" t="inlineStr">
+      <c r="E72" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 1:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que ha ocurrido un potencial compromiso post-explotación, Cuando accedo a la línea de tiempo FIM, Entonces puedo contrastar sincrónicamente sobre el mismo gráfico los intentos de acceso del atacante con la alteración detectada por dpkg.
+- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 2:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que encuentro un evento anómalo del sistema FIM en el timeline, Cuando clico sobre él, Entonces el panel expande el registro exacto mostrándome qué archivo crítico fue modificado por el posible atacante.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F72" s="12" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="G72" s="3" t="inlineStr">
-        <is>
-          <t>[Pendiente screenshot]</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="120" customHeight="1">
-      <c r="A73" s="3" t="inlineStr">
+      <c r="G72" s="12" t="inlineStr">
+        <is>
+          <t>[Pendiente screenshot]</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="120" customHeight="1" s="9">
+      <c r="A73" s="12" t="inlineStr">
         <is>
           <t>PB-HM-67</t>
         </is>
       </c>
-      <c r="B73" s="6" t="inlineStr">
+      <c r="B73" s="15" t="inlineStr">
         <is>
           <t>PB-HM-67.1</t>
         </is>
       </c>
-      <c r="C73" s="4" t="inlineStr">
+      <c r="C73" s="13" t="inlineStr">
         <is>
           <t>Como Analista quiero disponer del Kill Chain Visualizer alineado a MITRE ATT&amp;CK para mapear el comportamiento entero de un atacante desde que hace el escaneo hasta los posibles indicios de post-explotación de manera gráfica.</t>
         </is>
       </c>
-      <c r="D73" s="4" t="inlineStr">
+      <c r="D73" s="13" t="inlineStr">
         <is>
           <t>- [ ] Diseñar e implementar el componente UI necesario
 - [ ] Establecer lógica de estado (React hooks) y validaciones
 - [ ] Conectar la interfaz con la API Backend correspondiente</t>
         </is>
       </c>
-      <c r="E73" s="4" t="inlineStr">
-        <is>
-          <t>[Escenario 1:]
-- **Escenario 1:** Dado que la IA o Wazuh ha enlazado múltiples eventos de un mismo actor malicioso, Cuando accedo a la vista Kill Chain, Entonces visualizo un diagrama paso a paso acomodando las acciones bajo las tácticas de reconocimiento, persistencia o impacto según MITRE.
-[Escenario 2:]
-- **Escenario 2:** Dado que selecciono un atacante cuya IP cruzó varias fases, Cuando observo la representación visual, Entonces visualizo flechas y secuencias claras desde la fase exploratoria inicial hasta los eventos críticos más recientes en tiempo real.</t>
-        </is>
-      </c>
-      <c r="F73" s="3" t="inlineStr">
+      <c r="E73" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 1:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que la IA o Wazuh ha enlazado múltiples eventos de un mismo actor malicioso, Cuando accedo a la vista Kill Chain, Entonces visualizo un diagrama paso a paso acomodando las acciones bajo las tácticas de reconocimiento, persistencia o impacto según MITRE.
+- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 2:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que selecciono un atacante cuya IP cruzó varias fases, Cuando observo la representación visual, Entonces visualizo flechas y secuencias claras desde la fase exploratoria inicial hasta los eventos críticos más recientes en tiempo real.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F73" s="12" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="G73" s="3" t="inlineStr">
-        <is>
-          <t>[Pendiente screenshot]</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="120" customHeight="1">
-      <c r="A74" s="3" t="inlineStr">
+      <c r="G73" s="12" t="inlineStr">
+        <is>
+          <t>[Pendiente screenshot]</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="120" customHeight="1" s="9">
+      <c r="A74" s="12" t="inlineStr">
         <is>
           <t>PB-HM-68</t>
         </is>
       </c>
-      <c r="B74" s="6" t="inlineStr">
+      <c r="B74" s="15" t="inlineStr">
         <is>
           <t>PB-HM-68.1</t>
         </is>
       </c>
-      <c r="C74" s="4" t="inlineStr">
+      <c r="C74" s="13" t="inlineStr">
         <is>
           <t>Como Analista quiero poder utilizar un entorno HITL (Human-in-the-Loop) sobre Rootcheck para validar o rechazar alertas complejas de forma manual y reentrenar de mejor forma el modelo de detección.</t>
         </is>
       </c>
-      <c r="D74" s="4" t="inlineStr">
+      <c r="D74" s="13" t="inlineStr">
         <is>
           <t>- [ ] Diseñar e implementar el componente UI necesario
 - [ ] Establecer lógica de estado (React hooks) y validaciones
 - [ ] Conectar la interfaz con la API Backend correspondiente</t>
         </is>
       </c>
-      <c r="E74" s="4" t="inlineStr">
-        <is>
-          <t>[Escenario 1:]
-- **Escenario 1:** Dado que Rootcheck lanza una alerta por un posible troyano en un directorio del sistema (/bin/passwd), Cuando evalúo la información en el panel HITL, Entonces puedo decidir con botones explícitos marcarlo como "Compromiso Confirmado" o "Falso Positivo".
-[Escenario 2:]
-- **Escenario 2:** Dado que marco el evento como falso positivo, Cuando confirmo mi acción, Entonces el sistema ajusta la alerta en el histórico y etiqueta internamente la firma de ese evento para ser descartado como amenaza en el próximo ciclo de ML.</t>
-        </is>
-      </c>
-      <c r="F74" s="3" t="inlineStr">
+      <c r="E74" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 1:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que Rootcheck lanza una alerta por un posible troyano en un directorio del sistema (/bin/passwd), Cuando evalúo la información en el panel HITL, Entonces puedo decidir con botones explícitos marcarlo como "Compromiso Confirmado" o "Falso Positivo".
+- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 2:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que marco el evento como falso positivo, Cuando confirmo mi acción, Entonces el sistema ajusta la alerta en el histórico y etiqueta internamente la firma de ese evento para ser descartado como amenaza en el próximo ciclo de ML.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F74" s="12" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G74" s="3" t="inlineStr">
-        <is>
-          <t>[Pendiente screenshot]</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="120" customHeight="1">
-      <c r="A75" s="3" t="inlineStr">
+      <c r="G74" s="12" t="inlineStr">
+        <is>
+          <t>[Pendiente screenshot]</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="120" customHeight="1" s="9">
+      <c r="A75" s="12" t="inlineStr">
         <is>
           <t>PB-HM-69</t>
         </is>
       </c>
-      <c r="B75" s="6" t="inlineStr">
+      <c r="B75" s="15" t="inlineStr">
         <is>
           <t>PB-HM-69.1</t>
         </is>
       </c>
-      <c r="C75" s="4" t="inlineStr">
+      <c r="C75" s="13" t="inlineStr">
         <is>
           <t>Como Consultor quiero consultar un Dashboard de Compliance basado en el estándar CIS Benchmark para identificar deficiencias de hardening y saber exactamente cómo remediarlas.</t>
         </is>
       </c>
-      <c r="D75" s="4" t="inlineStr">
+      <c r="D75" s="13" t="inlineStr">
         <is>
           <t>- [ ] Preparar componente contenedor de la visualización
 - [ ] Integrar librería Plotly.js / Chart.js
 - [ ] Conectar endpoint para inyección dinámica de datos</t>
         </is>
       </c>
-      <c r="E75" s="4" t="inlineStr">
-        <is>
-          <t>[Escenario 1:]
-- **Escenario 1:** Dado que Wazuh terminó sus tareas de auditoría de configuración SCA, Cuando cargo el dashboard de Compliance, Entonces observo de manera destacada el porcentaje de cumplimiento CIS general de mi entorno (ej. 45%).
-[Escenario 2:]
-- **Escenario 2:** Dado que deseo aumentar mi nivel de hardening, Cuando bajo al desglose del reporte, Entonces encuentro listadas las recomendaciones de reparación (remediaciones) jerarquizadas por su peso o impacto sobre el score total del sistema.</t>
-        </is>
-      </c>
-      <c r="F75" s="3" t="inlineStr">
+      <c r="E75" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 1:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que Wazuh terminó sus tareas de auditoría de configuración SCA, Cuando cargo el dashboard de Compliance, Entonces observo de manera destacada el porcentaje de cumplimiento CIS general de mi entorno (ej. 45%).
+- </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Escenario 2:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Dado que deseo aumentar mi nivel de hardening, Cuando bajo al desglose del reporte, Entonces encuentro listadas las recomendaciones de reparación (remediaciones) jerarquizadas por su peso o impacto sobre el score total del sistema.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F75" s="12" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G75" s="3" t="inlineStr">
+      <c r="G75" s="12" t="inlineStr">
         <is>
           <t>[Pendiente screenshot]</t>
         </is>
@@ -5473,77 +6673,79 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B29" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B30" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B32" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B33" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B34" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B35" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B36" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B37" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B38" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B39" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B40" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B41" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B42" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B43" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B44" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B45" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B46" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B47" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B48" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B49" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B50" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B51" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B52" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B53" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B54" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B55" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B56" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B57" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B58" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B59" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B60" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B61" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B62" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B63" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B64" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B65" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B66" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B67" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B68" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B69" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B70" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B71" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B72" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B73" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B74" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B75" r:id="rId70"/>
+    <hyperlink ref="B6" location="'PRODUCT BACKLOG'!A7" display="PB-HM-01.1"/>
+    <hyperlink ref="B7" location="'PRODUCT BACKLOG'!A8" display="PB-HM-02.1"/>
+    <hyperlink ref="B8" location="'PRODUCT BACKLOG'!A9" display="PB-HM-03.1"/>
+    <hyperlink ref="B9" location="'PRODUCT BACKLOG'!A10" display="PB-HM-04.1"/>
+    <hyperlink ref="B10" location="'PRODUCT BACKLOG'!A11" display="PB-HM-05.1"/>
+    <hyperlink ref="B11" location="'PRODUCT BACKLOG'!A12" display="PB-HM-06.1"/>
+    <hyperlink ref="B12" location="'PRODUCT BACKLOG'!A13" display="PB-HM-07.1"/>
+    <hyperlink ref="B13" location="'PRODUCT BACKLOG'!A14" display="PB-HM-08.1"/>
+    <hyperlink ref="B14" location="'PRODUCT BACKLOG'!A15" display="PB-HM-09.1"/>
+    <hyperlink ref="B15" location="'PRODUCT BACKLOG'!A16" display="PB-HM-10.1"/>
+    <hyperlink ref="B16" location="'PRODUCT BACKLOG'!A17" display="PB-HM-11.1"/>
+    <hyperlink ref="B17" location="'PRODUCT BACKLOG'!A18" display="PB-HM-12.1"/>
+    <hyperlink ref="B18" location="'PRODUCT BACKLOG'!A19" display="PB-HM-13.1"/>
+    <hyperlink ref="B19" location="'PRODUCT BACKLOG'!A20" display="PB-HM-14.1"/>
+    <hyperlink ref="B20" location="'PRODUCT BACKLOG'!A21" display="PB-HM-15.1"/>
+    <hyperlink ref="B21" location="'PRODUCT BACKLOG'!A22" display="PB-HM-16.1"/>
+    <hyperlink ref="B22" location="'PRODUCT BACKLOG'!A23" display="PB-HM-17.1"/>
+    <hyperlink ref="B23" location="'PRODUCT BACKLOG'!A24" display="PB-HM-18.1"/>
+    <hyperlink ref="B24" location="'PRODUCT BACKLOG'!A25" display="PB-HM-19.1"/>
+    <hyperlink ref="B25" location="'PRODUCT BACKLOG'!A26" display="PB-HM-20.1"/>
+    <hyperlink ref="B26" location="'PRODUCT BACKLOG'!A27" display="PB-HM-21.1"/>
+    <hyperlink ref="B27" location="'PRODUCT BACKLOG'!A28" display="PB-HM-22.1"/>
+    <hyperlink ref="B28" location="'PRODUCT BACKLOG'!A29" display="PB-HM-23.1"/>
+    <hyperlink ref="B29" location="'PRODUCT BACKLOG'!A30" display="PB-HM-24.1"/>
+    <hyperlink ref="B30" location="'PRODUCT BACKLOG'!A31" display="PB-HM-25.1"/>
+    <hyperlink ref="B31" location="'PRODUCT BACKLOG'!A67" display="PB-HM-61.1"/>
+    <hyperlink ref="B32" location="'PRODUCT BACKLOG'!A32" display="PB-HM-26.1"/>
+    <hyperlink ref="B33" location="'PRODUCT BACKLOG'!A33" display="PB-HM-27.1"/>
+    <hyperlink ref="B34" location="'PRODUCT BACKLOG'!A34" display="PB-HM-28.1"/>
+    <hyperlink ref="B35" location="'PRODUCT BACKLOG'!A35" display="PB-HM-29.1"/>
+    <hyperlink ref="B36" location="'PRODUCT BACKLOG'!A36" display="PB-HM-30.1"/>
+    <hyperlink ref="B37" location="'PRODUCT BACKLOG'!A37" display="PB-HM-31.1"/>
+    <hyperlink ref="B38" location="'PRODUCT BACKLOG'!A38" display="PB-HM-32.1"/>
+    <hyperlink ref="B39" location="'PRODUCT BACKLOG'!A39" display="PB-HM-33.1"/>
+    <hyperlink ref="B40" location="'PRODUCT BACKLOG'!A40" display="PB-HM-34.1"/>
+    <hyperlink ref="B41" location="'PRODUCT BACKLOG'!A41" display="PB-HM-35.1"/>
+    <hyperlink ref="B42" location="'PRODUCT BACKLOG'!A42" display="PB-HM-36.1"/>
+    <hyperlink ref="B43" location="'PRODUCT BACKLOG'!A43" display="PB-HM-37.1"/>
+    <hyperlink ref="B44" location="'PRODUCT BACKLOG'!A44" display="PB-HM-38.1"/>
+    <hyperlink ref="B45" location="'PRODUCT BACKLOG'!A45" display="PB-HM-39.1"/>
+    <hyperlink ref="B46" location="'PRODUCT BACKLOG'!A46" display="PB-HM-40.1"/>
+    <hyperlink ref="B47" location="'PRODUCT BACKLOG'!A47" display="PB-HM-41.1"/>
+    <hyperlink ref="B48" location="'PRODUCT BACKLOG'!A48" display="PB-HM-42.1"/>
+    <hyperlink ref="B49" location="'PRODUCT BACKLOG'!A49" display="PB-HM-43.1"/>
+    <hyperlink ref="B50" location="'PRODUCT BACKLOG'!A50" display="PB-HM-44.1"/>
+    <hyperlink ref="B51" location="'PRODUCT BACKLOG'!A51" display="PB-HM-45.1"/>
+    <hyperlink ref="B52" location="'PRODUCT BACKLOG'!A52" display="PB-HM-46.1"/>
+    <hyperlink ref="B53" location="'PRODUCT BACKLOG'!A53" display="PB-HM-47.1"/>
+    <hyperlink ref="B54" location="'PRODUCT BACKLOG'!A68" display="PB-HM-62.1"/>
+    <hyperlink ref="B55" location="'PRODUCT BACKLOG'!A69" display="PB-HM-63.1"/>
+    <hyperlink ref="B56" location="'PRODUCT BACKLOG'!A76" display="PB-HM-70.1"/>
+    <hyperlink ref="B57" location="'PRODUCT BACKLOG'!A54" display="PB-HM-48.1"/>
+    <hyperlink ref="B58" location="'PRODUCT BACKLOG'!A55" display="PB-HM-49.1"/>
+    <hyperlink ref="B59" location="'PRODUCT BACKLOG'!A56" display="PB-HM-50.1"/>
+    <hyperlink ref="B60" location="'PRODUCT BACKLOG'!A57" display="PB-HM-51.1"/>
+    <hyperlink ref="B61" location="'PRODUCT BACKLOG'!A58" display="PB-HM-52.1"/>
+    <hyperlink ref="B62" location="'PRODUCT BACKLOG'!A59" display="PB-HM-53.1"/>
+    <hyperlink ref="B63" location="'PRODUCT BACKLOG'!A60" display="PB-HM-54.1"/>
+    <hyperlink ref="B64" location="'PRODUCT BACKLOG'!A61" display="PB-HM-55.1"/>
+    <hyperlink ref="B65" location="'PRODUCT BACKLOG'!A62" display="PB-HM-56.1"/>
+    <hyperlink ref="B66" location="'PRODUCT BACKLOG'!A63" display="PB-HM-57.1"/>
+    <hyperlink ref="B67" location="'PRODUCT BACKLOG'!A64" display="PB-HM-58.1"/>
+    <hyperlink ref="B68" location="'PRODUCT BACKLOG'!A65" display="PB-HM-59.1"/>
+    <hyperlink ref="B69" location="'PRODUCT BACKLOG'!A66" display="PB-HM-60.1"/>
+    <hyperlink ref="B70" location="'PRODUCT BACKLOG'!A70" display="PB-HM-64.1"/>
+    <hyperlink ref="B71" location="'PRODUCT BACKLOG'!A71" display="PB-HM-65.1"/>
+    <hyperlink ref="B72" location="'PRODUCT BACKLOG'!A72" display="PB-HM-66.1"/>
+    <hyperlink ref="B73" location="'PRODUCT BACKLOG'!A73" display="PB-HM-67.1"/>
+    <hyperlink ref="B74" location="'PRODUCT BACKLOG'!A74" display="PB-HM-68.1"/>
+    <hyperlink ref="B75" location="'PRODUCT BACKLOG'!A75" display="PB-HM-69.1"/>
   </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>